--- a/data/processed/index.xlsx
+++ b/data/processed/index.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F588"/>
+  <dimension ref="A1:F596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,16 +615,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>595.6064887677256</v>
+        <v>530.1122359354024</v>
       </c>
       <c r="D9" t="n">
-        <v>385.904008141884</v>
+        <v>347.8038520365844</v>
       </c>
       <c r="E9" t="n">
-        <v>2253.484207532634</v>
+        <v>1802.280064666623</v>
       </c>
       <c r="F9" t="n">
-        <v>1203.449510720201</v>
+        <v>981.4130827266171</v>
       </c>
     </row>
     <row r="10">
@@ -669,16 +669,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>248.7444188246095</v>
+        <v>221.3919131612913</v>
       </c>
       <c r="D12" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E12" t="n">
-        <v>941.1274559699107</v>
+        <v>752.690099418157</v>
       </c>
       <c r="F12" t="n">
-        <v>601.7247553601005</v>
+        <v>490.7065413633085</v>
       </c>
     </row>
     <row r="13">
@@ -761,16 +761,16 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>116.3081233779535</v>
+        <v>103.5186159051103</v>
       </c>
       <c r="D17" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E17" t="n">
-        <v>178.8473479926249</v>
+        <v>179.158676549304</v>
       </c>
       <c r="F17" t="n">
-        <v>244.5542624957397</v>
+        <v>249.7967514060011</v>
       </c>
     </row>
     <row r="18">
@@ -779,16 +779,16 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>109.0873427744636</v>
+        <v>97.091848864955</v>
       </c>
       <c r="D18" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E18" t="n">
-        <v>167.7439321359853</v>
+        <v>168.035932419298</v>
       </c>
       <c r="F18" t="n">
-        <v>244.5542624957398</v>
+        <v>249.7967514060011</v>
       </c>
     </row>
     <row r="19">
@@ -869,16 +869,16 @@
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>248.8345109719564</v>
+        <v>221.4720985698974</v>
       </c>
       <c r="D23" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E23" t="n">
-        <v>941.46832067689</v>
+        <v>752.9627144487323</v>
       </c>
       <c r="F23" t="n">
-        <v>601.7247553601005</v>
+        <v>490.7065413633085</v>
       </c>
     </row>
     <row r="24">
@@ -925,16 +925,16 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>91.60427797247621</v>
+        <v>81.53126188686488</v>
       </c>
       <c r="D26" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E26" t="n">
-        <v>140.8601712789914</v>
+        <v>141.1053736502318</v>
       </c>
       <c r="F26" t="n">
-        <v>244.5542624957398</v>
+        <v>249.7967514060011</v>
       </c>
     </row>
     <row r="27">
@@ -961,16 +961,16 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>98.99597763596132</v>
+        <v>88.11015333594908</v>
       </c>
       <c r="D28" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E28" t="n">
-        <v>152.2264098836362</v>
+        <v>152.4913980369941</v>
       </c>
       <c r="F28" t="n">
-        <v>244.5542624957398</v>
+        <v>249.7967514060011</v>
       </c>
     </row>
     <row r="29">
@@ -1033,16 +1033,16 @@
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>254.0799130153741</v>
+        <v>226.140704198035</v>
       </c>
       <c r="D32" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E32" t="n">
-        <v>961.3143614603895</v>
+        <v>768.8350793612981</v>
       </c>
       <c r="F32" t="n">
-        <v>601.7247553601004</v>
+        <v>490.7065413633085</v>
       </c>
     </row>
     <row r="33">
@@ -1051,16 +1051,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>101.1680289785851</v>
+        <v>90.04336094117016</v>
       </c>
       <c r="D33" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E33" t="n">
-        <v>155.5663797073237</v>
+        <v>155.8371819138181</v>
       </c>
       <c r="F33" t="n">
-        <v>244.5542624957397</v>
+        <v>249.7967514060011</v>
       </c>
     </row>
     <row r="34">
@@ -1087,16 +1087,16 @@
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>474.3058921598699</v>
+        <v>422.1501305843884</v>
       </c>
       <c r="D35" t="n">
-        <v>385.9040081418839</v>
+        <v>347.8038520365844</v>
       </c>
       <c r="E35" t="n">
-        <v>1794.541962988535</v>
+        <v>1435.229585497377</v>
       </c>
       <c r="F35" t="n">
-        <v>1203.449510720201</v>
+        <v>981.4130827266171</v>
       </c>
     </row>
     <row r="36">
@@ -1105,16 +1105,16 @@
         <v>11</v>
       </c>
       <c r="C36" t="n">
-        <v>213.2977599483302</v>
+        <v>189.8430500315078</v>
       </c>
       <c r="D36" t="n">
-        <v>385.904008141884</v>
+        <v>347.8038520365844</v>
       </c>
       <c r="E36" t="n">
-        <v>327.9886012395018</v>
+        <v>328.5595474625082</v>
       </c>
       <c r="F36" t="n">
-        <v>489.1085249914794</v>
+        <v>499.5935028120023</v>
       </c>
     </row>
     <row r="37">
@@ -1123,16 +1123,16 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>116.8223235493235</v>
+        <v>103.9762734486459</v>
       </c>
       <c r="D37" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E37" t="n">
-        <v>179.6380351287936</v>
+        <v>179.9507400742627</v>
       </c>
       <c r="F37" t="n">
-        <v>244.5542624957397</v>
+        <v>249.7967514060011</v>
       </c>
     </row>
     <row r="38">
@@ -1143,16 +1143,16 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>519.8428188888576</v>
+        <v>462.6797126174414</v>
       </c>
       <c r="D38" t="n">
-        <v>514.538677522512</v>
+        <v>463.7384693821124</v>
       </c>
       <c r="E38" t="n">
-        <v>794.0284027949756</v>
+        <v>791.8838823650058</v>
       </c>
       <c r="F38" t="n">
-        <v>650.2735466015619</v>
+        <v>662.9522566669917</v>
       </c>
     </row>
     <row r="39">
@@ -1161,16 +1161,16 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>140.1319840484568</v>
+        <v>124.7227503241011</v>
       </c>
       <c r="D39" t="n">
-        <v>257.269338761256</v>
+        <v>231.8692346910563</v>
       </c>
       <c r="E39" t="n">
-        <v>215.4813695563582</v>
+        <v>215.856468793379</v>
       </c>
       <c r="F39" t="n">
-        <v>326.0723499943197</v>
+        <v>333.0623352080015</v>
       </c>
     </row>
     <row r="40">
@@ -1179,16 +1179,16 @@
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>439.5598751078513</v>
+        <v>391.2248651001194</v>
       </c>
       <c r="D40" t="n">
-        <v>128.634669380628</v>
+        <v>115.9346173455281</v>
       </c>
       <c r="E40" t="n">
-        <v>668.1551350597298</v>
+        <v>664.1905974740174</v>
       </c>
       <c r="F40" t="n">
-        <v>161.1650216100824</v>
+        <v>163.3587538549896</v>
       </c>
     </row>
     <row r="41">
@@ -1197,16 +1197,16 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>63.67598913699166</v>
+        <v>56.67403161884115</v>
       </c>
       <c r="D41" t="n">
-        <v>128.634669380628</v>
+        <v>115.9346173455281</v>
       </c>
       <c r="E41" t="n">
-        <v>97.91475829208353</v>
+        <v>98.08520342710402</v>
       </c>
       <c r="F41" t="n">
-        <v>163.0361749971598</v>
+        <v>166.5311676040008</v>
       </c>
     </row>
     <row r="42">
@@ -1251,16 +1251,16 @@
         <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>51.37840897349473</v>
+        <v>45.72872151895652</v>
       </c>
       <c r="D44" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914609</v>
       </c>
       <c r="E44" t="n">
-        <v>79.00473261983512</v>
+        <v>79.14226012389611</v>
       </c>
       <c r="F44" t="n">
-        <v>122.2771312478698</v>
+        <v>124.8983757030006</v>
       </c>
     </row>
     <row r="45">
@@ -1269,16 +1269,16 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>111.5674057800538</v>
+        <v>99.29919846565225</v>
       </c>
       <c r="D45" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914609</v>
       </c>
       <c r="E45" t="n">
-        <v>422.1166017195345</v>
+        <v>337.5982550491961</v>
       </c>
       <c r="F45" t="n">
-        <v>300.8623776800503</v>
+        <v>245.3532706816543</v>
       </c>
     </row>
     <row r="46">
@@ -1287,16 +1287,16 @@
         <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>300.2762608363512</v>
+        <v>267.257195870405</v>
       </c>
       <c r="D46" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914609</v>
       </c>
       <c r="E46" t="n">
-        <v>456.4363968961352</v>
+        <v>453.7281048303712</v>
       </c>
       <c r="F46" t="n">
-        <v>120.8737662075617</v>
+        <v>122.5190653912422</v>
       </c>
     </row>
     <row r="47">
@@ -1305,16 +1305,16 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>286.2421037983191</v>
+        <v>254.7662668640874</v>
       </c>
       <c r="D47" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E47" t="n">
-        <v>435.9743677532917</v>
+        <v>433.9696751284858</v>
       </c>
       <c r="F47" t="n">
-        <v>243.1508974554316</v>
+        <v>247.4174410942427</v>
       </c>
     </row>
     <row r="48">
@@ -1361,16 +1361,16 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>112.6059536015944</v>
+        <v>100.2235451915278</v>
       </c>
       <c r="D50" t="n">
-        <v>231.5424048851304</v>
+        <v>208.6823112219506</v>
       </c>
       <c r="E50" t="n">
-        <v>296.0125542887823</v>
+        <v>252.4878479216471</v>
       </c>
       <c r="F50" t="n">
-        <v>510.291557785756</v>
+        <v>441.9782985564483</v>
       </c>
     </row>
     <row r="51">
@@ -1379,16 +1379,16 @@
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>330.7708217565842</v>
+        <v>294.3985050706096</v>
       </c>
       <c r="D51" t="n">
-        <v>154.3616032567536</v>
+        <v>139.1215408146338</v>
       </c>
       <c r="E51" t="n">
-        <v>503.4896478108492</v>
+        <v>500.9701298173769</v>
       </c>
       <c r="F51" t="n">
-        <v>194.5207179643453</v>
+        <v>197.9339528753942</v>
       </c>
     </row>
     <row r="52">
@@ -1397,16 +1397,16 @@
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>36.87772865236562</v>
+        <v>32.82256919761065</v>
       </c>
       <c r="D52" t="n">
-        <v>77.1808016283768</v>
+        <v>69.56077040731688</v>
       </c>
       <c r="E52" t="n">
-        <v>182.400729970324</v>
+        <v>137.6617644886888</v>
       </c>
       <c r="F52" t="n">
-        <v>314.6481477891642</v>
+        <v>242.1408974316474</v>
       </c>
     </row>
     <row r="53">
@@ -1451,16 +1451,16 @@
         <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>28.90819173582309</v>
+        <v>25.72938080246935</v>
       </c>
       <c r="D55" t="n">
-        <v>64.317334690314</v>
+        <v>57.96730867276406</v>
       </c>
       <c r="E55" t="n">
-        <v>44.45221259751054</v>
+        <v>44.52959279545311</v>
       </c>
       <c r="F55" t="n">
-        <v>81.5180874985799</v>
+        <v>83.26558380200038</v>
       </c>
     </row>
     <row r="56">
@@ -1469,16 +1469,16 @@
         <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>143.9119724365995</v>
+        <v>128.0870825367906</v>
       </c>
       <c r="D56" t="n">
-        <v>192.9520040709419</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E56" t="n">
-        <v>406.6991500054314</v>
+        <v>344.3226518292207</v>
       </c>
       <c r="F56" t="n">
-        <v>363.6110934505267</v>
+        <v>330.1000147251036</v>
       </c>
     </row>
     <row r="57">
@@ -1487,16 +1487,16 @@
         <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>219.2022622995565</v>
+        <v>195.0982797889443</v>
       </c>
       <c r="D57" t="n">
-        <v>128.634669380628</v>
+        <v>115.9346173455281</v>
       </c>
       <c r="E57" t="n">
-        <v>333.763309118689</v>
+        <v>332.1599294241134</v>
       </c>
       <c r="F57" t="n">
-        <v>162.1005983036211</v>
+        <v>164.9449607294952</v>
       </c>
     </row>
     <row r="58">
@@ -1541,16 +1541,16 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>25.80692978715241</v>
+        <v>22.96914071638068</v>
       </c>
       <c r="D60" t="n">
-        <v>64.317334690314</v>
+        <v>57.96730867276407</v>
       </c>
       <c r="E60" t="n">
-        <v>127.6435128595574</v>
+        <v>96.33531186328116</v>
       </c>
       <c r="F60" t="n">
-        <v>262.2067898243035</v>
+        <v>201.7840811930395</v>
       </c>
     </row>
     <row r="61">
@@ -1559,16 +1559,16 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>28.15820668033819</v>
+        <v>25.06186582038143</v>
       </c>
       <c r="D61" t="n">
-        <v>64.31733469031398</v>
+        <v>57.96730867276406</v>
       </c>
       <c r="E61" t="n">
-        <v>139.2731505121987</v>
+        <v>105.1124501997734</v>
       </c>
       <c r="F61" t="n">
-        <v>262.2067898243035</v>
+        <v>201.7840811930395</v>
       </c>
     </row>
     <row r="62">
@@ -1615,16 +1615,16 @@
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>184.2372457434186</v>
+        <v>163.978096487313</v>
       </c>
       <c r="D64" t="n">
-        <v>165.3874320608074</v>
+        <v>149.0587937299647</v>
       </c>
       <c r="E64" t="n">
-        <v>369.4787809026651</v>
+        <v>336.8397765684715</v>
       </c>
       <c r="F64" t="n">
-        <v>363.6920469667925</v>
+        <v>314.339178790744</v>
       </c>
     </row>
     <row r="65">
@@ -1633,16 +1633,16 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>27.51925997050215</v>
+        <v>24.493179153291</v>
       </c>
       <c r="D65" t="n">
-        <v>55.12914402026913</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E65" t="n">
-        <v>42.31644808205065</v>
+        <v>42.39011044748709</v>
       </c>
       <c r="F65" t="n">
-        <v>69.8726464273542</v>
+        <v>71.37050040171462</v>
       </c>
     </row>
     <row r="66">
@@ -1723,16 +1723,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>29.91388012337578</v>
+        <v>26.62448139293275</v>
       </c>
       <c r="D70" t="n">
-        <v>55.12914402026913</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E70" t="n">
-        <v>45.99866262866004</v>
+        <v>46.0787348098027</v>
       </c>
       <c r="F70" t="n">
-        <v>69.8726464273542</v>
+        <v>71.37050040171462</v>
       </c>
     </row>
     <row r="71">
@@ -1741,16 +1741,16 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>58.86786065964668</v>
+        <v>52.39461595454333</v>
       </c>
       <c r="D71" t="n">
-        <v>110.2582880405383</v>
+        <v>99.37252915330983</v>
       </c>
       <c r="E71" t="n">
-        <v>90.52128480109977</v>
+        <v>90.67885974566663</v>
       </c>
       <c r="F71" t="n">
-        <v>139.7452928547084</v>
+        <v>142.7410008034292</v>
       </c>
     </row>
     <row r="72">
@@ -1851,16 +1851,16 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>27.35817161945531</v>
+        <v>24.34980444605223</v>
       </c>
       <c r="D77" t="n">
-        <v>55.12914402026913</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E77" t="n">
-        <v>42.06874204449718</v>
+        <v>42.14197321559936</v>
       </c>
       <c r="F77" t="n">
-        <v>69.8726464273542</v>
+        <v>71.37050040171462</v>
       </c>
     </row>
     <row r="78">
@@ -1869,16 +1869,16 @@
         <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>691.179159752084</v>
+        <v>615.1755172550168</v>
       </c>
       <c r="D78" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E78" t="n">
-        <v>1245.291409231532</v>
+        <v>1320.109567678251</v>
       </c>
       <c r="F78" t="n">
-        <v>81.86817202045005</v>
+        <v>88.49327914786778</v>
       </c>
     </row>
     <row r="79">
@@ -1959,16 +1959,16 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>47.76612273259322</v>
+        <v>42.51365054153175</v>
       </c>
       <c r="D83" t="n">
-        <v>110.2582880405383</v>
+        <v>99.37252915330983</v>
       </c>
       <c r="E83" t="n">
-        <v>73.4501093002232</v>
+        <v>73.57796759263302</v>
       </c>
       <c r="F83" t="n">
-        <v>139.7452928547084</v>
+        <v>142.7410008034292</v>
       </c>
     </row>
     <row r="84">
@@ -1977,16 +1977,16 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>25.08881408098056</v>
+        <v>22.32999065700725</v>
       </c>
       <c r="D84" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E84" t="n">
-        <v>38.57914419341351</v>
+        <v>38.6463008463606</v>
       </c>
       <c r="F84" t="n">
-        <v>69.87264642735421</v>
+        <v>71.37050040171462</v>
       </c>
     </row>
     <row r="85">
@@ -2033,16 +2033,16 @@
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>22.71931497333239</v>
+        <v>20.22104709495657</v>
       </c>
       <c r="D87" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E87" t="n">
-        <v>112.3718782852889</v>
+        <v>84.80947990821004</v>
       </c>
       <c r="F87" t="n">
-        <v>224.7486769922602</v>
+        <v>172.9577838797481</v>
       </c>
     </row>
     <row r="88">
@@ -2051,16 +2051,16 @@
         <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>23.90924255415248</v>
+        <v>21.28012751527707</v>
       </c>
       <c r="D88" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E88" t="n">
-        <v>36.76531354071464</v>
+        <v>36.8293127675914</v>
       </c>
       <c r="F88" t="n">
-        <v>69.8726464273542</v>
+        <v>71.37050040171459</v>
       </c>
     </row>
     <row r="89">
@@ -2123,16 +2123,16 @@
         <v>7</v>
       </c>
       <c r="C92" t="n">
-        <v>23.98520055835678</v>
+        <v>21.34773300347321</v>
       </c>
       <c r="D92" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E92" t="n">
-        <v>36.88211439018416</v>
+        <v>36.94631693816293</v>
       </c>
       <c r="F92" t="n">
-        <v>69.8726464273542</v>
+        <v>71.37050040171462</v>
       </c>
     </row>
     <row r="93">
@@ -2159,16 +2159,16 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>83.10044790327099</v>
+        <v>73.9625324371105</v>
       </c>
       <c r="D94" t="n">
-        <v>110.2582880405383</v>
+        <v>99.37252915330981</v>
       </c>
       <c r="E94" t="n">
-        <v>126.7573676202806</v>
+        <v>126.2995457169042</v>
       </c>
       <c r="F94" t="n">
-        <v>138.9433699745323</v>
+        <v>141.3813949109959</v>
       </c>
     </row>
     <row r="95">
@@ -2213,16 +2213,16 @@
         <v>12</v>
       </c>
       <c r="C97" t="n">
-        <v>24.29091466026381</v>
+        <v>21.61983008296309</v>
       </c>
       <c r="D97" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E97" t="n">
-        <v>120.145158815109</v>
+        <v>90.67614235947713</v>
       </c>
       <c r="F97" t="n">
-        <v>224.7486769922602</v>
+        <v>172.9577838797481</v>
       </c>
     </row>
     <row r="98">
@@ -2269,16 +2269,16 @@
         <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>63.76459243310934</v>
+        <v>56.75289189370713</v>
       </c>
       <c r="D100" t="n">
-        <v>110.2582880405383</v>
+        <v>99.37252915330983</v>
       </c>
       <c r="E100" t="n">
-        <v>185.9554475874743</v>
+        <v>156.3695142201118</v>
       </c>
       <c r="F100" t="n">
-        <v>241.7940051016686</v>
+        <v>211.5723693626599</v>
       </c>
     </row>
     <row r="101">
@@ -2305,16 +2305,16 @@
         <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>22.39786414532084</v>
+        <v>19.93494373578557</v>
       </c>
       <c r="D102" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E102" t="n">
-        <v>34.4412624565572</v>
+        <v>34.5012160910458</v>
       </c>
       <c r="F102" t="n">
-        <v>69.8726464273542</v>
+        <v>71.37050040171462</v>
       </c>
     </row>
     <row r="103">
@@ -2323,16 +2323,16 @@
         <v>6</v>
       </c>
       <c r="C103" t="n">
-        <v>23.88015588437858</v>
+        <v>21.25423928229012</v>
       </c>
       <c r="D103" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E103" t="n">
-        <v>118.1135071027854</v>
+        <v>89.14281099841054</v>
       </c>
       <c r="F103" t="n">
-        <v>224.7486769922602</v>
+        <v>172.9577838797481</v>
       </c>
     </row>
     <row r="104">
@@ -2377,16 +2377,16 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>113.0730883465391</v>
+        <v>100.6393127306594</v>
       </c>
       <c r="D106" t="n">
-        <v>110.2582880405383</v>
+        <v>99.37252915330983</v>
       </c>
       <c r="E106" t="n">
-        <v>171.8773002136863</v>
+        <v>170.8574561968218</v>
       </c>
       <c r="F106" t="n">
-        <v>138.1414470943563</v>
+        <v>140.0217890185625</v>
       </c>
     </row>
     <row r="107">
@@ -2413,16 +2413,16 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>31.69113357597544</v>
+        <v>28.20630398779863</v>
       </c>
       <c r="D108" t="n">
-        <v>55.12914402026913</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E108" t="n">
-        <v>57.09763645814579</v>
+        <v>60.52811062651326</v>
       </c>
       <c r="F108" t="n">
-        <v>81.86817202045005</v>
+        <v>88.49327914786778</v>
       </c>
     </row>
     <row r="109">
@@ -2469,16 +2469,16 @@
         <v>2</v>
       </c>
       <c r="C111" t="n">
-        <v>106.260104717331</v>
+        <v>94.57550037605746</v>
       </c>
       <c r="D111" t="n">
-        <v>120.5950025443387</v>
+        <v>108.6887037614326</v>
       </c>
       <c r="E111" t="n">
-        <v>517.1697910959288</v>
+        <v>522.4514790930132</v>
       </c>
       <c r="F111" t="n">
-        <v>473.7036600728915</v>
+        <v>480.4023382055746</v>
       </c>
     </row>
     <row r="112">
@@ -2505,16 +2505,16 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>42.40938795022047</v>
+        <v>37.74595457725226</v>
       </c>
       <c r="D113" t="n">
-        <v>48.23800101773549</v>
+        <v>43.47548150457305</v>
       </c>
       <c r="E113" t="n">
-        <v>64.46459729002207</v>
+        <v>64.08209283036354</v>
       </c>
       <c r="F113" t="n">
-        <v>60.43688310378086</v>
+        <v>61.25953269562109</v>
       </c>
     </row>
     <row r="114">
@@ -2577,16 +2577,16 @@
         <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>17.9288122336527</v>
+        <v>15.95731900186552</v>
       </c>
       <c r="D117" t="n">
-        <v>48.2380010177355</v>
+        <v>43.47548150457305</v>
       </c>
       <c r="E117" t="n">
-        <v>88.67759914788978</v>
+        <v>66.92689646201126</v>
       </c>
       <c r="F117" t="n">
-        <v>196.6550923682276</v>
+        <v>151.3380608947796</v>
       </c>
     </row>
     <row r="118">
@@ -2759,16 +2759,16 @@
         <v>6</v>
       </c>
       <c r="C127" t="n">
-        <v>17.02998289133226</v>
+        <v>15.1573269914231</v>
       </c>
       <c r="D127" t="n">
-        <v>35.0821825583531</v>
+        <v>31.61853200332586</v>
       </c>
       <c r="E127" t="n">
-        <v>26.18705545249886</v>
+        <v>26.23264057449932</v>
       </c>
       <c r="F127" t="n">
-        <v>44.46441136286177</v>
+        <v>45.41759116472748</v>
       </c>
     </row>
     <row r="128">
@@ -2777,16 +2777,16 @@
         <v>7</v>
       </c>
       <c r="C128" t="n">
-        <v>26.53999812491263</v>
+        <v>23.62159918174684</v>
       </c>
       <c r="D128" t="n">
-        <v>52.62327383752963</v>
+        <v>47.42779800498877</v>
       </c>
       <c r="E128" t="n">
-        <v>180.6900354920178</v>
+        <v>106.2386290095018</v>
       </c>
       <c r="F128" t="n">
-        <v>295.3008285783051</v>
+        <v>177.0390735378136</v>
       </c>
     </row>
     <row r="129">
@@ -2795,16 +2795,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>26.16201993324255</v>
+        <v>23.28518433721484</v>
       </c>
       <c r="D129" t="n">
-        <v>52.62327383752963</v>
+        <v>47.42779800498877</v>
       </c>
       <c r="E129" t="n">
-        <v>178.116678382246</v>
+        <v>104.7255963148678</v>
       </c>
       <c r="F129" t="n">
-        <v>295.3008285783051</v>
+        <v>177.0390735378136</v>
       </c>
     </row>
     <row r="130">
@@ -2867,16 +2867,16 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>17.94754662470145</v>
+        <v>15.97399331639202</v>
       </c>
       <c r="D133" t="n">
-        <v>35.0821825583531</v>
+        <v>31.61853200332585</v>
       </c>
       <c r="E133" t="n">
-        <v>35.61429117502363</v>
+        <v>36.58931539132443</v>
       </c>
       <c r="F133" t="n">
-        <v>57.3798364429046</v>
+        <v>60.10982905045508</v>
       </c>
     </row>
     <row r="134">
@@ -2941,16 +2941,16 @@
         <v>4</v>
       </c>
       <c r="C137" t="n">
-        <v>64.41297006123139</v>
+        <v>57.32997243372174</v>
       </c>
       <c r="D137" t="n">
-        <v>103.8972329612765</v>
+        <v>93.63949862523425</v>
       </c>
       <c r="E137" t="n">
-        <v>262.9171475422724</v>
+        <v>182.8007347456792</v>
       </c>
       <c r="F137" t="n">
-        <v>408.0803783182635</v>
+        <v>280.6315813568581</v>
       </c>
     </row>
     <row r="138">
@@ -3105,16 +3105,16 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>40.43346630275553</v>
+        <v>35.98730979697471</v>
       </c>
       <c r="D146" t="n">
-        <v>68.91143002533641</v>
+        <v>62.10783072081864</v>
       </c>
       <c r="E146" t="n">
-        <v>219.8424256625186</v>
+        <v>143.9469333405421</v>
       </c>
       <c r="F146" t="n">
-        <v>317.9827589343969</v>
+        <v>209.2030636887547</v>
       </c>
     </row>
     <row r="147">
@@ -3123,16 +3123,16 @@
         <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>28.75694130817343</v>
+        <v>25.59476221805226</v>
       </c>
       <c r="D147" t="n">
-        <v>27.56457201013457</v>
+        <v>24.84313228832746</v>
       </c>
       <c r="E147" t="n">
-        <v>43.71212909038373</v>
+        <v>43.45276061495498</v>
       </c>
       <c r="F147" t="n">
-        <v>34.53536177358907</v>
+        <v>35.00544725464063</v>
       </c>
     </row>
     <row r="148">
@@ -3141,16 +3141,16 @@
         <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>11.12530499714304</v>
+        <v>9.901940994129717</v>
       </c>
       <c r="D148" t="n">
-        <v>27.56457201013457</v>
+        <v>24.84313228832746</v>
       </c>
       <c r="E148" t="n">
-        <v>55.02680958880617</v>
+        <v>41.52991988250593</v>
       </c>
       <c r="F148" t="n">
-        <v>112.3743384961301</v>
+        <v>86.47889193987405</v>
       </c>
     </row>
     <row r="149">
@@ -3177,16 +3177,16 @@
         <v>5</v>
       </c>
       <c r="C150" t="n">
-        <v>285.0755538562538</v>
+        <v>253.7279934238534</v>
       </c>
       <c r="D150" t="n">
-        <v>38.59040081418841</v>
+        <v>34.78038520365844</v>
       </c>
       <c r="E150" t="n">
-        <v>139.4081101001345</v>
+        <v>125.1890534169529</v>
       </c>
       <c r="F150" t="n">
-        <v>15.55467134118241</v>
+        <v>14.24279959320191</v>
       </c>
     </row>
     <row r="151">
@@ -3195,16 +3195,16 @@
         <v>6</v>
       </c>
       <c r="C151" t="n">
-        <v>246.9096689994387</v>
+        <v>219.7589166265898</v>
       </c>
       <c r="D151" t="n">
-        <v>64.31733469031401</v>
+        <v>57.96730867276407</v>
       </c>
       <c r="E151" t="n">
-        <v>144.5823946540934</v>
+        <v>133.2116701008283</v>
       </c>
       <c r="F151" t="n">
-        <v>47.78767566319888</v>
+        <v>46.91455036419983</v>
       </c>
     </row>
     <row r="152">
@@ -3231,16 +3231,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="n">
-        <v>266.9453499330265</v>
+        <v>237.5914282235791</v>
       </c>
       <c r="D153" t="n">
-        <v>132.6545027987726</v>
+        <v>119.5575741375759</v>
       </c>
       <c r="E153" t="n">
-        <v>459.9397582701702</v>
+        <v>439.4825089388673</v>
       </c>
       <c r="F153" t="n">
-        <v>319.8995383677879</v>
+        <v>314.8527490892148</v>
       </c>
     </row>
     <row r="154">
@@ -3249,16 +3249,16 @@
         <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>241.5489630189187</v>
+        <v>214.9876861462014</v>
       </c>
       <c r="D154" t="n">
-        <v>108.5355022899049</v>
+        <v>97.81983338528934</v>
       </c>
       <c r="E154" t="n">
-        <v>293.9726618844429</v>
+        <v>277.0711047217501</v>
       </c>
       <c r="F154" t="n">
-        <v>223.2514994633939</v>
+        <v>217.8732115296544</v>
       </c>
     </row>
     <row r="155">
@@ -3267,16 +3267,16 @@
         <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>19.61305053270321</v>
+        <v>17.45635460237572</v>
       </c>
       <c r="D155" t="n">
-        <v>36.17850076330163</v>
+        <v>32.60661112842978</v>
       </c>
       <c r="E155" t="n">
-        <v>133.5298812072749</v>
+        <v>78.51031448764761</v>
       </c>
       <c r="F155" t="n">
-        <v>203.0193196475848</v>
+        <v>121.7143630572468</v>
       </c>
     </row>
     <row r="156">
@@ -3323,16 +3323,16 @@
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>113.9482670489117</v>
+        <v>101.4182547796583</v>
       </c>
       <c r="D158" t="n">
-        <v>34.050353659578</v>
+        <v>30.68857517969862</v>
       </c>
       <c r="E158" t="n">
-        <v>55.7231665205646</v>
+        <v>50.03963159025705</v>
       </c>
       <c r="F158" t="n">
-        <v>13.72471000692566</v>
+        <v>12.56717611164874</v>
       </c>
     </row>
     <row r="159">
@@ -3377,16 +3377,16 @@
         <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>74.58625443106062</v>
+        <v>66.38457916786697</v>
       </c>
       <c r="D161" t="n">
-        <v>90.80094309220802</v>
+        <v>81.83620047919632</v>
       </c>
       <c r="E161" t="n">
-        <v>322.9613230354391</v>
+        <v>242.5826876551409</v>
       </c>
       <c r="F161" t="n">
-        <v>353.0756678237713</v>
+        <v>270.4136821549116</v>
       </c>
     </row>
     <row r="162">
@@ -3395,16 +3395,16 @@
         <v>5</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11073174301016</v>
+        <v>13.44912109248538</v>
       </c>
       <c r="D162" t="n">
-        <v>22.700235773052</v>
+        <v>20.45905011979908</v>
       </c>
       <c r="E162" t="n">
-        <v>57.17163259518311</v>
+        <v>45.72443567446251</v>
       </c>
       <c r="F162" t="n">
-        <v>70.7911476894236</v>
+        <v>57.73018133685983</v>
       </c>
     </row>
     <row r="163">
@@ -3431,16 +3431,16 @@
         <v>7</v>
       </c>
       <c r="C164" t="n">
-        <v>85.26086929679468</v>
+        <v>75.88538894905517</v>
       </c>
       <c r="D164" t="n">
-        <v>34.05035365957801</v>
+        <v>30.68857517969862</v>
       </c>
       <c r="E164" t="n">
-        <v>41.69440870455748</v>
+        <v>37.44174965684494</v>
       </c>
       <c r="F164" t="n">
-        <v>13.72471000692566</v>
+        <v>12.56717611164875</v>
       </c>
     </row>
     <row r="165">
@@ -3467,16 +3467,16 @@
         <v>9</v>
       </c>
       <c r="C166" t="n">
-        <v>124.9125923485988</v>
+        <v>111.1769177723426</v>
       </c>
       <c r="D166" t="n">
-        <v>75.03689047203301</v>
+        <v>67.62852678489139</v>
       </c>
       <c r="E166" t="n">
-        <v>96.88866959087089</v>
+        <v>92.19830683248787</v>
       </c>
       <c r="F166" t="n">
-        <v>66.99575888552569</v>
+        <v>66.85065323749998</v>
       </c>
     </row>
     <row r="167">
@@ -3485,16 +3485,16 @@
         <v>10</v>
       </c>
       <c r="C167" t="n">
-        <v>109.6994963876841</v>
+        <v>97.63668866566246</v>
       </c>
       <c r="D167" t="n">
-        <v>64.31733469031398</v>
+        <v>57.96730867276406</v>
       </c>
       <c r="E167" t="n">
-        <v>93.40083694244125</v>
+        <v>61.94055513673025</v>
       </c>
       <c r="F167" t="n">
-        <v>66.55500384687114</v>
+        <v>38.08443083735365</v>
       </c>
     </row>
     <row r="168">
@@ -3521,16 +3521,16 @@
         <v>12</v>
       </c>
       <c r="C169" t="n">
-        <v>32.37205318727661</v>
+        <v>28.81234812003423</v>
       </c>
       <c r="D169" t="n">
-        <v>30.46610590593821</v>
+        <v>27.4581988449935</v>
       </c>
       <c r="E169" t="n">
-        <v>77.20689761191812</v>
+        <v>73.55230885805091</v>
       </c>
       <c r="F169" t="n">
-        <v>59.89027272780281</v>
+        <v>58.17718555759061</v>
       </c>
     </row>
     <row r="170">
@@ -3595,16 +3595,16 @@
         <v>4</v>
       </c>
       <c r="C173" t="n">
-        <v>18.63575850035457</v>
+        <v>16.58652783889962</v>
       </c>
       <c r="D173" t="n">
-        <v>30.46610590593821</v>
+        <v>27.4581988449935</v>
       </c>
       <c r="E173" t="n">
-        <v>126.8762661173257</v>
+        <v>74.59825069736539</v>
       </c>
       <c r="F173" t="n">
-        <v>170.9636375979661</v>
+        <v>102.4963057324184</v>
       </c>
     </row>
     <row r="174">
@@ -3613,16 +3613,16 @@
         <v>5</v>
       </c>
       <c r="C174" t="n">
-        <v>709.3919464491262</v>
+        <v>631.3855842382673</v>
       </c>
       <c r="D174" t="n">
-        <v>50.77684317656369</v>
+        <v>45.76366474165584</v>
       </c>
       <c r="E174" t="n">
-        <v>371.8290054587259</v>
+        <v>382.5977802862</v>
       </c>
       <c r="F174" t="n">
-        <v>74.85198688809812</v>
+        <v>64.17969746853812</v>
       </c>
     </row>
     <row r="175">
@@ -3667,16 +3667,16 @@
         <v>8</v>
       </c>
       <c r="C177" t="n">
-        <v>156.7611997551502</v>
+        <v>139.5233794078536</v>
       </c>
       <c r="D177" t="n">
-        <v>30.46610590593821</v>
+        <v>27.4581988449935</v>
       </c>
       <c r="E177" t="n">
-        <v>76.65961636933163</v>
+        <v>68.84064923977559</v>
       </c>
       <c r="F177" t="n">
-        <v>12.28000369040717</v>
+        <v>11.24431546831729</v>
       </c>
     </row>
     <row r="178">
@@ -3703,16 +3703,16 @@
         <v>10</v>
       </c>
       <c r="C179" t="n">
-        <v>7.265567732588531</v>
+        <v>6.466629274021643</v>
       </c>
       <c r="D179" t="n">
-        <v>19.2952004070942</v>
+        <v>17.39019260182922</v>
       </c>
       <c r="E179" t="n">
-        <v>21.76811268978337</v>
+        <v>19.31427911207415</v>
       </c>
       <c r="F179" t="n">
-        <v>47.64902317857863</v>
+        <v>43.10899877300982</v>
       </c>
     </row>
     <row r="180">
@@ -3759,16 +3759,16 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>8.607267411595735</v>
+        <v>7.660792585210306</v>
       </c>
       <c r="D182" t="n">
-        <v>19.2952004070942</v>
+        <v>17.39019260182922</v>
       </c>
       <c r="E182" t="n">
-        <v>42.57235779688219</v>
+        <v>32.13027652749025</v>
       </c>
       <c r="F182" t="n">
-        <v>78.66203694729107</v>
+        <v>60.53522435791184</v>
       </c>
     </row>
     <row r="183">
@@ -3777,16 +3777,16 @@
         <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>17.35513855153852</v>
+        <v>15.44672779096042</v>
       </c>
       <c r="D183" t="n">
-        <v>28.9428006106413</v>
+        <v>26.08528890274383</v>
       </c>
       <c r="E183" t="n">
-        <v>118.1575291033185</v>
+        <v>69.47197649779314</v>
       </c>
       <c r="F183" t="n">
-        <v>162.4154557180678</v>
+        <v>97.37149044579745</v>
       </c>
     </row>
     <row r="184">
@@ -3795,16 +3795,16 @@
         <v>3</v>
       </c>
       <c r="C184" t="n">
-        <v>31.66840484546364</v>
+        <v>28.18607456051937</v>
       </c>
       <c r="D184" t="n">
-        <v>38.59040081418841</v>
+        <v>34.78038520365844</v>
       </c>
       <c r="E184" t="n">
-        <v>87.8913231724686</v>
+        <v>78.89144027126913</v>
       </c>
       <c r="F184" t="n">
-        <v>110.2209469908886</v>
+        <v>93.59563033566214</v>
       </c>
     </row>
     <row r="185">
@@ -3813,16 +3813,16 @@
         <v>4</v>
       </c>
       <c r="C185" t="n">
-        <v>85.47626540059177</v>
+        <v>76.07709960424278</v>
       </c>
       <c r="D185" t="n">
-        <v>77.1808016283768</v>
+        <v>69.56077040731688</v>
       </c>
       <c r="E185" t="n">
-        <v>84.62899171162601</v>
+        <v>86.11209597191692</v>
       </c>
       <c r="F185" t="n">
-        <v>87.87609965308</v>
+        <v>86.31139660512481</v>
       </c>
     </row>
     <row r="186">
@@ -3831,16 +3831,16 @@
         <v>5</v>
       </c>
       <c r="C186" t="n">
-        <v>18.14345294349221</v>
+        <v>16.14835732794419</v>
       </c>
       <c r="D186" t="n">
-        <v>28.9428006106413</v>
+        <v>26.08528890274383</v>
       </c>
       <c r="E186" t="n">
-        <v>92.15383372542442</v>
+        <v>69.21725859466891</v>
       </c>
       <c r="F186" t="n">
-        <v>121.1678785519396</v>
+        <v>92.79929994661008</v>
       </c>
     </row>
     <row r="187">
@@ -3849,16 +3849,16 @@
         <v>6</v>
       </c>
       <c r="C187" t="n">
-        <v>152.2227662024162</v>
+        <v>135.4840023969321</v>
       </c>
       <c r="D187" t="n">
-        <v>28.9428006106413</v>
+        <v>26.08528890274383</v>
       </c>
       <c r="E187" t="n">
-        <v>74.44022422629043</v>
+        <v>66.84762601215434</v>
       </c>
       <c r="F187" t="n">
-        <v>11.66600350588681</v>
+        <v>10.68209969490144</v>
       </c>
     </row>
     <row r="188">
@@ -3903,16 +3903,16 @@
         <v>9</v>
       </c>
       <c r="C190" t="n">
-        <v>9.725822264914658</v>
+        <v>8.656348586515948</v>
       </c>
       <c r="D190" t="n">
-        <v>19.2952004070942</v>
+        <v>17.39019260182922</v>
       </c>
       <c r="E190" t="n">
-        <v>48.10483577784735</v>
+        <v>36.30575697089851</v>
       </c>
       <c r="F190" t="n">
-        <v>78.66203694729107</v>
+        <v>60.53522435791184</v>
       </c>
     </row>
     <row r="191">
@@ -3939,16 +3939,16 @@
         <v>11</v>
       </c>
       <c r="C192" t="n">
-        <v>51.7187687179638</v>
+        <v>46.03165452684937</v>
       </c>
       <c r="D192" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914611</v>
       </c>
       <c r="E192" t="n">
-        <v>151.8850900680047</v>
+        <v>123.8544912196734</v>
       </c>
       <c r="F192" t="n">
-        <v>245.5905389748334</v>
+        <v>206.7980415368236</v>
       </c>
     </row>
     <row r="193">
@@ -3957,16 +3957,16 @@
         <v>12</v>
       </c>
       <c r="C193" t="n">
-        <v>6.527000615557397</v>
+        <v>5.809276687739755</v>
       </c>
       <c r="D193" t="n">
-        <v>19.2952004070942</v>
+        <v>17.39019260182922</v>
       </c>
       <c r="E193" t="n">
-        <v>19.55531765101572</v>
+        <v>17.35092373967063</v>
       </c>
       <c r="F193" t="n">
-        <v>47.64902317857864</v>
+        <v>43.10899877300982</v>
       </c>
     </row>
     <row r="194">
@@ -4013,16 +4013,16 @@
         <v>3</v>
       </c>
       <c r="C196" t="n">
-        <v>167.1835685259724</v>
+        <v>148.7996806521111</v>
       </c>
       <c r="D196" t="n">
-        <v>55.12914402026913</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E196" t="n">
-        <v>192.1566940542037</v>
+        <v>180.9104851490486</v>
       </c>
       <c r="F196" t="n">
-        <v>115.9099433136213</v>
+        <v>113.3621361371547</v>
       </c>
     </row>
     <row r="197">
@@ -4031,16 +4031,16 @@
         <v>4</v>
       </c>
       <c r="C197" t="n">
-        <v>38.0269045659806</v>
+        <v>33.84537909733141</v>
       </c>
       <c r="D197" t="n">
-        <v>27.56457201013457</v>
+        <v>24.84313228832746</v>
       </c>
       <c r="E197" t="n">
-        <v>17.4337836884132</v>
+        <v>18.60329280421544</v>
       </c>
       <c r="F197" t="n">
-        <v>10.41610667398398</v>
+        <v>11.33338900836225</v>
       </c>
     </row>
     <row r="198">
@@ -4049,16 +4049,16 @@
         <v>5</v>
       </c>
       <c r="C198" t="n">
-        <v>124.6501081277964</v>
+        <v>110.9432969172791</v>
       </c>
       <c r="D198" t="n">
-        <v>45.94095335022428</v>
+        <v>41.40522048054576</v>
       </c>
       <c r="E198" t="n">
-        <v>75.56649516334005</v>
+        <v>67.67167677995408</v>
       </c>
       <c r="F198" t="n">
-        <v>56.49050160425281</v>
+        <v>51.2296175884869</v>
       </c>
     </row>
     <row r="199">
@@ -4103,16 +4103,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="n">
-        <v>34.28230996931427</v>
+        <v>30.51254869379203</v>
       </c>
       <c r="D201" t="n">
-        <v>45.94095335022428</v>
+        <v>41.40522048054576</v>
       </c>
       <c r="E201" t="n">
-        <v>73.92604618830615</v>
+        <v>61.45862226409479</v>
       </c>
       <c r="F201" t="n">
-        <v>102.6539533457406</v>
+        <v>84.11044609724361</v>
       </c>
     </row>
     <row r="202">
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>16.52896848640465</v>
+        <v>14.71140527727</v>
       </c>
       <c r="D206" t="n">
-        <v>26.31163691876483</v>
+        <v>23.71389900249439</v>
       </c>
       <c r="E206" t="n">
-        <v>83.95357919426615</v>
+        <v>63.05800167089873</v>
       </c>
       <c r="F206" t="n">
-        <v>110.1526168653996</v>
+        <v>84.36299995146369</v>
       </c>
     </row>
     <row r="207">
@@ -4213,16 +4213,16 @@
         <v>2</v>
       </c>
       <c r="C207" t="n">
-        <v>9.956553842493392</v>
+        <v>8.861708391685674</v>
       </c>
       <c r="D207" t="n">
-        <v>17.54109127917655</v>
+        <v>15.80926600166293</v>
       </c>
       <c r="E207" t="n">
-        <v>49.24605595911969</v>
+        <v>37.16706045279583</v>
       </c>
       <c r="F207" t="n">
-        <v>71.51094267935551</v>
+        <v>55.03202214355623</v>
       </c>
     </row>
     <row r="208">
@@ -4231,16 +4231,16 @@
         <v>3</v>
       </c>
       <c r="C208" t="n">
-        <v>19.34466103261234</v>
+        <v>17.21747782605128</v>
       </c>
       <c r="D208" t="n">
-        <v>26.31163691876482</v>
+        <v>23.71389900249439</v>
       </c>
       <c r="E208" t="n">
-        <v>104.8566066372562</v>
+        <v>113.794432203905</v>
       </c>
       <c r="F208" t="n">
-        <v>117.5536259028605</v>
+        <v>130.0820737689991</v>
       </c>
     </row>
     <row r="209">
@@ -4249,16 +4249,16 @@
         <v>4</v>
       </c>
       <c r="C209" t="n">
-        <v>35.02287603025853</v>
+        <v>31.17168041553882</v>
       </c>
       <c r="D209" t="n">
-        <v>26.31163691876481</v>
+        <v>23.71389900249439</v>
       </c>
       <c r="E209" t="n">
-        <v>16.0565592131807</v>
+        <v>17.1336800897414</v>
       </c>
       <c r="F209" t="n">
-        <v>9.942647279711979</v>
+        <v>10.81823496252761</v>
       </c>
     </row>
     <row r="210">
@@ -4267,16 +4267,16 @@
         <v>5</v>
       </c>
       <c r="C210" t="n">
-        <v>40.53924421503314</v>
+        <v>36.08145612789544</v>
       </c>
       <c r="D210" t="n">
-        <v>26.31163691876483</v>
+        <v>23.71389900249439</v>
       </c>
       <c r="E210" t="n">
-        <v>18.58558887722128</v>
+        <v>19.83236444831598</v>
       </c>
       <c r="F210" t="n">
-        <v>9.942647279711979</v>
+        <v>10.81823496252761</v>
       </c>
     </row>
     <row r="211">
@@ -4285,16 +4285,16 @@
         <v>6</v>
       </c>
       <c r="C211" t="n">
-        <v>38.28760896607503</v>
+        <v>34.07741584484601</v>
       </c>
       <c r="D211" t="n">
-        <v>43.85272819794136</v>
+        <v>39.52316500415731</v>
       </c>
       <c r="E211" t="n">
-        <v>141.1611400315061</v>
+        <v>136.9512305729085</v>
       </c>
       <c r="F211" t="n">
-        <v>122.268057475445</v>
+        <v>121.2071076270101</v>
       </c>
     </row>
     <row r="212">
@@ -4303,16 +4303,16 @@
         <v>7</v>
       </c>
       <c r="C212" t="n">
-        <v>95.33740805809057</v>
+        <v>84.85388844322954</v>
       </c>
       <c r="D212" t="n">
-        <v>41.94608784150913</v>
+        <v>37.80476652571569</v>
       </c>
       <c r="E212" t="n">
-        <v>58.27791231548198</v>
+        <v>54.10679022295826</v>
       </c>
       <c r="F212" t="n">
-        <v>31.40993891779199</v>
+        <v>31.01023898739265</v>
       </c>
     </row>
     <row r="213">
@@ -4339,16 +4339,16 @@
         <v>9</v>
       </c>
       <c r="C214" t="n">
-        <v>34.18384105968055</v>
+        <v>30.42490765085435</v>
       </c>
       <c r="D214" t="n">
-        <v>33.55687027320731</v>
+        <v>30.24381322057256</v>
       </c>
       <c r="E214" t="n">
-        <v>58.57723750020303</v>
+        <v>61.07322909966793</v>
       </c>
       <c r="F214" t="n">
-        <v>46.18198822324477</v>
+        <v>48.65419377595986</v>
       </c>
     </row>
     <row r="215">
@@ -4375,16 +4375,16 @@
         <v>11</v>
       </c>
       <c r="C216" t="n">
-        <v>26.67984615288161</v>
+        <v>23.74606920045193</v>
       </c>
       <c r="D216" t="n">
-        <v>30.87232065135072</v>
+        <v>27.82430816292675</v>
       </c>
       <c r="E216" t="n">
-        <v>106.7790039614478</v>
+        <v>80.33878728128325</v>
       </c>
       <c r="F216" t="n">
-        <v>109.152477994894</v>
+        <v>83.83060343709322</v>
       </c>
     </row>
     <row r="217">
@@ -4393,16 +4393,16 @@
         <v>12</v>
       </c>
       <c r="C217" t="n">
-        <v>401.614694563176</v>
+        <v>357.4522234636465</v>
       </c>
       <c r="D217" t="n">
-        <v>38.5904008141884</v>
+        <v>34.78038520365844</v>
       </c>
       <c r="E217" t="n">
-        <v>89.61064174814869</v>
+        <v>93.34316436410158</v>
       </c>
       <c r="F217" t="n">
-        <v>41.67653987736421</v>
+        <v>38.38476855851185</v>
       </c>
     </row>
     <row r="218">
@@ -4413,16 +4413,16 @@
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>63.21605491291604</v>
+        <v>56.2646728148221</v>
       </c>
       <c r="D218" t="n">
-        <v>22.26369277741638</v>
+        <v>20.06560684826448</v>
       </c>
       <c r="E218" t="n">
-        <v>30.91401778996357</v>
+        <v>27.76091449529412</v>
       </c>
       <c r="F218" t="n">
-        <v>8.97384885068216</v>
+        <v>8.216999765308794</v>
       </c>
     </row>
     <row r="219">
@@ -4449,16 +4449,16 @@
         <v>3</v>
       </c>
       <c r="C220" t="n">
-        <v>103.0388746382427</v>
+        <v>91.70848412977577</v>
       </c>
       <c r="D220" t="n">
-        <v>141.0033875903038</v>
+        <v>127.0821767056751</v>
       </c>
       <c r="E220" t="n">
-        <v>314.4343808790122</v>
+        <v>188.8082069751731</v>
       </c>
       <c r="F220" t="n">
-        <v>357.3703980581752</v>
+        <v>266.8052045621987</v>
       </c>
     </row>
     <row r="221">
@@ -4467,16 +4467,16 @@
         <v>4</v>
       </c>
       <c r="C221" t="n">
-        <v>1270.409621605035</v>
+        <v>1130.712471679484</v>
       </c>
       <c r="D221" t="n">
-        <v>155.8458494419147</v>
+        <v>140.4592479378514</v>
       </c>
       <c r="E221" t="n">
-        <v>333.5226148419868</v>
+        <v>342.535333896485</v>
       </c>
       <c r="F221" t="n">
-        <v>181.8745956478744</v>
+        <v>165.5363756055084</v>
       </c>
     </row>
     <row r="222">
@@ -4503,16 +4503,16 @@
         <v>6</v>
       </c>
       <c r="C223" t="n">
-        <v>60.46753078626752</v>
+        <v>53.81838269243853</v>
       </c>
       <c r="D223" t="n">
-        <v>22.26369277741638</v>
+        <v>20.06560684826448</v>
       </c>
       <c r="E223" t="n">
-        <v>29.56993005996516</v>
+        <v>26.55391821289003</v>
       </c>
       <c r="F223" t="n">
-        <v>8.97384885068216</v>
+        <v>8.216999765308794</v>
       </c>
     </row>
     <row r="224">
@@ -4521,16 +4521,16 @@
         <v>7</v>
       </c>
       <c r="C224" t="n">
-        <v>366.1546376987461</v>
+        <v>325.8914356191571</v>
       </c>
       <c r="D224" t="n">
-        <v>59.3698474064437</v>
+        <v>53.50828492870528</v>
       </c>
       <c r="E224" t="n">
-        <v>108.6411888420134</v>
+        <v>108.9605372679755</v>
       </c>
       <c r="F224" t="n">
-        <v>30.99031416578907</v>
+        <v>30.8137497679076</v>
       </c>
     </row>
     <row r="225">
@@ -4539,16 +4539,16 @@
         <v>8</v>
       </c>
       <c r="C225" t="n">
-        <v>444.5758300754403</v>
+        <v>395.6892541780847</v>
       </c>
       <c r="D225" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E225" t="n">
-        <v>117.8638900691616</v>
+        <v>116.6648453096335</v>
       </c>
       <c r="F225" t="n">
-        <v>21.36819898453866</v>
+        <v>20.18166254994837</v>
       </c>
     </row>
     <row r="226">
@@ -4557,16 +4557,16 @@
         <v>9</v>
       </c>
       <c r="C226" t="n">
-        <v>56.27489739063535</v>
+        <v>50.08678086181649</v>
       </c>
       <c r="D226" t="n">
-        <v>42.87822312687601</v>
+        <v>38.64487244850938</v>
       </c>
       <c r="E226" t="n">
-        <v>123.5719400630113</v>
+        <v>133.2134718463924</v>
       </c>
       <c r="F226" t="n">
-        <v>77.60602157245073</v>
+        <v>85.3060652440046</v>
       </c>
     </row>
     <row r="227">
@@ -4575,16 +4575,16 @@
         <v>10</v>
       </c>
       <c r="C227" t="n">
-        <v>79.09119732807235</v>
+        <v>70.39414823222873</v>
       </c>
       <c r="D227" t="n">
-        <v>41.34685801520186</v>
+        <v>37.26469843249117</v>
       </c>
       <c r="E227" t="n">
-        <v>51.87844004419589</v>
+        <v>44.0604611115883</v>
       </c>
       <c r="F227" t="n">
-        <v>21.85356125220741</v>
+        <v>19.18319102732701</v>
       </c>
     </row>
     <row r="228">
@@ -4593,16 +4593,16 @@
         <v>11</v>
       </c>
       <c r="C228" t="n">
-        <v>42.67280029773735</v>
+        <v>37.98040150009233</v>
       </c>
       <c r="D228" t="n">
-        <v>20.67342900760093</v>
+        <v>18.63234921624559</v>
       </c>
       <c r="E228" t="n">
-        <v>35.16398317349693</v>
+        <v>26.23784895674375</v>
       </c>
       <c r="F228" t="n">
-        <v>14.04148124671942</v>
+        <v>10.68314927105532</v>
       </c>
     </row>
     <row r="229">
@@ -4611,16 +4611,16 @@
         <v>12</v>
       </c>
       <c r="C229" t="n">
-        <v>20.10119620797295</v>
+        <v>17.89082266184033</v>
       </c>
       <c r="D229" t="n">
-        <v>20.67342900760093</v>
+        <v>18.63234921624559</v>
       </c>
       <c r="E229" t="n">
-        <v>9.312321569117458</v>
+        <v>8.026595040511502</v>
       </c>
       <c r="F229" t="n">
-        <v>7.894089859091868</v>
+        <v>6.937957928648841</v>
       </c>
     </row>
     <row r="230">
@@ -4631,16 +4631,16 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>307.5663613927572</v>
+        <v>273.7456602827822</v>
       </c>
       <c r="D230" t="n">
-        <v>103.3671450380047</v>
+        <v>93.16174608122796</v>
       </c>
       <c r="E230" t="n">
-        <v>107.115366813489</v>
+        <v>100.3403990261645</v>
       </c>
       <c r="F230" t="n">
-        <v>32.67544000430413</v>
+        <v>30.19965882771389</v>
       </c>
     </row>
     <row r="231">
@@ -4649,16 +4649,16 @@
         <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>484.5138416344278</v>
+        <v>431.2355905689988</v>
       </c>
       <c r="D231" t="n">
-        <v>144.7140030532065</v>
+        <v>130.4264445137192</v>
       </c>
       <c r="E231" t="n">
-        <v>157.746285693803</v>
+        <v>151.3982253148542</v>
       </c>
       <c r="F231" t="n">
-        <v>41.99241938309648</v>
+        <v>39.95791360604318</v>
       </c>
     </row>
     <row r="232">
@@ -4667,16 +4667,16 @@
         <v>3</v>
       </c>
       <c r="C232" t="n">
-        <v>449.840548602734</v>
+        <v>400.3750522053164</v>
       </c>
       <c r="D232" t="n">
-        <v>96.476002035471</v>
+        <v>86.95096300914609</v>
       </c>
       <c r="E232" t="n">
-        <v>118.8836526209191</v>
+        <v>120.1312039344924</v>
       </c>
       <c r="F232" t="n">
-        <v>54.86103534492954</v>
+        <v>51.66044077335876</v>
       </c>
     </row>
     <row r="233">
@@ -4685,16 +4685,16 @@
         <v>4</v>
       </c>
       <c r="C233" t="n">
-        <v>422.8160191061945</v>
+        <v>376.3222018306461</v>
       </c>
       <c r="D233" t="n">
-        <v>82.69371603040372</v>
+        <v>74.52939686498237</v>
       </c>
       <c r="E233" t="n">
-        <v>108.2928202166825</v>
+        <v>109.7025055412503</v>
       </c>
       <c r="F233" t="n">
-        <v>20.82601878880196</v>
+        <v>20.86829879263746</v>
       </c>
     </row>
     <row r="234">
@@ -4703,16 +4703,16 @@
         <v>5</v>
       </c>
       <c r="C234" t="n">
-        <v>103.8692447504058</v>
+        <v>92.44754484371029</v>
       </c>
       <c r="D234" t="n">
-        <v>55.12914402026913</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E234" t="n">
-        <v>93.06754059871521</v>
+        <v>73.76766912930792</v>
       </c>
       <c r="F234" t="n">
-        <v>48.55000549855136</v>
+        <v>43.48961832907759</v>
       </c>
     </row>
     <row r="235">
@@ -4721,16 +4721,16 @@
         <v>6</v>
       </c>
       <c r="C235" t="n">
-        <v>14.59079891250683</v>
+        <v>12.98636126613662</v>
       </c>
       <c r="D235" t="n">
-        <v>20.67342900760092</v>
+        <v>18.63234921624559</v>
       </c>
       <c r="E235" t="n">
-        <v>34.79885292406352</v>
+        <v>33.15164910578537</v>
       </c>
       <c r="F235" t="n">
-        <v>40.63982792243763</v>
+        <v>39.47737591407932</v>
       </c>
     </row>
     <row r="236">
@@ -4739,16 +4739,16 @@
         <v>7</v>
       </c>
       <c r="C236" t="n">
-        <v>2.639639169315422</v>
+        <v>2.34937840419359</v>
       </c>
       <c r="D236" t="n">
-        <v>13.30703476351324</v>
+        <v>11.9932362771236</v>
       </c>
       <c r="E236" t="n">
-        <v>7.908530346540832</v>
+        <v>7.017032879983597</v>
       </c>
       <c r="F236" t="n">
-        <v>32.86139529557147</v>
+        <v>29.73034398138608</v>
       </c>
     </row>
     <row r="237">
@@ -4775,16 +4775,16 @@
         <v>9</v>
       </c>
       <c r="C238" t="n">
-        <v>16.37610245018842</v>
+        <v>14.5753487403024</v>
       </c>
       <c r="D238" t="n">
-        <v>19.96055214526986</v>
+        <v>17.9898544156854</v>
       </c>
       <c r="E238" t="n">
-        <v>7.586589896798249</v>
+        <v>6.539130375606923</v>
       </c>
       <c r="F238" t="n">
-        <v>7.62187986395077</v>
+        <v>6.698718000074744</v>
       </c>
     </row>
     <row r="239">
@@ -4793,16 +4793,16 @@
         <v>10</v>
       </c>
       <c r="C239" t="n">
-        <v>14.43971650422953</v>
+        <v>12.85189222529712</v>
       </c>
       <c r="D239" t="n">
-        <v>19.96055214526986</v>
+        <v>17.9898544156854</v>
       </c>
       <c r="E239" t="n">
-        <v>6.689516487627876</v>
+        <v>5.765913415305576</v>
       </c>
       <c r="F239" t="n">
-        <v>7.621879863950769</v>
+        <v>6.698718000074744</v>
       </c>
     </row>
     <row r="240">
@@ -4811,16 +4811,16 @@
         <v>11</v>
       </c>
       <c r="C240" t="n">
-        <v>66.7972599941896</v>
+        <v>59.45208038807556</v>
       </c>
       <c r="D240" t="n">
-        <v>19.96055214526986</v>
+        <v>17.9898544156854</v>
       </c>
       <c r="E240" t="n">
-        <v>18.26155614225993</v>
+        <v>18.75765712933077</v>
       </c>
       <c r="F240" t="n">
-        <v>4.497852113899756</v>
+        <v>4.710881617124482</v>
       </c>
     </row>
     <row r="241">
@@ -4829,16 +4829,16 @@
         <v>12</v>
       </c>
       <c r="C241" t="n">
-        <v>13.48108585618698</v>
+        <v>11.9986747975934</v>
       </c>
       <c r="D241" t="n">
-        <v>19.96055214526986</v>
+        <v>17.9898544156854</v>
       </c>
       <c r="E241" t="n">
-        <v>49.00588394856342</v>
+        <v>25.59925161147156</v>
       </c>
       <c r="F241" t="n">
-        <v>59.80663809106992</v>
+        <v>31.85551570252879</v>
       </c>
     </row>
     <row r="242">
@@ -4849,16 +4849,16 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>60.83867901366521</v>
+        <v>54.14871861120314</v>
       </c>
       <c r="D242" t="n">
-        <v>32.158667345157</v>
+        <v>28.98365433638203</v>
       </c>
       <c r="E242" t="n">
-        <v>23.75404420025485</v>
+        <v>23.30307918661827</v>
       </c>
       <c r="F242" t="n">
-        <v>36.11393916248885</v>
+        <v>33.29318474522687</v>
       </c>
     </row>
     <row r="243">
@@ -4867,16 +4867,16 @@
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>17.14579697513281</v>
+        <v>15.26040589347359</v>
       </c>
       <c r="D243" t="n">
-        <v>19.2952004070942</v>
+        <v>17.39019260182922</v>
       </c>
       <c r="E243" t="n">
-        <v>32.14520092992608</v>
+        <v>30.79591332309011</v>
       </c>
       <c r="F243" t="n">
-        <v>29.81681484563428</v>
+        <v>29.12690911299154</v>
       </c>
     </row>
     <row r="244">
@@ -4885,16 +4885,16 @@
         <v>3</v>
       </c>
       <c r="C244" t="n">
-        <v>11.97639844145996</v>
+        <v>10.65944625517927</v>
       </c>
       <c r="D244" t="n">
-        <v>12.44851639167368</v>
+        <v>11.21947909795433</v>
       </c>
       <c r="E244" t="n">
-        <v>18.20478294616725</v>
+        <v>18.09676380144667</v>
       </c>
       <c r="F244" t="n">
-        <v>15.5966149945241</v>
+        <v>15.80891166338609</v>
       </c>
     </row>
     <row r="245">
@@ -4903,16 +4903,16 @@
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>64.62355733390471</v>
+        <v>57.51740304786323</v>
       </c>
       <c r="D245" t="n">
-        <v>28.375294716315</v>
+        <v>25.57381264974885</v>
       </c>
       <c r="E245" t="n">
-        <v>103.252465898613</v>
+        <v>96.81627577662043</v>
       </c>
       <c r="F245" t="n">
-        <v>49.76068651085764</v>
+        <v>46.21196473414191</v>
       </c>
     </row>
     <row r="246">
@@ -4921,16 +4921,16 @@
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>34.64027318286915</v>
+        <v>30.83114945301613</v>
       </c>
       <c r="D246" t="n">
-        <v>17.025176829789</v>
+        <v>15.34428758984931</v>
       </c>
       <c r="E246" t="n">
-        <v>10.77673086074329</v>
+        <v>10.57282501856414</v>
       </c>
       <c r="F246" t="n">
-        <v>4.365669421630322</v>
+        <v>4.36728026285188</v>
       </c>
     </row>
     <row r="247">
@@ -4939,16 +4939,16 @@
         <v>6</v>
       </c>
       <c r="C247" t="n">
-        <v>48.25940530868098</v>
+        <v>42.95269063644218</v>
       </c>
       <c r="D247" t="n">
-        <v>56.75058943263</v>
+        <v>51.1476252994977</v>
       </c>
       <c r="E247" t="n">
-        <v>101.605960011121</v>
+        <v>67.6206440730228</v>
       </c>
       <c r="F247" t="n">
-        <v>155.9618471129392</v>
+        <v>112.3610967286266</v>
       </c>
     </row>
     <row r="248">
@@ -4957,16 +4957,16 @@
         <v>7</v>
       </c>
       <c r="C248" t="n">
-        <v>67.62301301372894</v>
+        <v>60.18703171545963</v>
       </c>
       <c r="D248" t="n">
-        <v>33.07748641216148</v>
+        <v>29.81175874599295</v>
       </c>
       <c r="E248" t="n">
-        <v>27.13633530271402</v>
+        <v>25.23035795301116</v>
       </c>
       <c r="F248" t="n">
-        <v>10.90722372723335</v>
+        <v>10.3465577952855</v>
       </c>
     </row>
     <row r="249">
@@ -4975,16 +4975,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="n">
-        <v>49.18921259925094</v>
+        <v>43.7802541890369</v>
       </c>
       <c r="D249" t="n">
-        <v>44.10331521621531</v>
+        <v>39.74901166132393</v>
       </c>
       <c r="E249" t="n">
-        <v>90.94570945518382</v>
+        <v>69.92327848706174</v>
       </c>
       <c r="F249" t="n">
-        <v>96.03538140250899</v>
+        <v>67.03648951056731</v>
       </c>
     </row>
     <row r="250">
@@ -4993,16 +4993,16 @@
         <v>9</v>
       </c>
       <c r="C250" t="n">
-        <v>181.6488619211496</v>
+        <v>161.6743372748825</v>
       </c>
       <c r="D250" t="n">
-        <v>93.71954483445755</v>
+        <v>84.46664978031335</v>
       </c>
       <c r="E250" t="n">
-        <v>203.2104764170525</v>
+        <v>190.7445430158799</v>
       </c>
       <c r="F250" t="n">
-        <v>101.6313910938361</v>
+        <v>94.35075240745211</v>
       </c>
     </row>
     <row r="251">
@@ -5011,16 +5011,16 @@
         <v>10</v>
       </c>
       <c r="C251" t="n">
-        <v>134.8796711197379</v>
+        <v>120.0479937474288</v>
       </c>
       <c r="D251" t="n">
-        <v>15.64475708683313</v>
+        <v>14.10015616364531</v>
       </c>
       <c r="E251" t="n">
-        <v>68.10733161572378</v>
+        <v>71.72125302266022</v>
       </c>
       <c r="F251" t="n">
-        <v>6.5113295796579</v>
+        <v>6.99165338307247</v>
       </c>
     </row>
     <row r="252">
@@ -5029,16 +5029,16 @@
         <v>11</v>
       </c>
       <c r="C252" t="n">
-        <v>503.0456403227021</v>
+        <v>447.7295902547158</v>
       </c>
       <c r="D252" t="n">
-        <v>88.65362349205444</v>
+        <v>79.90088492732343</v>
       </c>
       <c r="E252" t="n">
-        <v>180.1255190865205</v>
+        <v>163.0610180399307</v>
       </c>
       <c r="F252" t="n">
-        <v>112.3608135720314</v>
+        <v>80.64860690970711</v>
       </c>
     </row>
     <row r="253">
@@ -5047,16 +5047,16 @@
         <v>12</v>
       </c>
       <c r="C253" t="n">
-        <v>77.31478719285461</v>
+        <v>68.81307622163511</v>
       </c>
       <c r="D253" t="n">
-        <v>31.28951417366626</v>
+        <v>28.20031232729062</v>
       </c>
       <c r="E253" t="n">
-        <v>24.05294694803629</v>
+        <v>23.59784266198648</v>
       </c>
       <c r="F253" t="n">
-        <v>8.023392450563835</v>
+        <v>8.026352915511563</v>
       </c>
     </row>
     <row r="254">
@@ -5067,16 +5067,16 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>190.1938035075402</v>
+        <v>169.2796575252893</v>
       </c>
       <c r="D254" t="n">
-        <v>78.22378543416569</v>
+        <v>70.50078081822656</v>
       </c>
       <c r="E254" t="n">
-        <v>88.69902176134994</v>
+        <v>85.9829063434838</v>
       </c>
       <c r="F254" t="n">
-        <v>29.10882732629238</v>
+        <v>27.8033922678073</v>
       </c>
     </row>
     <row r="255">
@@ -5085,16 +5085,16 @@
         <v>2</v>
       </c>
       <c r="C255" t="n">
-        <v>132.7921383001415</v>
+        <v>118.1900108149824</v>
       </c>
       <c r="D255" t="n">
-        <v>46.9342712604994</v>
+        <v>42.30046849093593</v>
       </c>
       <c r="E255" t="n">
-        <v>60.353623483903</v>
+        <v>61.33451913025033</v>
       </c>
       <c r="F255" t="n">
-        <v>16.49693164425258</v>
+        <v>16.25517638142737</v>
       </c>
     </row>
     <row r="256">
@@ -5103,16 +5103,16 @@
         <v>3</v>
       </c>
       <c r="C256" t="n">
-        <v>88.30156010196556</v>
+        <v>78.59171843322902</v>
       </c>
       <c r="D256" t="n">
-        <v>71.08758044718915</v>
+        <v>64.06913063831819</v>
       </c>
       <c r="E256" t="n">
-        <v>112.0173385350561</v>
+        <v>107.5665630967543</v>
       </c>
       <c r="F256" t="n">
-        <v>106.0926348141784</v>
+        <v>102.0553092398031</v>
       </c>
     </row>
     <row r="257">
@@ -5121,16 +5121,16 @@
         <v>4</v>
       </c>
       <c r="C257" t="n">
-        <v>291.162880474457</v>
+        <v>259.1459436733902</v>
       </c>
       <c r="D257" t="n">
-        <v>335.1271649653203</v>
+        <v>302.0401872949286</v>
       </c>
       <c r="E257" t="n">
-        <v>439.7799002947376</v>
+        <v>392.4420140548302</v>
       </c>
       <c r="F257" t="n">
-        <v>641.1295614025531</v>
+        <v>583.4789351343945</v>
       </c>
     </row>
     <row r="258">
@@ -5139,16 +5139,16 @@
         <v>5</v>
       </c>
       <c r="C258" t="n">
-        <v>63.38439972987698</v>
+        <v>56.41450605037321</v>
       </c>
       <c r="D258" t="n">
-        <v>60.93221181187642</v>
+        <v>54.91639768998701</v>
       </c>
       <c r="E258" t="n">
-        <v>53.65339993854961</v>
+        <v>47.14403881345036</v>
       </c>
       <c r="F258" t="n">
-        <v>90.22902996207281</v>
+        <v>78.83971704742257</v>
       </c>
     </row>
     <row r="259">
@@ -5157,16 +5157,16 @@
         <v>6</v>
       </c>
       <c r="C259" t="n">
-        <v>346.6109919441639</v>
+        <v>308.4968538866345</v>
       </c>
       <c r="D259" t="n">
-        <v>133.5821566644983</v>
+        <v>120.3936410895869</v>
       </c>
       <c r="E259" t="n">
-        <v>163.4345981646769</v>
+        <v>166.6294940311982</v>
       </c>
       <c r="F259" t="n">
-        <v>53.09730405192333</v>
+        <v>54.92123550184588</v>
       </c>
     </row>
     <row r="260">
@@ -5175,16 +5175,16 @@
         <v>7</v>
       </c>
       <c r="C260" t="n">
-        <v>85.65074683507393</v>
+        <v>76.23239466080591</v>
       </c>
       <c r="D260" t="n">
-        <v>29.68492370322185</v>
+        <v>26.75414246435264</v>
       </c>
       <c r="E260" t="n">
-        <v>24.73154875837064</v>
+        <v>24.90325676357989</v>
       </c>
       <c r="F260" t="n">
-        <v>7.150524913808305</v>
+        <v>7.310335790604459</v>
       </c>
     </row>
     <row r="261">
@@ -5193,16 +5193,16 @@
         <v>8</v>
       </c>
       <c r="C261" t="n">
-        <v>210.1407157509108</v>
+        <v>187.0331616404269</v>
       </c>
       <c r="D261" t="n">
-        <v>89.05477110966555</v>
+        <v>80.26242739305793</v>
       </c>
       <c r="E261" t="n">
-        <v>114.4742432663164</v>
+        <v>117.3236108363546</v>
       </c>
       <c r="F261" t="n">
-        <v>41.67939941073634</v>
+        <v>43.49911789131021</v>
       </c>
     </row>
     <row r="262">
@@ -5211,16 +5211,16 @@
         <v>9</v>
       </c>
       <c r="C262" t="n">
-        <v>138.6975192356685</v>
+        <v>123.4460225455789</v>
       </c>
       <c r="D262" t="n">
-        <v>89.05477110966554</v>
+        <v>80.26242739305793</v>
       </c>
       <c r="E262" t="n">
-        <v>137.0068169920442</v>
+        <v>143.1576938833618</v>
       </c>
       <c r="F262" t="n">
-        <v>106.493186967014</v>
+        <v>114.9216144897851</v>
       </c>
     </row>
     <row r="263">
@@ -5229,16 +5229,16 @@
         <v>10</v>
       </c>
       <c r="C263" t="n">
-        <v>136.6466086298908</v>
+        <v>121.6206347644924</v>
       </c>
       <c r="D263" t="n">
-        <v>57.88560122128261</v>
+        <v>52.17057780548765</v>
       </c>
       <c r="E263" t="n">
-        <v>110.1134247325216</v>
+        <v>92.33969120314444</v>
       </c>
       <c r="F263" t="n">
-        <v>75.60107680370098</v>
+        <v>56.42486450025591</v>
       </c>
     </row>
     <row r="264">
@@ -5247,16 +5247,16 @@
         <v>11</v>
       </c>
       <c r="C264" t="n">
-        <v>243.1208546711835</v>
+        <v>216.3867289943649</v>
       </c>
       <c r="D264" t="n">
-        <v>115.7712024425652</v>
+        <v>104.3411556109753</v>
       </c>
       <c r="E264" t="n">
-        <v>93.72199803568815</v>
+        <v>95.18607836084757</v>
       </c>
       <c r="F264" t="n">
-        <v>35.67604143985184</v>
+        <v>36.0552713748499</v>
       </c>
     </row>
     <row r="265">
@@ -5265,16 +5265,16 @@
         <v>12</v>
       </c>
       <c r="C265" t="n">
-        <v>583.3565861257412</v>
+        <v>519.209360627632</v>
       </c>
       <c r="D265" t="n">
-        <v>274.9566058010923</v>
+        <v>247.8102445760663</v>
       </c>
       <c r="E265" t="n">
-        <v>234.963315241809</v>
+        <v>236.3603816911159</v>
       </c>
       <c r="F265" t="n">
-        <v>167.9827406049517</v>
+        <v>163.667809764456</v>
       </c>
     </row>
     <row r="266">
@@ -5285,16 +5285,16 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>201.12486369499</v>
+        <v>179.0087133136209</v>
       </c>
       <c r="D266" t="n">
-        <v>80.00448949282962</v>
+        <v>72.10567664173091</v>
       </c>
       <c r="E266" t="n">
-        <v>96.21628857890033</v>
+        <v>94.53615660861418</v>
       </c>
       <c r="F266" t="n">
-        <v>61.15111915803455</v>
+        <v>58.00755500816078</v>
       </c>
     </row>
     <row r="267">
@@ -5303,16 +5303,16 @@
         <v>2</v>
       </c>
       <c r="C267" t="n">
-        <v>90.87625056956763</v>
+        <v>80.8832900436155</v>
       </c>
       <c r="D267" t="n">
-        <v>56.47375728905619</v>
+        <v>50.89812468828064</v>
       </c>
       <c r="E267" t="n">
-        <v>73.91410632857537</v>
+        <v>78.29241290783688</v>
       </c>
       <c r="F267" t="n">
-        <v>50.77646356240704</v>
+        <v>54.99498896655792</v>
       </c>
     </row>
     <row r="268">
@@ -5321,16 +5321,16 @@
         <v>3</v>
       </c>
       <c r="C268" t="n">
-        <v>156.652668055179</v>
+        <v>139.4267821020374</v>
       </c>
       <c r="D268" t="n">
-        <v>70.59219661132025</v>
+        <v>63.6226558603508</v>
       </c>
       <c r="E268" t="n">
-        <v>81.34581445967828</v>
+        <v>84.67352729161914</v>
       </c>
       <c r="F268" t="n">
-        <v>45.90591764332944</v>
+        <v>47.14605569431038</v>
       </c>
     </row>
     <row r="269">
@@ -5339,16 +5339,16 @@
         <v>4</v>
       </c>
       <c r="C269" t="n">
-        <v>241.3585455044703</v>
+        <v>214.8182073775023</v>
       </c>
       <c r="D269" t="n">
-        <v>103.535221696603</v>
+        <v>93.31322859518117</v>
       </c>
       <c r="E269" t="n">
-        <v>115.3586228013193</v>
+        <v>121.0221079895776</v>
       </c>
       <c r="F269" t="n">
-        <v>82.44291431441603</v>
+        <v>80.84865716336014</v>
       </c>
     </row>
     <row r="270">
@@ -5357,16 +5357,16 @@
         <v>5</v>
       </c>
       <c r="C270" t="n">
-        <v>118.9322708817492</v>
+        <v>105.8542061427847</v>
       </c>
       <c r="D270" t="n">
-        <v>57.88560122128261</v>
+        <v>52.17057780548765</v>
       </c>
       <c r="E270" t="n">
-        <v>37.00031657323863</v>
+        <v>36.30023592640314</v>
       </c>
       <c r="F270" t="n">
-        <v>14.84327603354309</v>
+        <v>14.84875289369639</v>
       </c>
     </row>
     <row r="271">
@@ -5375,16 +5375,16 @@
         <v>6</v>
       </c>
       <c r="C271" t="n">
-        <v>97.29209053091667</v>
+        <v>86.59362955712743</v>
       </c>
       <c r="D271" t="n">
-        <v>65.88605017056555</v>
+        <v>59.38114546966074</v>
       </c>
       <c r="E271" t="n">
-        <v>99.52015636097396</v>
+        <v>104.4389471946412</v>
       </c>
       <c r="F271" t="n">
-        <v>72.06904729226083</v>
+        <v>76.85798042907963</v>
       </c>
     </row>
     <row r="272">
@@ -5393,16 +5393,16 @@
         <v>7</v>
       </c>
       <c r="C272" t="n">
-        <v>45.33862158410936</v>
+        <v>40.35308297582079</v>
       </c>
       <c r="D272" t="n">
-        <v>28.23687864452809</v>
+        <v>25.44906234414032</v>
       </c>
       <c r="E272" t="n">
-        <v>26.46002656188147</v>
+        <v>24.94204411028295</v>
       </c>
       <c r="F272" t="n">
-        <v>16.01747326449565</v>
+        <v>15.96819728458371</v>
       </c>
     </row>
     <row r="273">
@@ -5411,16 +5411,16 @@
         <v>8</v>
       </c>
       <c r="C273" t="n">
-        <v>19.7604718359863</v>
+        <v>17.58756512170636</v>
       </c>
       <c r="D273" t="n">
-        <v>14.11843932226405</v>
+        <v>12.72453117207016</v>
       </c>
       <c r="E273" t="n">
-        <v>6.147563719648582</v>
+        <v>6.031246055803867</v>
       </c>
       <c r="F273" t="n">
-        <v>3.620311227693438</v>
+        <v>3.621647047243023</v>
       </c>
     </row>
     <row r="274">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="C274" t="n">
-        <v>54.2848580132612</v>
+        <v>48.31557076952566</v>
       </c>
       <c r="D274" t="n">
-        <v>42.35531796679214</v>
+        <v>38.17359351621047</v>
       </c>
       <c r="E274" t="n">
-        <v>21.84735452318086</v>
+        <v>21.7435449369859</v>
       </c>
       <c r="F274" t="n">
-        <v>17.56736230237676</v>
+        <v>18.00071104009345</v>
       </c>
     </row>
     <row r="275">
@@ -5447,16 +5447,16 @@
         <v>10</v>
       </c>
       <c r="C275" t="n">
-        <v>109.5461211518851</v>
+        <v>97.50017892186379</v>
       </c>
       <c r="D275" t="n">
-        <v>80.00448949282962</v>
+        <v>72.10567664173091</v>
       </c>
       <c r="E275" t="n">
-        <v>69.44623884666278</v>
+        <v>69.47754013077399</v>
       </c>
       <c r="F275" t="n">
-        <v>54.47650709112962</v>
+        <v>55.97777941935179</v>
       </c>
     </row>
     <row r="276">
@@ -5465,16 +5465,16 @@
         <v>11</v>
       </c>
       <c r="C276" t="n">
-        <v>44.14641325022744</v>
+        <v>39.29197259926572</v>
       </c>
       <c r="D276" t="n">
-        <v>37.64917152603748</v>
+        <v>33.93208312552043</v>
       </c>
       <c r="E276" t="n">
-        <v>35.18545547661085</v>
+        <v>30.28205148835567</v>
       </c>
       <c r="F276" t="n">
-        <v>36.59304954612348</v>
+        <v>31.1801985512328</v>
       </c>
     </row>
     <row r="277">
@@ -5483,16 +5483,16 @@
         <v>12</v>
       </c>
       <c r="C277" t="n">
-        <v>13.7089283748975</v>
+        <v>12.20146323142104</v>
       </c>
       <c r="D277" t="n">
-        <v>28.23687864452809</v>
+        <v>25.44906234414032</v>
       </c>
       <c r="E277" t="n">
-        <v>12.16540481573287</v>
+        <v>12.42839713451815</v>
       </c>
       <c r="F277" t="n">
-        <v>20.65347969397978</v>
+        <v>21.51483389121481</v>
       </c>
     </row>
     <row r="278">
@@ -5503,16 +5503,16 @@
         <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>479.3984936759606</v>
+        <v>426.6827379809403</v>
       </c>
       <c r="D278" t="n">
-        <v>56.47375728905619</v>
+        <v>50.89812468828063</v>
       </c>
       <c r="E278" t="n">
-        <v>101.10590757789</v>
+        <v>107.4058487197018</v>
       </c>
       <c r="F278" t="n">
-        <v>26.44288929636914</v>
+        <v>27.51304773120418</v>
       </c>
     </row>
     <row r="279">
@@ -5521,16 +5521,16 @@
         <v>2</v>
       </c>
       <c r="C279" t="n">
-        <v>41.48200707054265</v>
+        <v>36.920550621854</v>
       </c>
       <c r="D279" t="n">
-        <v>43.41420091596195</v>
+        <v>39.12793335411573</v>
       </c>
       <c r="E279" t="n">
-        <v>18.2959772231293</v>
+        <v>17.41613948034833</v>
       </c>
       <c r="F279" t="n">
-        <v>19.82159025291472</v>
+        <v>19.59511114272588</v>
       </c>
     </row>
     <row r="280">
@@ -5539,16 +5539,16 @@
         <v>3</v>
       </c>
       <c r="C280" t="n">
-        <v>81.50123896894894</v>
+        <v>72.53917617775325</v>
       </c>
       <c r="D280" t="n">
-        <v>43.41420091596195</v>
+        <v>39.12793335411575</v>
       </c>
       <c r="E280" t="n">
-        <v>97.80714781447413</v>
+        <v>86.00226156632553</v>
       </c>
       <c r="F280" t="n">
-        <v>32.66720711668358</v>
+        <v>29.66238787282728</v>
       </c>
     </row>
     <row r="281">
@@ -5557,16 +5557,16 @@
         <v>4</v>
       </c>
       <c r="C281" t="n">
-        <v>60.62047807002102</v>
+        <v>53.95451154277823</v>
       </c>
       <c r="D281" t="n">
-        <v>14.47140030532065</v>
+        <v>13.04264445137191</v>
       </c>
       <c r="E281" t="n">
-        <v>27.55871803308997</v>
+        <v>29.99961248724256</v>
       </c>
       <c r="F281" t="n">
-        <v>5.422551662222501</v>
+        <v>6.018891855130818</v>
       </c>
     </row>
     <row r="282">
@@ -5575,16 +5575,16 @@
         <v>5</v>
       </c>
       <c r="C282" t="n">
-        <v>130.7177564212831</v>
+        <v>116.3437327157283</v>
       </c>
       <c r="D282" t="n">
-        <v>135.0664028496594</v>
+        <v>121.7313482128045</v>
       </c>
       <c r="E282" t="n">
-        <v>160.1582857131779</v>
+        <v>162.0255659111687</v>
       </c>
       <c r="F282" t="n">
-        <v>197.0256612668608</v>
+        <v>195.5328429972305</v>
       </c>
     </row>
     <row r="283">
@@ -5593,16 +5593,16 @@
         <v>6</v>
       </c>
       <c r="C283" t="n">
-        <v>58.93657590140933</v>
+        <v>52.45577511103439</v>
       </c>
       <c r="D283" t="n">
-        <v>28.9428006106413</v>
+        <v>26.08528890274383</v>
       </c>
       <c r="E283" t="n">
-        <v>42.16703312271248</v>
+        <v>43.25237140976182</v>
       </c>
       <c r="F283" t="n">
-        <v>27.78516279644821</v>
+        <v>27.86407368987448</v>
       </c>
     </row>
     <row r="284">
@@ -5611,16 +5611,16 @@
         <v>7</v>
       </c>
       <c r="C284" t="n">
-        <v>178.2903054036809</v>
+        <v>158.6850953197213</v>
       </c>
       <c r="D284" t="n">
-        <v>159.1854033585271</v>
+        <v>143.4690889650911</v>
       </c>
       <c r="E284" t="n">
-        <v>207.476122387189</v>
+        <v>205.9724011483707</v>
       </c>
       <c r="F284" t="n">
-        <v>203.8716726359135</v>
+        <v>204.5754750708196</v>
       </c>
     </row>
     <row r="285">
@@ -5629,16 +5629,16 @@
         <v>8</v>
       </c>
       <c r="C285" t="n">
-        <v>141.4420167961453</v>
+        <v>125.8887288722236</v>
       </c>
       <c r="D285" t="n">
-        <v>53.06180111950905</v>
+        <v>47.82302965503035</v>
       </c>
       <c r="E285" t="n">
-        <v>138.5928242643351</v>
+        <v>131.3991532779874</v>
       </c>
       <c r="F285" t="n">
-        <v>49.26834532519209</v>
+        <v>46.40774741985997</v>
       </c>
     </row>
     <row r="286">
@@ -5647,16 +5647,16 @@
         <v>9</v>
       </c>
       <c r="C286" t="n">
-        <v>97.9271721876276</v>
+        <v>87.1588761811814</v>
       </c>
       <c r="D286" t="n">
-        <v>28.9428006106413</v>
+        <v>26.08528890274383</v>
       </c>
       <c r="E286" t="n">
-        <v>34.30651456204362</v>
+        <v>34.57200748627707</v>
       </c>
       <c r="F286" t="n">
-        <v>9.505283704046404</v>
+        <v>9.067138055506454</v>
       </c>
     </row>
     <row r="287">
@@ -5665,16 +5665,16 @@
         <v>10</v>
       </c>
       <c r="C287" t="n">
-        <v>96.80427782563892</v>
+        <v>86.15945785351235</v>
       </c>
       <c r="D287" t="n">
-        <v>48.23800101773549</v>
+        <v>43.47548150457305</v>
       </c>
       <c r="E287" t="n">
-        <v>64.3154236031293</v>
+        <v>60.05347843874286</v>
       </c>
       <c r="F287" t="n">
-        <v>61.84716253306078</v>
+        <v>53.41209443428716</v>
       </c>
     </row>
     <row r="288">
@@ -5683,16 +5683,16 @@
         <v>11</v>
       </c>
       <c r="C288" t="n">
-        <v>6.825613082246997</v>
+        <v>6.075053044076166</v>
       </c>
       <c r="D288" t="n">
-        <v>14.11843932226405</v>
+        <v>12.72453117207016</v>
       </c>
       <c r="E288" t="n">
-        <v>6.057099722918187</v>
+        <v>6.188042402210193</v>
       </c>
       <c r="F288" t="n">
-        <v>10.32673984698989</v>
+        <v>10.75741694560741</v>
       </c>
     </row>
     <row r="289">
@@ -5701,16 +5701,16 @@
         <v>12</v>
       </c>
       <c r="C289" t="n">
-        <v>17.75846521181856</v>
+        <v>15.80570372847206</v>
       </c>
       <c r="D289" t="n">
-        <v>23.53073220377341</v>
+        <v>21.20755195345027</v>
       </c>
       <c r="E289" t="n">
-        <v>23.11582776613181</v>
+        <v>23.12853965060437</v>
       </c>
       <c r="F289" t="n">
-        <v>22.11930240382518</v>
+        <v>22.7104964959725</v>
       </c>
     </row>
     <row r="290">
@@ -5721,16 +5721,16 @@
         <v>1</v>
       </c>
       <c r="C290" t="n">
-        <v>84.88859410123764</v>
+        <v>75.55404998612961</v>
       </c>
       <c r="D290" t="n">
-        <v>65.88605017056555</v>
+        <v>59.38114546966074</v>
       </c>
       <c r="E290" t="n">
-        <v>64.315580341161</v>
+        <v>60.50564994309574</v>
       </c>
       <c r="F290" t="n">
-        <v>55.45486449567233</v>
+        <v>54.67655753091974</v>
       </c>
     </row>
     <row r="291">
@@ -5739,16 +5739,16 @@
         <v>2</v>
       </c>
       <c r="C291" t="n">
-        <v>121.9743002743053</v>
+        <v>108.5617270202109</v>
       </c>
       <c r="D291" t="n">
-        <v>68.91143002533641</v>
+        <v>62.10783072081864</v>
       </c>
       <c r="E291" t="n">
-        <v>199.8690405796897</v>
+        <v>142.3810843531612</v>
       </c>
       <c r="F291" t="n">
-        <v>190.8600650342433</v>
+        <v>125.4073718337206</v>
       </c>
     </row>
     <row r="292">
@@ -5757,16 +5757,16 @@
         <v>3</v>
       </c>
       <c r="C292" t="n">
-        <v>45.71260204649867</v>
+        <v>40.68593969053443</v>
       </c>
       <c r="D292" t="n">
-        <v>70.59219661132025</v>
+        <v>63.62265586035079</v>
       </c>
       <c r="E292" t="n">
-        <v>48.49458183654531</v>
+        <v>46.31759054510519</v>
       </c>
       <c r="F292" t="n">
-        <v>120.3160537669134</v>
+        <v>111.875053540359</v>
       </c>
     </row>
     <row r="293">
@@ -5775,16 +5775,16 @@
         <v>4</v>
       </c>
       <c r="C293" t="n">
-        <v>267.5322529645865</v>
+        <v>238.1137940543834</v>
       </c>
       <c r="D293" t="n">
-        <v>122.3598074596218</v>
+        <v>110.2792701579414</v>
       </c>
       <c r="E293" t="n">
-        <v>158.4761661944156</v>
+        <v>168.0899216886087</v>
       </c>
       <c r="F293" t="n">
-        <v>147.0569241486039</v>
+        <v>143.3256543685266</v>
       </c>
     </row>
     <row r="294">
@@ -5793,16 +5793,16 @@
         <v>5</v>
       </c>
       <c r="C294" t="n">
-        <v>17.8412828885578</v>
+        <v>15.8794145839096</v>
       </c>
       <c r="D294" t="n">
-        <v>23.53073220377342</v>
+        <v>21.20755195345027</v>
       </c>
       <c r="E294" t="n">
-        <v>19.40994942419042</v>
+        <v>19.5378902273797</v>
       </c>
       <c r="F294" t="n">
-        <v>17.12764158497343</v>
+        <v>17.75798611562381</v>
       </c>
     </row>
     <row r="295">
@@ -5811,16 +5811,16 @@
         <v>6</v>
       </c>
       <c r="C295" t="n">
-        <v>143.2328365796114</v>
+        <v>127.4826260131609</v>
       </c>
       <c r="D295" t="n">
-        <v>37.64917152603746</v>
+        <v>33.93208312552043</v>
       </c>
       <c r="E295" t="n">
-        <v>39.89687089956722</v>
+        <v>39.47067003320708</v>
       </c>
       <c r="F295" t="n">
-        <v>31.10325773297174</v>
+        <v>28.61612702099574</v>
       </c>
     </row>
     <row r="296">
@@ -5829,16 +5829,16 @@
         <v>7</v>
       </c>
       <c r="C296" t="n">
-        <v>49.28494152034229</v>
+        <v>43.86545653884409</v>
       </c>
       <c r="D296" t="n">
-        <v>14.11843932226405</v>
+        <v>12.72453117207016</v>
       </c>
       <c r="E296" t="n">
-        <v>15.3327471595941</v>
+        <v>15.04263722153435</v>
       </c>
       <c r="F296" t="n">
-        <v>3.620311227693437</v>
+        <v>3.621647047243022</v>
       </c>
     </row>
     <row r="297">
@@ -5847,16 +5847,16 @@
         <v>8</v>
       </c>
       <c r="C297" t="n">
-        <v>50.65878297130241</v>
+        <v>45.08822723917006</v>
       </c>
       <c r="D297" t="n">
-        <v>27.56457201013458</v>
+        <v>24.84313228832745</v>
       </c>
       <c r="E297" t="n">
-        <v>74.95626229635772</v>
+        <v>49.03130962088265</v>
       </c>
       <c r="F297" t="n">
-        <v>80.4463529920107</v>
+        <v>49.62012799553713</v>
       </c>
     </row>
     <row r="298">
@@ -5865,16 +5865,16 @@
         <v>9</v>
       </c>
       <c r="C298" t="n">
-        <v>17.50979027975533</v>
+        <v>15.58437366114881</v>
       </c>
       <c r="D298" t="n">
-        <v>36.75276268017943</v>
+        <v>33.1241763844366</v>
       </c>
       <c r="E298" t="n">
-        <v>65.7017675291313</v>
+        <v>19.39573035306657</v>
       </c>
       <c r="F298" t="n">
-        <v>109.9085354027337</v>
+        <v>43.11315295802095</v>
       </c>
     </row>
     <row r="299">
@@ -5883,16 +5883,16 @@
         <v>10</v>
       </c>
       <c r="C299" t="n">
-        <v>50.73629725655181</v>
+        <v>45.15721787618529</v>
       </c>
       <c r="D299" t="n">
-        <v>36.75276268017943</v>
+        <v>33.12417638443662</v>
       </c>
       <c r="E299" t="n">
-        <v>28.31831000325455</v>
+        <v>27.33552585282733</v>
       </c>
       <c r="F299" t="n">
-        <v>33.9814220984917</v>
+        <v>31.77412248885491</v>
       </c>
     </row>
     <row r="300">
@@ -5901,16 +5901,16 @@
         <v>11</v>
       </c>
       <c r="C300" t="n">
-        <v>82.4553874619475</v>
+        <v>73.38840431844115</v>
       </c>
       <c r="D300" t="n">
-        <v>55.12914402026914</v>
+        <v>49.68626457665491</v>
       </c>
       <c r="E300" t="n">
-        <v>43.46206834325324</v>
+        <v>45.27128457694967</v>
       </c>
       <c r="F300" t="n">
-        <v>33.55465832422798</v>
+        <v>35.57654184829448</v>
       </c>
     </row>
     <row r="301">
@@ -5919,16 +5919,16 @@
         <v>12</v>
       </c>
       <c r="C301" t="n">
-        <v>132.8328713474748</v>
+        <v>118.226264763194</v>
       </c>
       <c r="D301" t="n">
-        <v>40.38530317763902</v>
+        <v>36.39807753871232</v>
       </c>
       <c r="E301" t="n">
-        <v>63.44163107794854</v>
+        <v>62.71940053775535</v>
       </c>
       <c r="F301" t="n">
-        <v>23.66709086381781</v>
+        <v>23.96926029038594</v>
       </c>
     </row>
     <row r="302">
@@ -5939,16 +5939,16 @@
         <v>1</v>
       </c>
       <c r="C302" t="n">
-        <v>110.5828943745125</v>
+        <v>98.42294618778466</v>
       </c>
       <c r="D302" t="n">
-        <v>40.38530317763902</v>
+        <v>36.39807753871232</v>
       </c>
       <c r="E302" t="n">
-        <v>47.39659880780961</v>
+        <v>42.74834306211811</v>
       </c>
       <c r="F302" t="n">
-        <v>15.87851205391908</v>
+        <v>14.05038248149418</v>
       </c>
     </row>
     <row r="303">
@@ -5957,16 +5957,16 @@
         <v>2</v>
       </c>
       <c r="C303" t="n">
-        <v>69.32845972621566</v>
+        <v>61.70494360371911</v>
       </c>
       <c r="D303" t="n">
-        <v>49.35981499489215</v>
+        <v>44.48653921398172</v>
       </c>
       <c r="E303" t="n">
-        <v>41.07924462854287</v>
+        <v>37.78738896421017</v>
       </c>
       <c r="F303" t="n">
-        <v>42.86085901241001</v>
+        <v>40.24460600060831</v>
       </c>
     </row>
     <row r="304">
@@ -5975,16 +5975,16 @@
         <v>3</v>
       </c>
       <c r="C304" t="n">
-        <v>39.44806075384405</v>
+        <v>35.11026169778864</v>
       </c>
       <c r="D304" t="n">
-        <v>57.00854665732377</v>
+        <v>51.38011450540451</v>
       </c>
       <c r="E304" t="n">
-        <v>49.87874417410232</v>
+        <v>36.61507382576687</v>
       </c>
       <c r="F304" t="n">
-        <v>93.1820651451177</v>
+        <v>71.47414206006853</v>
       </c>
     </row>
     <row r="305">
@@ -5993,16 +5993,16 @@
         <v>4</v>
       </c>
       <c r="C305" t="n">
-        <v>39.04687022744577</v>
+        <v>34.75318699998757</v>
       </c>
       <c r="D305" t="n">
-        <v>26.31163691876482</v>
+        <v>23.71389900249438</v>
       </c>
       <c r="E305" t="n">
-        <v>23.20439844301472</v>
+        <v>24.07383218991717</v>
       </c>
       <c r="F305" t="n">
-        <v>20.73711911022582</v>
+        <v>22.43295390723056</v>
       </c>
     </row>
     <row r="306">
@@ -6011,16 +6011,16 @@
         <v>5</v>
       </c>
       <c r="C306" t="n">
-        <v>148.9959809646145</v>
+        <v>132.6120418499047</v>
       </c>
       <c r="D306" t="n">
-        <v>52.62327383752963</v>
+        <v>47.42779800498877</v>
       </c>
       <c r="E306" t="n">
-        <v>42.40034758976662</v>
+        <v>42.80857667252222</v>
       </c>
       <c r="F306" t="n">
-        <v>69.96163944046236</v>
+        <v>64.10442572226818</v>
       </c>
     </row>
     <row r="307">
@@ -6029,16 +6029,16 @@
         <v>6</v>
       </c>
       <c r="C307" t="n">
-        <v>7.900183723603905</v>
+        <v>7.031461438045828</v>
       </c>
       <c r="D307" t="n">
-        <v>17.1512892507504</v>
+        <v>15.45794897940375</v>
       </c>
       <c r="E307" t="n">
-        <v>34.23337739924807</v>
+        <v>26.54656283455733</v>
       </c>
       <c r="F307" t="n">
-        <v>61.70422777035603</v>
+        <v>48.71372377521897</v>
       </c>
     </row>
     <row r="308">
@@ -6047,16 +6047,16 @@
         <v>7</v>
       </c>
       <c r="C308" t="n">
-        <v>51.91041756399946</v>
+        <v>46.20222922709583</v>
       </c>
       <c r="D308" t="n">
-        <v>47.1660454395636</v>
+        <v>42.50935969336031</v>
       </c>
       <c r="E308" t="n">
-        <v>75.34200772327438</v>
+        <v>53.52451972099019</v>
       </c>
       <c r="F308" t="n">
-        <v>72.34810777486317</v>
+        <v>55.32081796681907</v>
       </c>
     </row>
     <row r="309">
@@ -6065,16 +6065,16 @@
         <v>8</v>
       </c>
       <c r="C309" t="n">
-        <v>150.8436080046402</v>
+        <v>134.25649959144</v>
       </c>
       <c r="D309" t="n">
-        <v>104.8652196037728</v>
+        <v>94.51191631428922</v>
       </c>
       <c r="E309" t="n">
-        <v>85.55722216912423</v>
+        <v>82.13226276410028</v>
       </c>
       <c r="F309" t="n">
-        <v>76.30646026782838</v>
+        <v>73.12667905049535</v>
       </c>
     </row>
     <row r="310">
@@ -6083,16 +6083,16 @@
         <v>9</v>
       </c>
       <c r="C310" t="n">
-        <v>141.0576123051785</v>
+        <v>125.5465943789752</v>
       </c>
       <c r="D310" t="n">
-        <v>75.50295811471644</v>
+        <v>68.04857974628824</v>
       </c>
       <c r="E310" t="n">
-        <v>82.25825457400626</v>
+        <v>70.81256157863169</v>
       </c>
       <c r="F310" t="n">
-        <v>80.4480382643888</v>
+        <v>64.01047387372255</v>
       </c>
     </row>
     <row r="311">
@@ -6119,16 +6119,16 @@
         <v>11</v>
       </c>
       <c r="C312" t="n">
-        <v>47.66074355650047</v>
+        <v>42.41985910085229</v>
       </c>
       <c r="D312" t="n">
-        <v>75.50295811471644</v>
+        <v>68.04857974628824</v>
       </c>
       <c r="E312" t="n">
-        <v>20.84754656814441</v>
+        <v>20.93809739915725</v>
       </c>
       <c r="F312" t="n">
-        <v>38.20605272965993</v>
+        <v>39.76826089083906</v>
       </c>
     </row>
     <row r="313">
@@ -6137,16 +6137,16 @@
         <v>12</v>
       </c>
       <c r="C313" t="n">
-        <v>47.66306347645632</v>
+        <v>42.42192391709956</v>
       </c>
       <c r="D313" t="n">
-        <v>146.811307445282</v>
+        <v>132.3166828400049</v>
       </c>
       <c r="E313" t="n">
-        <v>37.20128675969446</v>
+        <v>37.50486563848042</v>
       </c>
       <c r="F313" t="n">
-        <v>99.87974190773933</v>
+        <v>101.4117177024644</v>
       </c>
     </row>
     <row r="314">
@@ -6157,16 +6157,16 @@
         <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>117.8756342135203</v>
+        <v>104.9137596612075</v>
       </c>
       <c r="D314" t="n">
-        <v>115.7712024425652</v>
+        <v>104.3411556109753</v>
       </c>
       <c r="E314" t="n">
-        <v>34.88373126974924</v>
+        <v>36.59046829045523</v>
       </c>
       <c r="F314" t="n">
-        <v>59.18680217175142</v>
+        <v>61.92895986153806</v>
       </c>
     </row>
     <row r="315">
@@ -6175,16 +6175,16 @@
         <v>2</v>
       </c>
       <c r="C315" t="n">
-        <v>106.3995912963175</v>
+        <v>94.69964869153755</v>
       </c>
       <c r="D315" t="n">
-        <v>47.1660454395636</v>
+        <v>42.50935969336031</v>
       </c>
       <c r="E315" t="n">
-        <v>42.22705743596121</v>
+        <v>42.86780118454647</v>
       </c>
       <c r="F315" t="n">
-        <v>24.85616112177732</v>
+        <v>25.61498280834184</v>
       </c>
     </row>
     <row r="316">
@@ -6193,16 +6193,16 @@
         <v>3</v>
       </c>
       <c r="C316" t="n">
-        <v>247.8153381130062</v>
+        <v>220.564996291377</v>
       </c>
       <c r="D316" t="n">
-        <v>138.4220898769801</v>
+        <v>124.7557295348618</v>
       </c>
       <c r="E316" t="n">
-        <v>166.3177613342177</v>
+        <v>159.9833796278005</v>
       </c>
       <c r="F316" t="n">
-        <v>117.6537110322261</v>
+        <v>119.4519114101849</v>
       </c>
     </row>
     <row r="317">
@@ -6211,16 +6211,16 @@
         <v>4</v>
       </c>
       <c r="C317" t="n">
-        <v>192.3679188468002</v>
+        <v>171.2147021653521</v>
       </c>
       <c r="D317" t="n">
-        <v>154.3616032567536</v>
+        <v>139.1215408146338</v>
       </c>
       <c r="E317" t="n">
-        <v>147.8386130657705</v>
+        <v>149.9626900251571</v>
       </c>
       <c r="F317" t="n">
-        <v>127.6508682453336</v>
+        <v>134.6349393460852</v>
       </c>
     </row>
     <row r="318">
@@ -6229,16 +6229,16 @@
         <v>5</v>
       </c>
       <c r="C318" t="n">
-        <v>11.53615777601618</v>
+        <v>10.26761546100687</v>
       </c>
       <c r="D318" t="n">
-        <v>25.7269338761256</v>
+        <v>23.18692346910563</v>
       </c>
       <c r="E318" t="n">
-        <v>6.044804404882994</v>
+        <v>6.34976355296365</v>
       </c>
       <c r="F318" t="n">
-        <v>12.01216384887664</v>
+        <v>12.7593703018652</v>
       </c>
     </row>
     <row r="319">
@@ -6247,16 +6247,16 @@
         <v>6</v>
       </c>
       <c r="C319" t="n">
-        <v>89.30387550609407</v>
+        <v>79.48381694124623</v>
       </c>
       <c r="D319" t="n">
-        <v>176.1735689343384</v>
+        <v>158.7800194080059</v>
       </c>
       <c r="E319" t="n">
-        <v>137.4358989339389</v>
+        <v>107.5043519160964</v>
       </c>
       <c r="F319" t="n">
-        <v>199.1451637809171</v>
+        <v>166.4781855102475</v>
       </c>
     </row>
     <row r="320">
@@ -6265,16 +6265,16 @@
         <v>7</v>
       </c>
       <c r="C320" t="n">
-        <v>30.78231361327578</v>
+        <v>27.39741994846216</v>
       </c>
       <c r="D320" t="n">
-        <v>81.46862394106438</v>
+        <v>73.4252576521678</v>
       </c>
       <c r="E320" t="n">
-        <v>35.91826174693267</v>
+        <v>31.71037609879161</v>
       </c>
       <c r="F320" t="n">
-        <v>87.11529082404402</v>
+        <v>76.68830376844043</v>
       </c>
     </row>
     <row r="321">
@@ -6283,16 +6283,16 @@
         <v>8</v>
       </c>
       <c r="C321" t="n">
-        <v>101.1888572274112</v>
+        <v>90.06189886808001</v>
       </c>
       <c r="D321" t="n">
-        <v>175.8007148201916</v>
+        <v>158.4439770388884</v>
       </c>
       <c r="E321" t="n">
-        <v>61.70830799438611</v>
+        <v>64.22710222947926</v>
       </c>
       <c r="F321" t="n">
-        <v>116.3281450660332</v>
+        <v>118.8166396286334</v>
       </c>
     </row>
     <row r="322">
@@ -6301,16 +6301,16 @@
         <v>9</v>
       </c>
       <c r="C322" t="n">
-        <v>95.3761552911287</v>
+        <v>84.8883749418314</v>
       </c>
       <c r="D322" t="n">
-        <v>137.2103140060032</v>
+        <v>123.66359183523</v>
       </c>
       <c r="E322" t="n">
-        <v>55.27313411913383</v>
+        <v>56.35997745618314</v>
       </c>
       <c r="F322" t="n">
-        <v>78.64342431887995</v>
+        <v>81.86740914351108</v>
       </c>
     </row>
     <row r="323">
@@ -6319,16 +6319,16 @@
         <v>10</v>
       </c>
       <c r="C323" t="n">
-        <v>38.74990067924254</v>
+        <v>34.48887290306018</v>
       </c>
       <c r="D323" t="n">
-        <v>128.634669380628</v>
+        <v>115.9346173455281</v>
       </c>
       <c r="E323" t="n">
-        <v>63.85167195857976</v>
+        <v>37.14511571570819</v>
       </c>
       <c r="F323" t="n">
-        <v>126.1438393618686</v>
+        <v>104.7455216317741</v>
       </c>
     </row>
     <row r="324">
@@ -6337,16 +6337,16 @@
         <v>11</v>
       </c>
       <c r="C324" t="n">
-        <v>59.62990549453383</v>
+        <v>53.07286459508591</v>
       </c>
       <c r="D324" t="n">
-        <v>38.5904008141884</v>
+        <v>34.78038520365844</v>
       </c>
       <c r="E324" t="n">
-        <v>26.20337769453445</v>
+        <v>24.29440490214374</v>
       </c>
       <c r="F324" t="n">
-        <v>18.22944709378502</v>
+        <v>17.33848074357394</v>
       </c>
     </row>
     <row r="325">
@@ -6355,16 +6355,16 @@
         <v>12</v>
       </c>
       <c r="C325" t="n">
-        <v>24.05793711359053</v>
+        <v>21.41247128060142</v>
       </c>
       <c r="D325" t="n">
-        <v>50.33530540981096</v>
+        <v>45.36571983085883</v>
       </c>
       <c r="E325" t="n">
-        <v>118.4977950748032</v>
+        <v>128.6105329139264</v>
       </c>
       <c r="F325" t="n">
-        <v>104.0254510760636</v>
+        <v>114.1352055817079</v>
       </c>
     </row>
     <row r="326">
@@ -6375,16 +6375,16 @@
         <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>206.4335009981734</v>
+        <v>183.7336007076165</v>
       </c>
       <c r="D326" t="n">
-        <v>121.6436547403765</v>
+        <v>109.6338229245755</v>
       </c>
       <c r="E326" t="n">
-        <v>137.613402432055</v>
+        <v>122.7428377483355</v>
       </c>
       <c r="F326" t="n">
-        <v>124.3569366394705</v>
+        <v>108.8014239453054</v>
       </c>
     </row>
     <row r="327">
@@ -6393,16 +6393,16 @@
         <v>2</v>
       </c>
       <c r="C327" t="n">
-        <v>31.63549270479268</v>
+        <v>28.15678151417161</v>
       </c>
       <c r="D327" t="n">
-        <v>75.50295811471644</v>
+        <v>68.04857974628824</v>
       </c>
       <c r="E327" t="n">
-        <v>40.66904336458255</v>
+        <v>41.63019418378374</v>
       </c>
       <c r="F327" t="n">
-        <v>63.24633236982852</v>
+        <v>66.02496127911833</v>
       </c>
     </row>
     <row r="328">
@@ -6411,16 +6411,16 @@
         <v>3</v>
       </c>
       <c r="C328" t="n">
-        <v>26.10956076389692</v>
+        <v>23.23849369820811</v>
       </c>
       <c r="D328" t="n">
-        <v>83.89217568301827</v>
+        <v>75.60953305143137</v>
       </c>
       <c r="E328" t="n">
-        <v>39.57968392249608</v>
+        <v>38.48049254922466</v>
       </c>
       <c r="F328" t="n">
-        <v>86.15902824473561</v>
+        <v>82.98533080971649</v>
       </c>
     </row>
     <row r="329">
@@ -6429,16 +6429,16 @@
         <v>4</v>
       </c>
       <c r="C329" t="n">
-        <v>107.7969246259359</v>
+        <v>95.94332804977226</v>
       </c>
       <c r="D329" t="n">
-        <v>83.89217568301827</v>
+        <v>75.60953305143138</v>
       </c>
       <c r="E329" t="n">
-        <v>33.68862144512296</v>
+        <v>34.48753042227176</v>
       </c>
       <c r="F329" t="n">
-        <v>53.46929870478997</v>
+        <v>53.06340779331984</v>
       </c>
     </row>
     <row r="330">
@@ -6447,16 +6447,16 @@
         <v>5</v>
       </c>
       <c r="C330" t="n">
-        <v>140.4111841062563</v>
+        <v>124.9712489044635</v>
       </c>
       <c r="D330" t="n">
-        <v>109.0598283879237</v>
+        <v>98.2923929668608</v>
       </c>
       <c r="E330" t="n">
-        <v>80.9681763737559</v>
+        <v>72.3080282950104</v>
       </c>
       <c r="F330" t="n">
-        <v>134.6864794145756</v>
+        <v>112.8299902622214</v>
       </c>
     </row>
     <row r="331">
@@ -6465,16 +6465,16 @@
         <v>6</v>
       </c>
       <c r="C331" t="n">
-        <v>23.23402515802826</v>
+        <v>20.67915856958535</v>
       </c>
       <c r="D331" t="n">
-        <v>58.72452297811279</v>
+        <v>52.92667313600197</v>
       </c>
       <c r="E331" t="n">
-        <v>30.18359862975751</v>
+        <v>27.2173123925485</v>
       </c>
       <c r="F331" t="n">
-        <v>54.59528923881954</v>
+        <v>51.16302916275772</v>
       </c>
     </row>
     <row r="332">
@@ -6483,16 +6483,16 @@
         <v>7</v>
       </c>
       <c r="C332" t="n">
-        <v>183.1184182258857</v>
+        <v>162.9822978045744</v>
       </c>
       <c r="D332" t="n">
-        <v>113.2544371720746</v>
+        <v>102.0728696194324</v>
       </c>
       <c r="E332" t="n">
-        <v>66.88833995478321</v>
+        <v>68.38036270209278</v>
       </c>
       <c r="F332" t="n">
-        <v>45.23231534902712</v>
+        <v>46.71900435069936</v>
       </c>
     </row>
     <row r="333">
@@ -6501,16 +6501,16 @@
         <v>8</v>
       </c>
       <c r="C333" t="n">
-        <v>71.70406728111921</v>
+        <v>63.81932391418291</v>
       </c>
       <c r="D333" t="n">
-        <v>142.616698661131</v>
+        <v>128.5362061874334</v>
       </c>
       <c r="E333" t="n">
-        <v>62.28854278853267</v>
+        <v>55.26561473382369</v>
       </c>
       <c r="F333" t="n">
-        <v>122.6441365474847</v>
+        <v>113.0284553910242</v>
       </c>
     </row>
     <row r="334">
@@ -6519,16 +6519,16 @@
         <v>9</v>
       </c>
       <c r="C334" t="n">
-        <v>91.6221385235565</v>
+        <v>81.54715845086606</v>
       </c>
       <c r="D334" t="n">
-        <v>113.2544371720746</v>
+        <v>102.0728696194324</v>
       </c>
       <c r="E334" t="n">
-        <v>35.43018549373755</v>
+        <v>35.3583125224516</v>
       </c>
       <c r="F334" t="n">
-        <v>44.56733904223159</v>
+        <v>45.96791094445778</v>
       </c>
     </row>
     <row r="335">
@@ -6537,16 +6537,16 @@
         <v>10</v>
       </c>
       <c r="C335" t="n">
-        <v>137.235089103931</v>
+        <v>122.1444045785909</v>
       </c>
       <c r="D335" t="n">
-        <v>159.3951337977347</v>
+        <v>143.6581127977196</v>
       </c>
       <c r="E335" t="n">
-        <v>63.63405591123768</v>
+        <v>60.09137876283473</v>
       </c>
       <c r="F335" t="n">
-        <v>90.95371692852396</v>
+        <v>86.81894591267826</v>
       </c>
     </row>
     <row r="336">
@@ -6555,16 +6555,16 @@
         <v>11</v>
       </c>
       <c r="C336" t="n">
-        <v>385.1765943844817</v>
+        <v>342.8216944069758</v>
       </c>
       <c r="D336" t="n">
-        <v>197.1466128550929</v>
+        <v>177.6824026708638</v>
       </c>
       <c r="E336" t="n">
-        <v>146.6546337759594</v>
+        <v>146.4862697759027</v>
       </c>
       <c r="F336" t="n">
-        <v>91.60135565567708</v>
+        <v>92.76591474757005</v>
       </c>
     </row>
     <row r="337">
@@ -6573,16 +6573,16 @@
         <v>12</v>
       </c>
       <c r="C337" t="n">
-        <v>223.6460480747973</v>
+        <v>199.0534167086321</v>
       </c>
       <c r="D337" t="n">
-        <v>184.5627865026402</v>
+        <v>166.340972713149</v>
       </c>
       <c r="E337" t="n">
-        <v>82.09622493857565</v>
+        <v>83.2008631387159</v>
       </c>
       <c r="F337" t="n">
-        <v>77.26247775285033</v>
+        <v>81.15812112543516</v>
       </c>
     </row>
     <row r="338">
@@ -6593,16 +6593,16 @@
         <v>1</v>
       </c>
       <c r="C338" t="n">
-        <v>98.09172729809671</v>
+        <v>87.30533643504106</v>
       </c>
       <c r="D338" t="n">
-        <v>151.0059162294329</v>
+        <v>136.0971594925765</v>
       </c>
       <c r="E338" t="n">
-        <v>39.44463595128063</v>
+        <v>40.11456937230517</v>
       </c>
       <c r="F338" t="n">
-        <v>72.50395488911934</v>
+        <v>75.90976959668585</v>
       </c>
     </row>
     <row r="339">
@@ -6611,16 +6611,16 @@
         <v>2</v>
       </c>
       <c r="C339" t="n">
-        <v>94.3613731201464</v>
+        <v>83.98518054117973</v>
       </c>
       <c r="D339" t="n">
-        <v>75.50295811471642</v>
+        <v>68.04857974628824</v>
       </c>
       <c r="E339" t="n">
-        <v>80.20577253280058</v>
+        <v>59.34416427015147</v>
       </c>
       <c r="F339" t="n">
-        <v>51.91127519999004</v>
+        <v>43.03991508213544</v>
       </c>
     </row>
     <row r="340">
@@ -6629,16 +6629,16 @@
         <v>3</v>
       </c>
       <c r="C340" t="n">
-        <v>23.96555198842317</v>
+        <v>21.33024503526456</v>
       </c>
       <c r="D340" t="n">
-        <v>37.75147905735822</v>
+        <v>34.02428987314412</v>
       </c>
       <c r="E340" t="n">
-        <v>38.45605026436159</v>
+        <v>20.65734389522123</v>
       </c>
       <c r="F340" t="n">
-        <v>33.20431144824069</v>
+        <v>23.18998762513793</v>
       </c>
     </row>
     <row r="341">
@@ -6647,16 +6647,16 @@
         <v>4</v>
       </c>
       <c r="C341" t="n">
-        <v>142.4383331606564</v>
+        <v>126.7754880087514</v>
       </c>
       <c r="D341" t="n">
-        <v>88.08678446716918</v>
+        <v>79.39000970400295</v>
       </c>
       <c r="E341" t="n">
-        <v>49.56669187200598</v>
+        <v>51.40748809421112</v>
       </c>
       <c r="F341" t="n">
-        <v>32.40318247163857</v>
+        <v>34.070052943581</v>
       </c>
     </row>
     <row r="342">
@@ -6665,16 +6665,16 @@
         <v>5</v>
       </c>
       <c r="C342" t="n">
-        <v>171.4301832277782</v>
+        <v>152.5793278809181</v>
       </c>
       <c r="D342" t="n">
-        <v>71.30834933056552</v>
+        <v>64.26810309371669</v>
       </c>
       <c r="E342" t="n">
-        <v>89.97555714610748</v>
+        <v>87.18983526576491</v>
       </c>
       <c r="F342" t="n">
-        <v>52.93007963394238</v>
+        <v>46.48883017552269</v>
       </c>
     </row>
     <row r="343">
@@ -6683,16 +6683,16 @@
         <v>6</v>
       </c>
       <c r="C343" t="n">
-        <v>71.88821585001793</v>
+        <v>63.98322308493434</v>
       </c>
       <c r="D343" t="n">
-        <v>71.30834933056552</v>
+        <v>64.26810309371669</v>
       </c>
       <c r="E343" t="n">
-        <v>95.71444409214554</v>
+        <v>94.43959345515968</v>
       </c>
       <c r="F343" t="n">
-        <v>100.9788579808861</v>
+        <v>101.8898195126297</v>
       </c>
     </row>
     <row r="344">
@@ -6701,16 +6701,16 @@
         <v>7</v>
       </c>
       <c r="C344" t="n">
-        <v>74.38175723191964</v>
+        <v>66.20256894883218</v>
       </c>
       <c r="D344" t="n">
-        <v>46.14069662566004</v>
+        <v>41.58524317828726</v>
       </c>
       <c r="E344" t="n">
-        <v>53.19564533487518</v>
+        <v>50.99968896859627</v>
       </c>
       <c r="F344" t="n">
-        <v>52.90784938100634</v>
+        <v>46.16959022130701</v>
       </c>
     </row>
     <row r="345">
@@ -6719,16 +6719,16 @@
         <v>8</v>
       </c>
       <c r="C345" t="n">
-        <v>196.4313813233706</v>
+        <v>174.8313370068412</v>
       </c>
       <c r="D345" t="n">
-        <v>188.7573952867911</v>
+        <v>170.1214493657206</v>
       </c>
       <c r="E345" t="n">
-        <v>78.46898260053932</v>
+        <v>81.8501267213401</v>
       </c>
       <c r="F345" t="n">
-        <v>77.66309231427772</v>
+        <v>81.38538788744842</v>
       </c>
     </row>
     <row r="346">
@@ -6737,16 +6737,16 @@
         <v>9</v>
       </c>
       <c r="C346" t="n">
-        <v>351.7141465074478</v>
+        <v>313.0388538931545</v>
       </c>
       <c r="D346" t="n">
-        <v>243.287309480753</v>
+        <v>219.2676458491511</v>
       </c>
       <c r="E346" t="n">
-        <v>167.3083320043454</v>
+        <v>166.8376028645236</v>
       </c>
       <c r="F346" t="n">
-        <v>117.4088133421181</v>
+        <v>119.9615730877815</v>
       </c>
     </row>
     <row r="347">
@@ -6755,16 +6755,16 @@
         <v>10</v>
       </c>
       <c r="C347" t="n">
-        <v>59.18077892498793</v>
+        <v>52.67312501116606</v>
       </c>
       <c r="D347" t="n">
-        <v>138.4220898769801</v>
+        <v>124.7557295348618</v>
       </c>
       <c r="E347" t="n">
-        <v>41.36963108849031</v>
+        <v>37.2009589681703</v>
       </c>
       <c r="F347" t="n">
-        <v>71.47158806461357</v>
+        <v>72.84599666813553</v>
       </c>
     </row>
     <row r="348">
@@ -6773,16 +6773,16 @@
         <v>11</v>
       </c>
       <c r="C348" t="n">
-        <v>98.51631226603122</v>
+        <v>87.68323306803778</v>
       </c>
       <c r="D348" t="n">
-        <v>138.4220898769801</v>
+        <v>124.7557295348618</v>
       </c>
       <c r="E348" t="n">
-        <v>43.3020626123378</v>
+        <v>44.78799977565889</v>
       </c>
       <c r="F348" t="n">
-        <v>68.14344232108276</v>
+        <v>71.68890623037871</v>
       </c>
     </row>
     <row r="349">
@@ -6791,16 +6791,16 @@
         <v>12</v>
       </c>
       <c r="C349" t="n">
-        <v>44.46232909828019</v>
+        <v>39.5731496175436</v>
       </c>
       <c r="D349" t="n">
-        <v>88.08678446716918</v>
+        <v>79.39000970400295</v>
       </c>
       <c r="E349" t="n">
-        <v>28.80313429685888</v>
+        <v>26.03095978143448</v>
       </c>
       <c r="F349" t="n">
-        <v>39.42594438164134</v>
+        <v>40.42592659126041</v>
       </c>
     </row>
     <row r="350">
@@ -6811,16 +6811,16 @@
         <v>1</v>
       </c>
       <c r="C350" t="n">
-        <v>57.97320640897412</v>
+        <v>51.59833993311453</v>
       </c>
       <c r="D350" t="n">
-        <v>121.6436547403764</v>
+        <v>109.6338229245755</v>
       </c>
       <c r="E350" t="n">
-        <v>36.46441272839425</v>
+        <v>35.01752016600942</v>
       </c>
       <c r="F350" t="n">
-        <v>79.99747085776406</v>
+        <v>80.16753489978679</v>
       </c>
     </row>
     <row r="351">
@@ -6829,16 +6829,16 @@
         <v>2</v>
       </c>
       <c r="C351" t="n">
-        <v>332.6569339402852</v>
+        <v>296.0772160413302</v>
       </c>
       <c r="D351" t="n">
-        <v>184.5627865026401</v>
+        <v>166.340972713149</v>
       </c>
       <c r="E351" t="n">
-        <v>178.1999490829895</v>
+        <v>171.0432567366021</v>
       </c>
       <c r="F351" t="n">
-        <v>146.6521430004217</v>
+        <v>136.5994505392655</v>
       </c>
     </row>
     <row r="352">
@@ -6847,16 +6847,16 @@
         <v>3</v>
       </c>
       <c r="C352" t="n">
-        <v>73.40081968509286</v>
+        <v>65.32949753999445</v>
       </c>
       <c r="D352" t="n">
-        <v>134.2274810928292</v>
+        <v>120.9752528822902</v>
       </c>
       <c r="E352" t="n">
-        <v>47.07133967405906</v>
+        <v>45.15172334057507</v>
       </c>
       <c r="F352" t="n">
-        <v>68.91368416111288</v>
+        <v>70.60818960328717</v>
       </c>
     </row>
     <row r="353">
@@ -6865,16 +6865,16 @@
         <v>4</v>
       </c>
       <c r="C353" t="n">
-        <v>185.9660975399754</v>
+        <v>165.5168397830246</v>
       </c>
       <c r="D353" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914611</v>
       </c>
       <c r="E353" t="n">
-        <v>92.36702351116654</v>
+        <v>85.86885825220381</v>
       </c>
       <c r="F353" t="n">
-        <v>119.7189560016922</v>
+        <v>102.9253246122602</v>
       </c>
     </row>
     <row r="354">
@@ -6883,16 +6883,16 @@
         <v>5</v>
       </c>
       <c r="C354" t="n">
-        <v>52.30669581817886</v>
+        <v>46.55493181737526</v>
       </c>
       <c r="D354" t="n">
-        <v>33.55687027320731</v>
+        <v>30.24381322057256</v>
       </c>
       <c r="E354" t="n">
-        <v>45.67298144686122</v>
+        <v>46.91630168670481</v>
       </c>
       <c r="F354" t="n">
-        <v>23.55271837436584</v>
+        <v>24.65204740999875</v>
       </c>
     </row>
     <row r="355">
@@ -6901,16 +6901,16 @@
         <v>6</v>
       </c>
       <c r="C355" t="n">
-        <v>60.02825790629539</v>
+        <v>53.42741326383209</v>
       </c>
       <c r="D355" t="n">
-        <v>146.811307445282</v>
+        <v>132.3166828400049</v>
       </c>
       <c r="E355" t="n">
-        <v>78.49299069414027</v>
+        <v>73.22817639319352</v>
       </c>
       <c r="F355" t="n">
-        <v>183.7601712198552</v>
+        <v>174.2876861313688</v>
       </c>
     </row>
     <row r="356">
@@ -6919,16 +6919,16 @@
         <v>7</v>
       </c>
       <c r="C356" t="n">
-        <v>8.053913172960344</v>
+        <v>7.168286445268409</v>
       </c>
       <c r="D356" t="n">
-        <v>32.158667345157</v>
+        <v>28.98365433638203</v>
       </c>
       <c r="E356" t="n">
-        <v>11.09983062689255</v>
+        <v>9.327360559745756</v>
       </c>
       <c r="F356" t="n">
-        <v>35.79790705040948</v>
+        <v>30.83171392398128</v>
       </c>
     </row>
     <row r="357">
@@ -6937,16 +6937,16 @@
         <v>8</v>
       </c>
       <c r="C357" t="n">
-        <v>126.1711050753336</v>
+        <v>112.2970415589435</v>
       </c>
       <c r="D357" t="n">
-        <v>156.7735033076404</v>
+        <v>141.2953148898624</v>
       </c>
       <c r="E357" t="n">
-        <v>81.65353329430889</v>
+        <v>74.174282991376</v>
       </c>
       <c r="F357" t="n">
-        <v>121.2672952757945</v>
+        <v>112.1564693447289</v>
       </c>
     </row>
     <row r="358">
@@ -6955,16 +6955,16 @@
         <v>9</v>
       </c>
       <c r="C358" t="n">
-        <v>74.4690602660669</v>
+        <v>66.28027194151029</v>
       </c>
       <c r="D358" t="n">
-        <v>112.5553357080495</v>
+        <v>101.4427901773371</v>
       </c>
       <c r="E358" t="n">
-        <v>64.05066326968468</v>
+        <v>42.69746429139839</v>
       </c>
       <c r="F358" t="n">
-        <v>90.11943488447287</v>
+        <v>72.56257853561333</v>
       </c>
     </row>
     <row r="359">
@@ -6973,16 +6973,16 @@
         <v>10</v>
       </c>
       <c r="C359" t="n">
-        <v>29.54870334042006</v>
+        <v>26.2994602849108</v>
       </c>
       <c r="D359" t="n">
-        <v>72.35700152660326</v>
+        <v>65.21322225685957</v>
       </c>
       <c r="E359" t="n">
-        <v>14.02653053802682</v>
+        <v>14.15056881747241</v>
       </c>
       <c r="F359" t="n">
-        <v>36.6141338659241</v>
+        <v>38.11125002038743</v>
       </c>
     </row>
     <row r="360">
@@ -6991,16 +6991,16 @@
         <v>11</v>
       </c>
       <c r="C360" t="n">
-        <v>119.544924973914</v>
+        <v>106.3994913886261</v>
       </c>
       <c r="D360" t="n">
-        <v>168.8330035620743</v>
+        <v>152.1641852660057</v>
       </c>
       <c r="E360" t="n">
-        <v>56.51291349516517</v>
+        <v>56.89366097246124</v>
       </c>
       <c r="F360" t="n">
-        <v>71.21754472406033</v>
+        <v>73.18967826822943</v>
       </c>
     </row>
     <row r="361">
@@ -7009,16 +7009,16 @@
         <v>12</v>
       </c>
       <c r="C361" t="n">
-        <v>247.350472008906</v>
+        <v>220.1512479281498</v>
       </c>
       <c r="D361" t="n">
-        <v>253.2495053431114</v>
+        <v>228.2462778990086</v>
       </c>
       <c r="E361" t="n">
-        <v>124.7391434117755</v>
+        <v>129.7601912240532</v>
       </c>
       <c r="F361" t="n">
-        <v>119.3755948212406</v>
+        <v>126.5161203947364</v>
       </c>
     </row>
     <row r="362">
@@ -7029,16 +7029,16 @@
         <v>1</v>
       </c>
       <c r="C362" t="n">
-        <v>115.52596867581</v>
+        <v>102.8224687243458</v>
       </c>
       <c r="D362" t="n">
-        <v>164.8131701439296</v>
+        <v>148.5412284739579</v>
       </c>
       <c r="E362" t="n">
-        <v>80.76745627146492</v>
+        <v>82.75778595000178</v>
       </c>
       <c r="F362" t="n">
-        <v>93.22581811174436</v>
+        <v>97.44465099058336</v>
       </c>
     </row>
     <row r="363">
@@ -7047,16 +7047,16 @@
         <v>2</v>
       </c>
       <c r="C363" t="n">
-        <v>33.92916069851863</v>
+        <v>30.19823252516237</v>
       </c>
       <c r="D363" t="n">
-        <v>40.19833418144625</v>
+        <v>36.22956792047754</v>
       </c>
       <c r="E363" t="n">
-        <v>31.13838431066812</v>
+        <v>31.00373547326098</v>
       </c>
       <c r="F363" t="n">
-        <v>30.0592809000613</v>
+        <v>30.71516224421378</v>
       </c>
     </row>
     <row r="364">
@@ -7065,16 +7065,16 @@
         <v>3</v>
       </c>
       <c r="C364" t="n">
-        <v>105.3755447660477</v>
+        <v>93.7882086617515</v>
       </c>
       <c r="D364" t="n">
-        <v>88.43633519918176</v>
+        <v>79.70504942505057</v>
       </c>
       <c r="E364" t="n">
-        <v>93.89877786503445</v>
+        <v>63.46952869489547</v>
       </c>
       <c r="F364" t="n">
-        <v>78.32696082626543</v>
+        <v>58.0655665125712</v>
       </c>
     </row>
     <row r="365">
@@ -7083,16 +7083,16 @@
         <v>4</v>
       </c>
       <c r="C365" t="n">
-        <v>67.76293308233265</v>
+        <v>60.31156585304637</v>
       </c>
       <c r="D365" t="n">
-        <v>88.43633519918174</v>
+        <v>79.70504942505057</v>
       </c>
       <c r="E365" t="n">
-        <v>70.93619527537746</v>
+        <v>62.75540448878567</v>
       </c>
       <c r="F365" t="n">
-        <v>70.78120697649646</v>
+        <v>69.83383309057267</v>
       </c>
     </row>
     <row r="366">
@@ -7101,16 +7101,16 @@
         <v>5</v>
       </c>
       <c r="C366" t="n">
-        <v>50.40774860686307</v>
+        <v>44.86479718805546</v>
       </c>
       <c r="D366" t="n">
-        <v>52.25783443588012</v>
+        <v>47.0984382966208</v>
       </c>
       <c r="E366" t="n">
-        <v>40.2397211821105</v>
+        <v>36.54663126304865</v>
       </c>
       <c r="F366" t="n">
-        <v>55.59491216673213</v>
+        <v>50.03126559722764</v>
       </c>
     </row>
     <row r="367">
@@ -7119,16 +7119,16 @@
         <v>6</v>
       </c>
       <c r="C367" t="n">
-        <v>111.6452089775646</v>
+        <v>99.36844624547525</v>
       </c>
       <c r="D367" t="n">
-        <v>72.35700152660326</v>
+        <v>65.21322225685957</v>
       </c>
       <c r="E367" t="n">
-        <v>42.89620243177123</v>
+        <v>42.76541781836379</v>
       </c>
       <c r="F367" t="n">
-        <v>27.0383961388415</v>
+        <v>27.92554109264454</v>
       </c>
     </row>
     <row r="368">
@@ -7137,16 +7137,16 @@
         <v>7</v>
       </c>
       <c r="C368" t="n">
-        <v>88.25908015247821</v>
+        <v>78.55390967622276</v>
       </c>
       <c r="D368" t="n">
-        <v>70.88032802606034</v>
+        <v>63.88234016998488</v>
       </c>
       <c r="E368" t="n">
-        <v>36.47088659450205</v>
+        <v>33.97568422999818</v>
       </c>
       <c r="F368" t="n">
-        <v>29.73458820345533</v>
+        <v>29.08671730170277</v>
       </c>
     </row>
     <row r="369">
@@ -7155,16 +7155,16 @@
         <v>8</v>
       </c>
       <c r="C369" t="n">
-        <v>77.68364862135944</v>
+        <v>69.14137680314755</v>
       </c>
       <c r="D369" t="n">
-        <v>110.2582880405383</v>
+        <v>99.37252915330983</v>
       </c>
       <c r="E369" t="n">
-        <v>84.70973800456842</v>
+        <v>48.38337331935575</v>
       </c>
       <c r="F369" t="n">
-        <v>130.8560093750162</v>
+        <v>97.35128342276199</v>
       </c>
     </row>
     <row r="370">
@@ -7173,16 +7173,16 @@
         <v>9</v>
       </c>
       <c r="C370" t="n">
-        <v>82.65969657158108</v>
+        <v>73.5702471307213</v>
       </c>
       <c r="D370" t="n">
-        <v>137.8228600506729</v>
+        <v>124.2156614416373</v>
       </c>
       <c r="E370" t="n">
-        <v>49.37711779929594</v>
+        <v>47.49122601720948</v>
       </c>
       <c r="F370" t="n">
-        <v>78.16556297103818</v>
+        <v>79.55636098918389</v>
       </c>
     </row>
     <row r="371">
@@ -7191,16 +7191,16 @@
         <v>10</v>
       </c>
       <c r="C371" t="n">
-        <v>93.50537860884161</v>
+        <v>83.2233131456867</v>
       </c>
       <c r="D371" t="n">
-        <v>129.9472680477772</v>
+        <v>117.1176236449723</v>
       </c>
       <c r="E371" t="n">
-        <v>89.9936048961127</v>
+        <v>87.65393343568225</v>
       </c>
       <c r="F371" t="n">
-        <v>121.752753056166</v>
+        <v>120.0197425215142</v>
       </c>
     </row>
     <row r="372">
@@ -7209,16 +7209,16 @@
         <v>11</v>
       </c>
       <c r="C372" t="n">
-        <v>137.00956975382</v>
+        <v>121.9436838524259</v>
       </c>
       <c r="D372" t="n">
-        <v>177.2008200651508</v>
+        <v>159.7058504249622</v>
       </c>
       <c r="E372" t="n">
-        <v>122.8285924770501</v>
+        <v>97.77748305968525</v>
       </c>
       <c r="F372" t="n">
-        <v>144.4764297149381</v>
+        <v>121.1674168367931</v>
       </c>
     </row>
     <row r="373">
@@ -7227,16 +7227,16 @@
         <v>12</v>
       </c>
       <c r="C373" t="n">
-        <v>157.4723825815672</v>
+        <v>140.1563589427992</v>
       </c>
       <c r="D373" t="n">
-        <v>220.5165760810766</v>
+        <v>198.7450583066197</v>
       </c>
       <c r="E373" t="n">
-        <v>102.963098804709</v>
+        <v>98.32513586258376</v>
       </c>
       <c r="F373" t="n">
-        <v>149.9121020131819</v>
+        <v>146.9071815118471</v>
       </c>
     </row>
     <row r="374">
@@ -7247,16 +7247,16 @@
         <v>1</v>
       </c>
       <c r="C374" t="n">
-        <v>98.36382553450771</v>
+        <v>87.54751412655067</v>
       </c>
       <c r="D374" t="n">
-        <v>126.0094720463295</v>
+        <v>113.5686047466398</v>
       </c>
       <c r="E374" t="n">
-        <v>63.21052257290987</v>
+        <v>62.70850960307116</v>
       </c>
       <c r="F374" t="n">
-        <v>86.74127510441583</v>
+        <v>86.64750458885364</v>
       </c>
     </row>
     <row r="375">
@@ -7265,16 +7265,16 @@
         <v>2</v>
       </c>
       <c r="C375" t="n">
-        <v>201.4182049067123</v>
+        <v>179.269798054252</v>
       </c>
       <c r="D375" t="n">
-        <v>157.5118400579118</v>
+        <v>141.9607559332997</v>
       </c>
       <c r="E375" t="n">
-        <v>117.9891648867251</v>
+        <v>94.3159699282032</v>
       </c>
       <c r="F375" t="n">
-        <v>94.50036014139005</v>
+        <v>79.58191163924639</v>
       </c>
     </row>
     <row r="376">
@@ -7283,16 +7283,16 @@
         <v>3</v>
       </c>
       <c r="C376" t="n">
-        <v>122.754153516363</v>
+        <v>109.2558258147086</v>
       </c>
       <c r="D376" t="n">
-        <v>200.8275960738376</v>
+        <v>180.9999638149572</v>
       </c>
       <c r="E376" t="n">
-        <v>248.5260980425389</v>
+        <v>187.9085495127993</v>
       </c>
       <c r="F376" t="n">
-        <v>325.7228780079885</v>
+        <v>255.2121422177107</v>
       </c>
     </row>
     <row r="377">
@@ -7301,16 +7301,16 @@
         <v>4</v>
       </c>
       <c r="C377" t="n">
-        <v>207.3543655896773</v>
+        <v>184.5532049208041</v>
       </c>
       <c r="D377" t="n">
-        <v>275.6457201013458</v>
+        <v>248.4313228832746</v>
       </c>
       <c r="E377" t="n">
-        <v>171.3463076833795</v>
+        <v>165.5701130417929</v>
       </c>
       <c r="F377" t="n">
-        <v>213.323121572079</v>
+        <v>211.1332759651346</v>
       </c>
     </row>
     <row r="378">
@@ -7319,16 +7319,16 @@
         <v>5</v>
       </c>
       <c r="C378" t="n">
-        <v>269.2706554384064</v>
+        <v>239.661037813025</v>
       </c>
       <c r="D378" t="n">
-        <v>405.592988149123</v>
+        <v>365.5489465282468</v>
       </c>
       <c r="E378" t="n">
-        <v>264.4962921628622</v>
+        <v>239.9277929070482</v>
       </c>
       <c r="F378" t="n">
-        <v>327.9878676555192</v>
+        <v>307.8865629304141</v>
       </c>
     </row>
     <row r="379">
@@ -7337,16 +7337,16 @@
         <v>6</v>
       </c>
       <c r="C379" t="n">
-        <v>676.3317525915826</v>
+        <v>601.9607649712043</v>
       </c>
       <c r="D379" t="n">
-        <v>515.8512761896612</v>
+        <v>464.9214756815567</v>
       </c>
       <c r="E379" t="n">
-        <v>852.1413337672449</v>
+        <v>703.9690987094056</v>
       </c>
       <c r="F379" t="n">
-        <v>708.2929581798585</v>
+        <v>555.8794224599575</v>
       </c>
     </row>
     <row r="380">
@@ -7355,16 +7355,16 @@
         <v>7</v>
       </c>
       <c r="C380" t="n">
-        <v>198.1668325829058</v>
+        <v>176.3759540734761</v>
       </c>
       <c r="D380" t="n">
-        <v>273.3486724338345</v>
+        <v>246.3610618592472</v>
       </c>
       <c r="E380" t="n">
-        <v>148.4227365720444</v>
+        <v>142.0464140914148</v>
       </c>
       <c r="F380" t="n">
-        <v>179.8115074108693</v>
+        <v>183.1304908079212</v>
       </c>
     </row>
     <row r="381">
@@ -7373,16 +7373,16 @@
         <v>8</v>
       </c>
       <c r="C381" t="n">
-        <v>189.6940758315086</v>
+        <v>168.8348810483776</v>
       </c>
       <c r="D381" t="n">
-        <v>241.1900050886775</v>
+        <v>217.3774075228652</v>
       </c>
       <c r="E381" t="n">
-        <v>151.3867519872929</v>
+        <v>140.0743829865182</v>
       </c>
       <c r="F381" t="n">
-        <v>190.2918817887551</v>
+        <v>185.8645928743413</v>
       </c>
     </row>
     <row r="382">
@@ -7391,16 +7391,16 @@
         <v>9</v>
       </c>
       <c r="C382" t="n">
-        <v>93.81726494277399</v>
+        <v>83.50090374444035</v>
       </c>
       <c r="D382" t="n">
-        <v>162.0796834195912</v>
+        <v>146.0776178553654</v>
       </c>
       <c r="E382" t="n">
-        <v>89.92041306006644</v>
+        <v>84.77564418960523</v>
       </c>
       <c r="F382" t="n">
-        <v>128.2067071476515</v>
+        <v>126.1550665354484</v>
       </c>
     </row>
     <row r="383">
@@ -7409,16 +7409,16 @@
         <v>10</v>
       </c>
       <c r="C383" t="n">
-        <v>150.6809304778572</v>
+        <v>134.1117104578666</v>
       </c>
       <c r="D383" t="n">
-        <v>200.6700842337797</v>
+        <v>180.8580030590238</v>
       </c>
       <c r="E383" t="n">
-        <v>155.1126806538182</v>
+        <v>159.266434541353</v>
       </c>
       <c r="F383" t="n">
-        <v>156.0561800308905</v>
+        <v>156.0442830630199</v>
       </c>
     </row>
     <row r="384">
@@ -7427,16 +7427,16 @@
         <v>11</v>
       </c>
       <c r="C384" t="n">
-        <v>371.4790984176947</v>
+        <v>330.6304064499009</v>
       </c>
       <c r="D384" t="n">
-        <v>142.7844830124971</v>
+        <v>128.6874252535362</v>
       </c>
       <c r="E384" t="n">
-        <v>161.2759769671892</v>
+        <v>160.0202741443818</v>
       </c>
       <c r="F384" t="n">
-        <v>70.16234311875085</v>
+        <v>71.12751581496465</v>
       </c>
     </row>
     <row r="385">
@@ -7445,16 +7445,16 @@
         <v>12</v>
       </c>
       <c r="C385" t="n">
-        <v>259.204254247227</v>
+        <v>230.7015611385524</v>
       </c>
       <c r="D385" t="n">
-        <v>150.5025631753348</v>
+        <v>135.6435022942679</v>
       </c>
       <c r="E385" t="n">
-        <v>131.8657335499097</v>
+        <v>134.7738501902781</v>
       </c>
       <c r="F385" t="n">
-        <v>81.07981746393193</v>
+        <v>84.10630251853084</v>
       </c>
     </row>
     <row r="386">
@@ -7465,16 +7465,16 @@
         <v>1</v>
       </c>
       <c r="C386" t="n">
-        <v>169.0158630431419</v>
+        <v>150.4304918700992</v>
       </c>
       <c r="D386" t="n">
-        <v>262.4147255364812</v>
+        <v>236.5066193848774</v>
       </c>
       <c r="E386" t="n">
-        <v>77.72707003899076</v>
+        <v>79.4831005139653</v>
       </c>
       <c r="F386" t="n">
-        <v>146.7934820974382</v>
+        <v>153.0068236387371</v>
       </c>
     </row>
     <row r="387">
@@ -7483,16 +7483,16 @@
         <v>2</v>
       </c>
       <c r="C387" t="n">
-        <v>239.8612355276527</v>
+        <v>213.4855450330383</v>
       </c>
       <c r="D387" t="n">
-        <v>200.6700842337797</v>
+        <v>180.8580030590238</v>
       </c>
       <c r="E387" t="n">
-        <v>141.5271926571322</v>
+        <v>117.0559209313936</v>
       </c>
       <c r="F387" t="n">
-        <v>129.3243866339106</v>
+        <v>111.9888247582662</v>
       </c>
     </row>
     <row r="388">
@@ -7501,16 +7501,16 @@
         <v>3</v>
       </c>
       <c r="C388" t="n">
-        <v>24.33700279887114</v>
+        <v>21.66085026435463</v>
       </c>
       <c r="D388" t="n">
-        <v>57.88560122128259</v>
+        <v>52.17057780548766</v>
       </c>
       <c r="E388" t="n">
-        <v>11.75290050375865</v>
+        <v>11.86740989882687</v>
       </c>
       <c r="F388" t="n">
-        <v>28.71338585037142</v>
+        <v>29.8633901314054</v>
       </c>
     </row>
     <row r="389">
@@ -7519,16 +7519,16 @@
         <v>4</v>
       </c>
       <c r="C389" t="n">
-        <v>117.7731530008047</v>
+        <v>104.8225475172189</v>
       </c>
       <c r="D389" t="n">
-        <v>115.7712024425652</v>
+        <v>104.3411556109753</v>
       </c>
       <c r="E389" t="n">
-        <v>50.83409166597381</v>
+        <v>50.92216196070793</v>
       </c>
       <c r="F389" t="n">
-        <v>50.18208939113276</v>
+        <v>51.86981082025477</v>
       </c>
     </row>
     <row r="390">
@@ -7537,16 +7537,16 @@
         <v>5</v>
       </c>
       <c r="C390" t="n">
-        <v>57.96494986303774</v>
+        <v>51.59099129586832</v>
       </c>
       <c r="D390" t="n">
-        <v>169.7977635824289</v>
+        <v>153.0336948960971</v>
       </c>
       <c r="E390" t="n">
-        <v>63.48610365173024</v>
+        <v>60.35362272824947</v>
       </c>
       <c r="F390" t="n">
-        <v>163.2940000009451</v>
+        <v>160.5177920369447</v>
       </c>
     </row>
     <row r="391">
@@ -7555,16 +7555,16 @@
         <v>6</v>
       </c>
       <c r="C391" t="n">
-        <v>68.86879125232646</v>
+        <v>61.29582132738769</v>
       </c>
       <c r="D391" t="n">
-        <v>113.50117886526</v>
+        <v>102.2952505989954</v>
       </c>
       <c r="E391" t="n">
-        <v>38.06931902638872</v>
+        <v>39.27915357373235</v>
       </c>
       <c r="F391" t="n">
-        <v>65.07898826364044</v>
+        <v>68.25146705903066</v>
       </c>
     </row>
     <row r="392">
@@ -7573,16 +7573,16 @@
         <v>7</v>
       </c>
       <c r="C392" t="n">
-        <v>177.9427243963275</v>
+        <v>158.3757351155401</v>
       </c>
       <c r="D392" t="n">
-        <v>314.019928193886</v>
+        <v>283.0168599905539</v>
       </c>
       <c r="E392" t="n">
-        <v>121.2155175954483</v>
+        <v>118.5938875208309</v>
       </c>
       <c r="F392" t="n">
-        <v>227.6023534243907</v>
+        <v>228.9197031238559</v>
       </c>
     </row>
     <row r="393">
@@ -7591,16 +7591,16 @@
         <v>8</v>
       </c>
       <c r="C393" t="n">
-        <v>53.65363752156011</v>
+        <v>47.75376072793895</v>
       </c>
       <c r="D393" t="n">
-        <v>87.017570463366</v>
+        <v>78.42635879256315</v>
       </c>
       <c r="E393" t="n">
-        <v>57.51235134685226</v>
+        <v>54.95739501441348</v>
       </c>
       <c r="F393" t="n">
-        <v>80.65259157823385</v>
+        <v>79.54858757043822</v>
       </c>
     </row>
     <row r="394">
@@ -7609,16 +7609,16 @@
         <v>9</v>
       </c>
       <c r="C394" t="n">
-        <v>45.04935533917808</v>
+        <v>40.0956251093049</v>
       </c>
       <c r="D394" t="n">
-        <v>45.40047154610401</v>
+        <v>40.91810023959817</v>
       </c>
       <c r="E394" t="n">
-        <v>21.93555276682968</v>
+        <v>19.86484583514211</v>
       </c>
       <c r="F394" t="n">
-        <v>21.34000253468422</v>
+        <v>20.4995044078377</v>
       </c>
     </row>
     <row r="395">
@@ -7627,16 +7627,16 @@
         <v>10</v>
       </c>
       <c r="C395" t="n">
-        <v>81.7579578357465</v>
+        <v>72.76766565033509</v>
       </c>
       <c r="D395" t="n">
-        <v>132.41804200947</v>
+        <v>119.3444590321613</v>
       </c>
       <c r="E395" t="n">
-        <v>79.61085485884935</v>
+        <v>66.46767893010221</v>
       </c>
       <c r="F395" t="n">
-        <v>113.3180717690457</v>
+        <v>104.7575853977311</v>
       </c>
     </row>
     <row r="396">
@@ -7645,16 +7645,16 @@
         <v>11</v>
       </c>
       <c r="C396" t="n">
-        <v>56.83105705266981</v>
+        <v>50.58178393437896</v>
       </c>
       <c r="D396" t="n">
-        <v>124.851296751786</v>
+        <v>112.5247756588949</v>
       </c>
       <c r="E396" t="n">
-        <v>38.31941137449325</v>
+        <v>37.28024550628618</v>
       </c>
       <c r="F396" t="n">
-        <v>74.67759954043014</v>
+        <v>76.72620143564905</v>
       </c>
     </row>
     <row r="397">
@@ -7663,16 +7663,16 @@
         <v>12</v>
       </c>
       <c r="C397" t="n">
-        <v>254.8260091270038</v>
+        <v>226.8047578734357</v>
       </c>
       <c r="D397" t="n">
-        <v>147.551532524838</v>
+        <v>132.983825778694</v>
       </c>
       <c r="E397" t="n">
-        <v>123.3581472165188</v>
+        <v>124.4866814192385</v>
       </c>
       <c r="F397" t="n">
-        <v>91.94252785978931</v>
+        <v>93.23082159995116</v>
       </c>
     </row>
     <row r="398">
@@ -7683,16 +7683,16 @@
         <v>1</v>
       </c>
       <c r="C398" t="n">
-        <v>177.8966478825379</v>
+        <v>158.3347252806748</v>
       </c>
       <c r="D398" t="n">
-        <v>234.569102988204</v>
+        <v>211.4101845712571</v>
       </c>
       <c r="E398" t="n">
-        <v>154.2344595228386</v>
+        <v>126.40753940027</v>
       </c>
       <c r="F398" t="n">
-        <v>202.1281402410646</v>
+        <v>181.9218779684279</v>
       </c>
     </row>
     <row r="399">
@@ -7701,16 +7701,16 @@
         <v>2</v>
       </c>
       <c r="C399" t="n">
-        <v>178.8738029549106</v>
+        <v>159.2044301446073</v>
       </c>
       <c r="D399" t="n">
-        <v>147.551532524838</v>
+        <v>132.983825778694</v>
       </c>
       <c r="E399" t="n">
-        <v>102.1904219955423</v>
+        <v>85.39163093610759</v>
       </c>
       <c r="F399" t="n">
-        <v>96.71213887477427</v>
+        <v>79.71321880659646</v>
       </c>
     </row>
     <row r="400">
@@ -7719,16 +7719,16 @@
         <v>3</v>
       </c>
       <c r="C400" t="n">
-        <v>84.27219638234703</v>
+        <v>75.00543277132621</v>
       </c>
       <c r="D400" t="n">
-        <v>100.3350421168898</v>
+        <v>90.42900152951194</v>
       </c>
       <c r="E400" t="n">
-        <v>46.4115055730393</v>
+        <v>45.27486539147894</v>
       </c>
       <c r="F400" t="n">
-        <v>56.57390176757679</v>
+        <v>57.32012562328645</v>
       </c>
     </row>
     <row r="401">
@@ -7737,16 +7737,16 @@
         <v>4</v>
       </c>
       <c r="C401" t="n">
-        <v>94.14788861755861</v>
+        <v>83.79517128315686</v>
       </c>
       <c r="D401" t="n">
-        <v>94.58431572104999</v>
+        <v>85.24604216582951</v>
       </c>
       <c r="E401" t="n">
-        <v>77.28952667458543</v>
+        <v>66.30143136794261</v>
       </c>
       <c r="F401" t="n">
-        <v>63.77604989617677</v>
+        <v>63.46762249173928</v>
       </c>
     </row>
     <row r="402">
@@ -7755,16 +7755,16 @@
         <v>5</v>
       </c>
       <c r="C402" t="n">
-        <v>54.68265490173363</v>
+        <v>48.66962500159515</v>
       </c>
       <c r="D402" t="n">
-        <v>79.45082520568201</v>
+        <v>71.60667541929679</v>
       </c>
       <c r="E402" t="n">
-        <v>20.45931132521774</v>
+        <v>20.75741305523909</v>
       </c>
       <c r="F402" t="n">
-        <v>37.0179634679892</v>
+        <v>38.54814838970994</v>
       </c>
     </row>
     <row r="403">
@@ -7773,16 +7773,16 @@
         <v>6</v>
       </c>
       <c r="C403" t="n">
-        <v>98.30816704804276</v>
+        <v>87.4979759746582</v>
       </c>
       <c r="D403" t="n">
-        <v>102.151060978734</v>
+        <v>92.06572553909585</v>
       </c>
       <c r="E403" t="n">
-        <v>42.85425107592825</v>
+        <v>43.19504698268986</v>
       </c>
       <c r="F403" t="n">
-        <v>50.80647961297083</v>
+        <v>52.59735347442044</v>
       </c>
     </row>
     <row r="404">
@@ -7791,16 +7791,16 @@
         <v>7</v>
       </c>
       <c r="C404" t="n">
-        <v>29.10777137417669</v>
+        <v>25.9070142069571</v>
       </c>
       <c r="D404" t="n">
-        <v>37.83372628842</v>
+        <v>34.0984168663318</v>
       </c>
       <c r="E404" t="n">
-        <v>24.29097399774524</v>
+        <v>24.50923355082503</v>
       </c>
       <c r="F404" t="n">
-        <v>32.03950633718914</v>
+        <v>33.50172706968519</v>
       </c>
     </row>
     <row r="405">
@@ -7809,16 +7809,16 @@
         <v>8</v>
       </c>
       <c r="C405" t="n">
-        <v>210.947961118088</v>
+        <v>187.7516404592661</v>
       </c>
       <c r="D405" t="n">
-        <v>329.153418709254</v>
+        <v>296.6562267370867</v>
       </c>
       <c r="E405" t="n">
-        <v>279.344949987667</v>
+        <v>268.6679595134733</v>
       </c>
       <c r="F405" t="n">
-        <v>365.126421938564</v>
+        <v>362.644878816989</v>
       </c>
     </row>
     <row r="406">
@@ -7827,16 +7827,16 @@
         <v>9</v>
       </c>
       <c r="C406" t="n">
-        <v>176.3510556005031</v>
+        <v>156.9590898637921</v>
       </c>
       <c r="D406" t="n">
-        <v>162.685023040206</v>
+        <v>146.6231925252267</v>
       </c>
       <c r="E406" t="n">
-        <v>117.377430203953</v>
+        <v>110.4166189790107</v>
       </c>
       <c r="F406" t="n">
-        <v>103.2282678309656</v>
+        <v>100.7191353764168</v>
       </c>
     </row>
     <row r="407">
@@ -7845,16 +7845,16 @@
         <v>10</v>
       </c>
       <c r="C407" t="n">
-        <v>118.2100085881741</v>
+        <v>105.2113654642503</v>
       </c>
       <c r="D407" t="n">
-        <v>109.717806236418</v>
+        <v>98.88540891236221</v>
       </c>
       <c r="E407" t="n">
-        <v>119.8335769845978</v>
+        <v>112.4920264046213</v>
       </c>
       <c r="F407" t="n">
-        <v>90.83868967690908</v>
+        <v>88.18439383979016</v>
       </c>
     </row>
     <row r="408">
@@ -7863,16 +7863,16 @@
         <v>11</v>
       </c>
       <c r="C408" t="n">
-        <v>304.9211896710232</v>
+        <v>271.3913576982978</v>
       </c>
       <c r="D408" t="n">
-        <v>128.634669380628</v>
+        <v>115.9346173455281</v>
       </c>
       <c r="E408" t="n">
-        <v>220.6009305310651</v>
+        <v>166.8427937076901</v>
       </c>
       <c r="F408" t="n">
-        <v>159.8251027396657</v>
+        <v>130.1354675872023</v>
       </c>
     </row>
     <row r="409">
@@ -7881,16 +7881,16 @@
         <v>12</v>
       </c>
       <c r="C409" t="n">
-        <v>71.08710691459351</v>
+        <v>63.27020592176625</v>
       </c>
       <c r="D409" t="n">
-        <v>98.36768834989199</v>
+        <v>88.65588385246268</v>
       </c>
       <c r="E409" t="n">
-        <v>41.23033077339282</v>
+        <v>38.65913996238672</v>
       </c>
       <c r="F409" t="n">
-        <v>63.67974875343463</v>
+        <v>62.25210507173686</v>
       </c>
     </row>
     <row r="410">
@@ -7901,16 +7901,16 @@
         <v>1</v>
       </c>
       <c r="C410" t="n">
-        <v>132.5600316190678</v>
+        <v>117.9834271158456</v>
       </c>
       <c r="D410" t="n">
-        <v>144.7140030532065</v>
+        <v>130.4264445137191</v>
       </c>
       <c r="E410" t="n">
-        <v>64.51048331741455</v>
+        <v>63.36427405895672</v>
       </c>
       <c r="F410" t="n">
-        <v>99.53586100432628</v>
+        <v>97.86524417679142</v>
       </c>
     </row>
     <row r="411">
@@ -7919,16 +7919,16 @@
         <v>2</v>
       </c>
       <c r="C411" t="n">
-        <v>154.7055442604931</v>
+        <v>137.6937684967298</v>
       </c>
       <c r="D411" t="n">
-        <v>137.292772127401</v>
+        <v>123.737908897631</v>
       </c>
       <c r="E411" t="n">
-        <v>76.72124896677306</v>
+        <v>76.2523126106819</v>
       </c>
       <c r="F411" t="n">
-        <v>67.66800486450047</v>
+        <v>68.90811843454287</v>
       </c>
     </row>
     <row r="412">
@@ -7937,16 +7937,16 @@
         <v>3</v>
       </c>
       <c r="C412" t="n">
-        <v>88.7865744202183</v>
+        <v>79.0233994668618</v>
       </c>
       <c r="D412" t="n">
-        <v>166.9776958306228</v>
+        <v>150.4920513619836</v>
       </c>
       <c r="E412" t="n">
-        <v>40.10549525961599</v>
+        <v>39.32202888490965</v>
       </c>
       <c r="F412" t="n">
-        <v>83.0789618328551</v>
+        <v>85.80506960696326</v>
       </c>
     </row>
     <row r="413">
@@ -7955,16 +7955,16 @@
         <v>4</v>
       </c>
       <c r="C413" t="n">
-        <v>302.1586898620639</v>
+        <v>268.9326286916203</v>
       </c>
       <c r="D413" t="n">
-        <v>367.3509308273704</v>
+        <v>331.082512996364</v>
       </c>
       <c r="E413" t="n">
-        <v>200.1549178484207</v>
+        <v>169.0558004839326</v>
       </c>
       <c r="F413" t="n">
-        <v>235.440302823101</v>
+        <v>224.3062449215205</v>
       </c>
     </row>
     <row r="414">
@@ -7973,16 +7973,16 @@
         <v>5</v>
       </c>
       <c r="C414" t="n">
-        <v>163.1548996507608</v>
+        <v>145.2140134279338</v>
       </c>
       <c r="D414" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E414" t="n">
-        <v>192.5377338570793</v>
+        <v>180.3369585077884</v>
       </c>
       <c r="F414" t="n">
-        <v>188.3801896814807</v>
+        <v>182.9158719867482</v>
       </c>
     </row>
     <row r="415">
@@ -7991,16 +7991,16 @@
         <v>6</v>
       </c>
       <c r="C415" t="n">
-        <v>210.8628192910617</v>
+        <v>187.675861022427</v>
       </c>
       <c r="D415" t="n">
-        <v>204.0838504596502</v>
+        <v>183.9347294424244</v>
       </c>
       <c r="E415" t="n">
-        <v>112.4585788496867</v>
+        <v>107.3906336650093</v>
       </c>
       <c r="F415" t="n">
-        <v>151.1650445751161</v>
+        <v>142.004716030202</v>
       </c>
     </row>
     <row r="416">
@@ -8009,16 +8009,16 @@
         <v>7</v>
       </c>
       <c r="C416" t="n">
-        <v>73.23586468203629</v>
+        <v>65.18268136665161</v>
       </c>
       <c r="D416" t="n">
-        <v>118.7396948128874</v>
+        <v>107.0165698574106</v>
       </c>
       <c r="E416" t="n">
-        <v>83.04617298873382</v>
+        <v>77.07329493108514</v>
       </c>
       <c r="F416" t="n">
-        <v>134.4833659064076</v>
+        <v>123.5010185754836</v>
       </c>
     </row>
     <row r="417">
@@ -8027,16 +8027,16 @@
         <v>8</v>
       </c>
       <c r="C417" t="n">
-        <v>113.3217652759415</v>
+        <v>100.8606445756898</v>
       </c>
       <c r="D417" t="n">
-        <v>185.5307731451365</v>
+        <v>167.213390402204</v>
       </c>
       <c r="E417" t="n">
-        <v>69.98413001233324</v>
+        <v>69.6814959484164</v>
       </c>
       <c r="F417" t="n">
-        <v>104.7710279634256</v>
+        <v>108.060454185771</v>
       </c>
     </row>
     <row r="418">
@@ -8045,16 +8045,16 @@
         <v>9</v>
       </c>
       <c r="C418" t="n">
-        <v>170.6508573625977</v>
+        <v>151.8856984717291</v>
       </c>
       <c r="D418" t="n">
-        <v>241.1900050886775</v>
+        <v>217.3774075228652</v>
       </c>
       <c r="E418" t="n">
-        <v>138.3639201305753</v>
+        <v>125.4075264515475</v>
       </c>
       <c r="F418" t="n">
-        <v>189.441747178656</v>
+        <v>178.3916591828612</v>
       </c>
     </row>
     <row r="419">
@@ -8063,16 +8063,16 @@
         <v>10</v>
       </c>
       <c r="C419" t="n">
-        <v>58.06828453276186</v>
+        <v>51.68296304877926</v>
       </c>
       <c r="D419" t="n">
-        <v>181.601886184416</v>
+        <v>163.6724009583926</v>
       </c>
       <c r="E419" t="n">
-        <v>33.78338895540224</v>
+        <v>34.56383377271182</v>
       </c>
       <c r="F419" t="n">
-        <v>102.7614890908016</v>
+        <v>107.510293905212</v>
       </c>
     </row>
     <row r="420">
@@ -8081,16 +8081,16 @@
         <v>11</v>
       </c>
       <c r="C420" t="n">
-        <v>96.57015595805312</v>
+        <v>85.95108056238502</v>
       </c>
       <c r="D420" t="n">
-        <v>75.66745257683999</v>
+        <v>68.19683373266361</v>
       </c>
       <c r="E420" t="n">
-        <v>41.84846684433961</v>
+        <v>42.28301178905178</v>
       </c>
       <c r="F420" t="n">
-        <v>57.92500766511038</v>
+        <v>57.71189379793853</v>
       </c>
     </row>
     <row r="421">
@@ -8099,16 +8099,16 @@
         <v>12</v>
       </c>
       <c r="C421" t="n">
-        <v>31.28665841714608</v>
+        <v>27.84630584326704</v>
       </c>
       <c r="D421" t="n">
-        <v>77.92292472095734</v>
+        <v>70.22962396892568</v>
       </c>
       <c r="E421" t="n">
-        <v>17.28391620885645</v>
+        <v>18.12432336988751</v>
       </c>
       <c r="F421" t="n">
-        <v>41.70781939037328</v>
+        <v>44.02197484387223</v>
       </c>
     </row>
     <row r="422">
@@ -8119,16 +8119,16 @@
         <v>1</v>
       </c>
       <c r="C422" t="n">
-        <v>76.03866936459269</v>
+        <v>67.67728323076868</v>
       </c>
       <c r="D422" t="n">
-        <v>159.5564649048174</v>
+        <v>143.8035157458955</v>
       </c>
       <c r="E422" t="n">
-        <v>104.3198221222594</v>
+        <v>97.13560131200272</v>
       </c>
       <c r="F422" t="n">
-        <v>143.1625069266808</v>
+        <v>142.5659470283389</v>
       </c>
     </row>
     <row r="423">
@@ -8137,16 +8137,16 @@
         <v>2</v>
       </c>
       <c r="C423" t="n">
-        <v>21.46996584766075</v>
+        <v>19.10907925887073</v>
       </c>
       <c r="D423" t="n">
-        <v>55.65923194354097</v>
+        <v>50.16401712066121</v>
       </c>
       <c r="E423" t="n">
-        <v>9.041940070711959</v>
+        <v>9.06119544179287</v>
       </c>
       <c r="F423" t="n">
-        <v>27.60902485612637</v>
+        <v>28.71479820327442</v>
       </c>
     </row>
     <row r="424">
@@ -8155,16 +8155,16 @@
         <v>3</v>
       </c>
       <c r="C424" t="n">
-        <v>136.2998976267087</v>
+        <v>121.3120488968324</v>
       </c>
       <c r="D424" t="n">
-        <v>204.0838504596502</v>
+        <v>183.9347294424244</v>
       </c>
       <c r="E424" t="n">
-        <v>93.99153771975796</v>
+        <v>94.84814958357411</v>
       </c>
       <c r="F424" t="n">
-        <v>120.653320531313</v>
+        <v>124.8535805966123</v>
       </c>
     </row>
     <row r="425">
@@ -8173,16 +8173,16 @@
         <v>4</v>
       </c>
       <c r="C425" t="n">
-        <v>82.06672720784246</v>
+        <v>73.04248203551049</v>
       </c>
       <c r="D425" t="n">
-        <v>174.3989267564284</v>
+        <v>157.1805869780718</v>
       </c>
       <c r="E425" t="n">
-        <v>51.08070162254802</v>
+        <v>47.2179783587576</v>
       </c>
       <c r="F425" t="n">
-        <v>114.4964461728413</v>
+        <v>112.4857304786015</v>
       </c>
     </row>
     <row r="426">
@@ -8191,16 +8191,16 @@
         <v>5</v>
       </c>
       <c r="C426" t="n">
-        <v>78.40690027895555</v>
+        <v>69.78509805297057</v>
       </c>
       <c r="D426" t="n">
-        <v>178.1095422193311</v>
+        <v>160.5248547861159</v>
       </c>
       <c r="E426" t="n">
-        <v>41.34467927637294</v>
+        <v>40.29046991269438</v>
       </c>
       <c r="F426" t="n">
-        <v>98.51595152528998</v>
+        <v>101.1787895301322</v>
       </c>
     </row>
     <row r="427">
@@ -8209,16 +8209,16 @@
         <v>6</v>
       </c>
       <c r="C427" t="n">
-        <v>58.77698825498127</v>
+        <v>52.31373608749944</v>
       </c>
       <c r="D427" t="n">
-        <v>141.0033875903038</v>
+        <v>127.0821767056751</v>
       </c>
       <c r="E427" t="n">
-        <v>44.9159909938569</v>
+        <v>45.65956128702111</v>
       </c>
       <c r="F427" t="n">
-        <v>89.89246798334563</v>
+        <v>93.6093115244975</v>
       </c>
     </row>
     <row r="428">
@@ -8227,16 +8227,16 @@
         <v>7</v>
       </c>
       <c r="C428" t="n">
-        <v>83.51853364763527</v>
+        <v>74.33464451603733</v>
       </c>
       <c r="D428" t="n">
-        <v>118.7396948128874</v>
+        <v>107.0165698574106</v>
       </c>
       <c r="E428" t="n">
-        <v>108.4629887162815</v>
+        <v>60.72788841426705</v>
       </c>
       <c r="F428" t="n">
-        <v>122.3924530265788</v>
+        <v>89.73350494411791</v>
       </c>
     </row>
     <row r="429">
@@ -8245,16 +8245,16 @@
         <v>8</v>
       </c>
       <c r="C429" t="n">
-        <v>87.46909763948783</v>
+        <v>77.85079544860979</v>
       </c>
       <c r="D429" t="n">
-        <v>207.7944659225529</v>
+        <v>187.2789972504685</v>
       </c>
       <c r="E429" t="n">
-        <v>113.9631869730037</v>
+        <v>81.16894670062952</v>
       </c>
       <c r="F429" t="n">
-        <v>176.4400117697667</v>
+        <v>160.5221780592152</v>
       </c>
     </row>
     <row r="430">
@@ -8263,16 +8263,16 @@
         <v>9</v>
       </c>
       <c r="C430" t="n">
-        <v>74.05701108175936</v>
+        <v>65.91353262867884</v>
       </c>
       <c r="D430" t="n">
-        <v>100.1866174983737</v>
+        <v>90.29523081719016</v>
       </c>
       <c r="E430" t="n">
-        <v>50.90452940917196</v>
+        <v>53.56010326196277</v>
       </c>
       <c r="F430" t="n">
-        <v>53.80524234192758</v>
+        <v>56.40722901028118</v>
       </c>
     </row>
     <row r="431">
@@ -8281,16 +8281,16 @@
         <v>10</v>
       </c>
       <c r="C431" t="n">
-        <v>23.06176635558076</v>
+        <v>20.52584173935079</v>
       </c>
       <c r="D431" t="n">
-        <v>63.08046286934643</v>
+        <v>56.85255273674937</v>
       </c>
       <c r="E431" t="n">
-        <v>18.87969079156877</v>
+        <v>16.3223873485248</v>
       </c>
       <c r="F431" t="n">
-        <v>49.83154814317498</v>
+        <v>45.73519433344931</v>
       </c>
     </row>
     <row r="432">
@@ -8299,16 +8299,16 @@
         <v>11</v>
       </c>
       <c r="C432" t="n">
-        <v>15.79017352205434</v>
+        <v>14.05384989828168</v>
       </c>
       <c r="D432" t="n">
-        <v>64.317334690314</v>
+        <v>57.96730867276407</v>
       </c>
       <c r="E432" t="n">
-        <v>17.42683197216313</v>
+        <v>17.57896286179571</v>
       </c>
       <c r="F432" t="n">
-        <v>41.14027823961578</v>
+        <v>42.75384264418892</v>
       </c>
     </row>
     <row r="433">
@@ -8317,16 +8317,16 @@
         <v>12</v>
       </c>
       <c r="C433" t="n">
-        <v>17.3345782306304</v>
+        <v>15.42842833000138</v>
       </c>
       <c r="D433" t="n">
-        <v>52.967216803788</v>
+        <v>47.73778361286453</v>
       </c>
       <c r="E433" t="n">
-        <v>12.23372619271078</v>
+        <v>12.84416983174211</v>
       </c>
       <c r="F433" t="n">
-        <v>33.30458547312559</v>
+        <v>35.47404496468805</v>
       </c>
     </row>
     <row r="434">
@@ -8337,16 +8337,16 @@
         <v>1</v>
       </c>
       <c r="C434" t="n">
-        <v>19.99297677989879</v>
+        <v>17.79450328978859</v>
       </c>
       <c r="D434" t="n">
-        <v>111.3184638870819</v>
+        <v>100.3280342413224</v>
       </c>
       <c r="E434" t="n">
-        <v>12.54280231550221</v>
+        <v>12.93009487313565</v>
       </c>
       <c r="F434" t="n">
-        <v>60.33079599729632</v>
+        <v>63.15818509324271</v>
       </c>
     </row>
     <row r="435">
@@ -8355,16 +8355,16 @@
         <v>2</v>
       </c>
       <c r="C435" t="n">
-        <v>26.69643283003757</v>
+        <v>23.76083196862136</v>
       </c>
       <c r="D435" t="n">
-        <v>48.23800101773549</v>
+        <v>43.47548150457305</v>
       </c>
       <c r="E435" t="n">
-        <v>32.9727026229865</v>
+        <v>28.78509237631831</v>
       </c>
       <c r="F435" t="n">
-        <v>49.39572579404524</v>
+        <v>46.57104912529439</v>
       </c>
     </row>
     <row r="436">
@@ -8373,16 +8373,16 @@
         <v>3</v>
       </c>
       <c r="C436" t="n">
-        <v>11.59099894517201</v>
+        <v>10.31642616967235</v>
       </c>
       <c r="D436" t="n">
-        <v>74.21230925805462</v>
+        <v>66.88535616088161</v>
       </c>
       <c r="E436" t="n">
-        <v>10.45448907547515</v>
+        <v>10.83427922684781</v>
       </c>
       <c r="F436" t="n">
-        <v>50.1061385211281</v>
+        <v>52.71845232397329</v>
       </c>
     </row>
     <row r="437">
@@ -8391,16 +8391,16 @@
         <v>4</v>
       </c>
       <c r="C437" t="n">
-        <v>68.59458704229766</v>
+        <v>61.05176923993982</v>
       </c>
       <c r="D437" t="n">
-        <v>181.8201576822338</v>
+        <v>163.86912259416</v>
       </c>
       <c r="E437" t="n">
-        <v>108.7799697539032</v>
+        <v>95.4405886134772</v>
       </c>
       <c r="F437" t="n">
-        <v>172.8691621026229</v>
+        <v>161.2049115615248</v>
       </c>
     </row>
     <row r="438">
@@ -8409,16 +8409,16 @@
         <v>5</v>
       </c>
       <c r="C438" t="n">
-        <v>77.56970772471168</v>
+        <v>69.03996510830287</v>
       </c>
       <c r="D438" t="n">
-        <v>144.7140030532065</v>
+        <v>130.4264445137191</v>
       </c>
       <c r="E438" t="n">
-        <v>108.4974804309467</v>
+        <v>65.28212199085881</v>
       </c>
       <c r="F438" t="n">
-        <v>143.9184869652411</v>
+        <v>114.6985003737761</v>
       </c>
     </row>
     <row r="439">
@@ -8427,16 +8427,16 @@
         <v>6</v>
       </c>
       <c r="C439" t="n">
-        <v>66.68808849739112</v>
+        <v>59.35491363895569</v>
       </c>
       <c r="D439" t="n">
-        <v>204.0838504596502</v>
+        <v>183.9347294424244</v>
       </c>
       <c r="E439" t="n">
-        <v>43.43484697032063</v>
+        <v>40.78942198896068</v>
       </c>
       <c r="F439" t="n">
-        <v>147.7113551401316</v>
+        <v>145.38736076157</v>
       </c>
     </row>
     <row r="440">
@@ -8445,16 +8445,16 @@
         <v>7</v>
       </c>
       <c r="C440" t="n">
-        <v>83.32989701353976</v>
+        <v>74.16675079801121</v>
       </c>
       <c r="D440" t="n">
-        <v>118.7396948128874</v>
+        <v>107.0165698574106</v>
       </c>
       <c r="E440" t="n">
-        <v>64.69043894124464</v>
+        <v>67.21638869675274</v>
       </c>
       <c r="F440" t="n">
-        <v>71.35341270189036</v>
+        <v>74.49660588685632</v>
       </c>
     </row>
     <row r="441">
@@ -8463,16 +8463,16 @@
         <v>8</v>
       </c>
       <c r="C441" t="n">
-        <v>26.79148057277594</v>
+        <v>23.84542804400646</v>
       </c>
       <c r="D441" t="n">
-        <v>74.21230925805462</v>
+        <v>66.88535616088161</v>
       </c>
       <c r="E441" t="n">
-        <v>33.05122902482473</v>
+        <v>19.32734716011175</v>
       </c>
       <c r="F441" t="n">
-        <v>61.03358411310922</v>
+        <v>47.59633055489638</v>
       </c>
     </row>
     <row r="442">
@@ -8481,16 +8481,16 @@
         <v>9</v>
       </c>
       <c r="C442" t="n">
-        <v>55.76804264385687</v>
+        <v>49.63566102317082</v>
       </c>
       <c r="D442" t="n">
-        <v>133.5821566644983</v>
+        <v>120.3936410895869</v>
       </c>
       <c r="E442" t="n">
-        <v>47.79753495141185</v>
+        <v>41.34481776245587</v>
       </c>
       <c r="F442" t="n">
-        <v>89.3879106013749</v>
+        <v>91.48628137768762</v>
       </c>
     </row>
     <row r="443">
@@ -8499,16 +8499,16 @@
         <v>10</v>
       </c>
       <c r="C443" t="n">
-        <v>15.96097324024662</v>
+        <v>14.20586808850552</v>
       </c>
       <c r="D443" t="n">
-        <v>111.3184638870819</v>
+        <v>100.3280342413224</v>
       </c>
       <c r="E443" t="n">
-        <v>10.23194716118654</v>
+        <v>10.52787566890618</v>
       </c>
       <c r="F443" t="n">
-        <v>60.33079599729631</v>
+        <v>63.15818509324269</v>
       </c>
     </row>
     <row r="444">
@@ -8517,16 +8517,16 @@
         <v>11</v>
       </c>
       <c r="C444" t="n">
-        <v>72.20320794944861</v>
+        <v>64.26357793210309</v>
       </c>
       <c r="D444" t="n">
-        <v>144.7140030532065</v>
+        <v>130.4264445137191</v>
       </c>
       <c r="E444" t="n">
-        <v>38.34557644818324</v>
+        <v>38.0726330114673</v>
       </c>
       <c r="F444" t="n">
-        <v>82.27254610567863</v>
+        <v>84.58922345774597</v>
       </c>
     </row>
     <row r="445">
@@ -8535,16 +8535,16 @@
         <v>12</v>
       </c>
       <c r="C445" t="n">
-        <v>11.22891517312673</v>
+        <v>9.994157958001301</v>
       </c>
       <c r="D445" t="n">
-        <v>77.92292472095733</v>
+        <v>70.22962396892568</v>
       </c>
       <c r="E445" t="n">
-        <v>7.573770326168638</v>
+        <v>7.759203643531963</v>
       </c>
       <c r="F445" t="n">
-        <v>43.32046021770184</v>
+        <v>45.25372040112087</v>
       </c>
     </row>
     <row r="446">
@@ -8555,16 +8555,16 @@
         <v>1</v>
       </c>
       <c r="C446" t="n">
-        <v>41.2354143666218</v>
+        <v>36.70107381610043</v>
       </c>
       <c r="D446" t="n">
-        <v>152.135233979012</v>
+        <v>137.1149801298073</v>
       </c>
       <c r="E446" t="n">
-        <v>69.66562702316455</v>
+        <v>68.83329232938527</v>
       </c>
       <c r="F446" t="n">
-        <v>130.2976639317918</v>
+        <v>133.418726587389</v>
       </c>
     </row>
     <row r="447">
@@ -8573,16 +8573,16 @@
         <v>2</v>
       </c>
       <c r="C447" t="n">
-        <v>161.5485501605109</v>
+        <v>143.7843018045231</v>
       </c>
       <c r="D447" t="n">
-        <v>148.4246185161092</v>
+        <v>133.7707123217632</v>
       </c>
       <c r="E447" t="n">
-        <v>78.94805635858781</v>
+        <v>71.78531886707603</v>
       </c>
       <c r="F447" t="n">
-        <v>99.17940222403182</v>
+        <v>99.34375750684073</v>
       </c>
     </row>
     <row r="448">
@@ -8591,16 +8591,16 @@
         <v>3</v>
       </c>
       <c r="C448" t="n">
-        <v>40.756970582089</v>
+        <v>36.27524080525998</v>
       </c>
       <c r="D448" t="n">
-        <v>45.400471546104</v>
+        <v>40.91810023959815</v>
       </c>
       <c r="E448" t="n">
-        <v>53.39760639612837</v>
+        <v>51.80476508582657</v>
       </c>
       <c r="F448" t="n">
-        <v>38.94812561825417</v>
+        <v>39.42544316170532</v>
       </c>
     </row>
     <row r="449">
@@ -8609,16 +8609,16 @@
         <v>4</v>
       </c>
       <c r="C449" t="n">
-        <v>45.61226728051274</v>
+        <v>40.59663796507993</v>
       </c>
       <c r="D449" t="n">
-        <v>68.100707319156</v>
+        <v>61.37715035939724</v>
       </c>
       <c r="E449" t="n">
-        <v>55.9223537908108</v>
+        <v>39.67322116166441</v>
       </c>
       <c r="F449" t="n">
-        <v>70.94558735986396</v>
+        <v>56.27694420349955</v>
       </c>
     </row>
     <row r="450">
@@ -8627,16 +8627,16 @@
         <v>5</v>
       </c>
       <c r="C450" t="n">
-        <v>29.03825375881737</v>
+        <v>25.84514090770666</v>
       </c>
       <c r="D450" t="n">
-        <v>83.234197834524</v>
+        <v>75.01651710592996</v>
       </c>
       <c r="E450" t="n">
-        <v>34.39821022553937</v>
+        <v>34.52005957787335</v>
       </c>
       <c r="F450" t="n">
-        <v>63.20203513843065</v>
+        <v>65.47510925081491</v>
       </c>
     </row>
     <row r="451">
@@ -8645,16 +8645,16 @@
         <v>6</v>
       </c>
       <c r="C451" t="n">
-        <v>23.79905513033635</v>
+        <v>21.18205655279985</v>
       </c>
       <c r="D451" t="n">
-        <v>52.96721680378799</v>
+        <v>47.73778361286452</v>
       </c>
       <c r="E451" t="n">
-        <v>41.05838206377858</v>
+        <v>35.58851170864423</v>
       </c>
       <c r="F451" t="n">
-        <v>61.09355173889957</v>
+        <v>54.37812073361872</v>
       </c>
     </row>
     <row r="452">
@@ -8663,16 +8663,16 @@
         <v>7</v>
       </c>
       <c r="C452" t="n">
-        <v>25.32574112505126</v>
+        <v>22.54086466099224</v>
       </c>
       <c r="D452" t="n">
-        <v>89.05477110966554</v>
+        <v>80.26242739305793</v>
       </c>
       <c r="E452" t="n">
-        <v>13.32817312142194</v>
+        <v>13.52221695103836</v>
       </c>
       <c r="F452" t="n">
-        <v>50.48016067499779</v>
+        <v>52.67023983933338</v>
       </c>
     </row>
     <row r="453">
@@ -8681,16 +8681,16 @@
         <v>8</v>
       </c>
       <c r="C453" t="n">
-        <v>48.1384794476029</v>
+        <v>42.84506205984434</v>
       </c>
       <c r="D453" t="n">
-        <v>113.50117886526</v>
+        <v>102.2952505989954</v>
       </c>
       <c r="E453" t="n">
-        <v>43.7931723757119</v>
+        <v>46.66378693084565</v>
       </c>
       <c r="F453" t="n">
-        <v>67.96930353424958</v>
+        <v>71.46494772324851</v>
       </c>
     </row>
     <row r="454">
@@ -8699,16 +8699,16 @@
         <v>9</v>
       </c>
       <c r="C454" t="n">
-        <v>55.48874914257315</v>
+        <v>49.38707927458366</v>
       </c>
       <c r="D454" t="n">
-        <v>90.80094309220802</v>
+        <v>81.83620047919632</v>
       </c>
       <c r="E454" t="n">
-        <v>30.23522553720373</v>
+        <v>30.51250029459247</v>
       </c>
       <c r="F454" t="n">
-        <v>57.12739461535597</v>
+        <v>59.10410791318835</v>
       </c>
     </row>
     <row r="455">
@@ -8717,16 +8717,16 @@
         <v>10</v>
       </c>
       <c r="C455" t="n">
-        <v>146.0477474946068</v>
+        <v>129.9880028806871</v>
       </c>
       <c r="D455" t="n">
-        <v>136.201414638312</v>
+        <v>122.7543007187945</v>
       </c>
       <c r="E455" t="n">
-        <v>85.93893420013852</v>
+        <v>88.78710594119565</v>
       </c>
       <c r="F455" t="n">
-        <v>104.6124921753377</v>
+        <v>109.596632147041</v>
       </c>
     </row>
     <row r="456">
@@ -8735,16 +8735,16 @@
         <v>11</v>
       </c>
       <c r="C456" t="n">
-        <v>25.33720831986426</v>
+        <v>22.5510708968155</v>
       </c>
       <c r="D456" t="n">
-        <v>68.100707319156</v>
+        <v>61.37715035939724</v>
       </c>
       <c r="E456" t="n">
-        <v>11.87243252375624</v>
+        <v>12.03371761953516</v>
       </c>
       <c r="F456" t="n">
-        <v>35.27201862213865</v>
+        <v>36.94408947514628</v>
       </c>
     </row>
     <row r="457">
@@ -8753,16 +8753,16 @@
         <v>12</v>
       </c>
       <c r="C457" t="n">
-        <v>106.3997791782823</v>
+        <v>94.69981591357146</v>
       </c>
       <c r="D457" t="n">
-        <v>456.4057019370359</v>
+        <v>411.3449403894219</v>
       </c>
       <c r="E457" t="n">
-        <v>106.3936588462005</v>
+        <v>67.54486918687043</v>
       </c>
       <c r="F457" t="n">
-        <v>280.7641088388843</v>
+        <v>241.8059799337439</v>
       </c>
     </row>
     <row r="458">
@@ -8773,16 +8773,16 @@
         <v>1</v>
       </c>
       <c r="C458" t="n">
-        <v>104.6549022806233</v>
+        <v>93.14680967355589</v>
       </c>
       <c r="D458" t="n">
-        <v>278.2961597177048</v>
+        <v>250.820085603306</v>
       </c>
       <c r="E458" t="n">
-        <v>104.1211636903284</v>
+        <v>78.32857292156956</v>
       </c>
       <c r="F458" t="n">
-        <v>165.870988293895</v>
+        <v>156.4946566680304</v>
       </c>
     </row>
     <row r="459">
@@ -8791,16 +8791,16 @@
         <v>2</v>
       </c>
       <c r="C459" t="n">
-        <v>138.3889916777405</v>
+        <v>123.1714213841319</v>
       </c>
       <c r="D459" t="n">
-        <v>222.6369277741638</v>
+        <v>200.6560684826448</v>
       </c>
       <c r="E459" t="n">
-        <v>64.845862520401</v>
+        <v>64.82995157373506</v>
       </c>
       <c r="F459" t="n">
-        <v>103.4540470770167</v>
+        <v>108.6649821798622</v>
       </c>
     </row>
     <row r="460">
@@ -8809,16 +8809,16 @@
         <v>3</v>
       </c>
       <c r="C460" t="n">
-        <v>99.89292784538871</v>
+        <v>88.90847284725264</v>
       </c>
       <c r="D460" t="n">
-        <v>100.1866174983737</v>
+        <v>90.29523081719017</v>
       </c>
       <c r="E460" t="n">
-        <v>49.00297762653971</v>
+        <v>49.01281605707014</v>
       </c>
       <c r="F460" t="n">
-        <v>56.23778482358051</v>
+        <v>58.51920739881686</v>
       </c>
     </row>
     <row r="461">
@@ -8827,16 +8827,16 @@
         <v>4</v>
       </c>
       <c r="C461" t="n">
-        <v>21.83937942890679</v>
+        <v>19.43787127714508</v>
       </c>
       <c r="D461" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E461" t="n">
-        <v>10.69186358087563</v>
+        <v>10.8210509677481</v>
       </c>
       <c r="F461" t="n">
-        <v>36.14928631399066</v>
+        <v>37.72361312436742</v>
       </c>
     </row>
     <row r="462">
@@ -8845,16 +8845,16 @@
         <v>5</v>
       </c>
       <c r="C462" t="n">
-        <v>77.73585426638489</v>
+        <v>69.18784179594867</v>
       </c>
       <c r="D462" t="n">
-        <v>100.1866174983737</v>
+        <v>90.29523081719017</v>
       </c>
       <c r="E462" t="n">
-        <v>29.41443033010066</v>
+        <v>28.48296202966387</v>
       </c>
       <c r="F462" t="n">
-        <v>43.64748014078109</v>
+        <v>44.77086712904229</v>
       </c>
     </row>
     <row r="463">
@@ -8863,16 +8863,16 @@
         <v>6</v>
       </c>
       <c r="C463" t="n">
-        <v>17.8645145386522</v>
+        <v>15.90009162858299</v>
       </c>
       <c r="D463" t="n">
-        <v>111.3184638870819</v>
+        <v>100.3280342413224</v>
       </c>
       <c r="E463" t="n">
-        <v>12.53928014922988</v>
+        <v>12.90357112322332</v>
       </c>
       <c r="F463" t="n">
-        <v>64.63602029429552</v>
+        <v>67.71917512882128</v>
       </c>
     </row>
     <row r="464">
@@ -8881,16 +8881,16 @@
         <v>7</v>
       </c>
       <c r="C464" t="n">
-        <v>18.29955157648917</v>
+        <v>16.28729099795118</v>
       </c>
       <c r="D464" t="n">
-        <v>68.100707319156</v>
+        <v>61.37715035939724</v>
       </c>
       <c r="E464" t="n">
-        <v>7.974557107446373</v>
+        <v>8.109018223446061</v>
       </c>
       <c r="F464" t="n">
-        <v>31.28820683073472</v>
+        <v>32.83100710802562</v>
       </c>
     </row>
     <row r="465">
@@ -8899,16 +8899,16 @@
         <v>8</v>
       </c>
       <c r="C465" t="n">
-        <v>13.7593361906503</v>
+        <v>12.24632808837151</v>
       </c>
       <c r="D465" t="n">
-        <v>34.050353659578</v>
+        <v>30.68857517969862</v>
       </c>
       <c r="E465" t="n">
-        <v>5.961704806928617</v>
+        <v>5.962831009276871</v>
       </c>
       <c r="F465" t="n">
-        <v>17.52231817858434</v>
+        <v>18.15121800225871</v>
       </c>
     </row>
     <row r="466">
@@ -8917,16 +8917,16 @@
         <v>9</v>
       </c>
       <c r="C466" t="n">
-        <v>98.59760643993188</v>
+        <v>87.75558794849611</v>
       </c>
       <c r="D466" t="n">
-        <v>136.201414638312</v>
+        <v>122.7543007187945</v>
       </c>
       <c r="E466" t="n">
-        <v>90.38574386566067</v>
+        <v>93.91809527129179</v>
       </c>
       <c r="F466" t="n">
-        <v>84.37407524062817</v>
+        <v>87.57749391942593</v>
       </c>
     </row>
     <row r="467">
@@ -8935,16 +8935,16 @@
         <v>10</v>
       </c>
       <c r="C467" t="n">
-        <v>58.87630846410425</v>
+        <v>52.40213481908594</v>
       </c>
       <c r="D467" t="n">
-        <v>129.8715412015956</v>
+        <v>117.0493732815428</v>
       </c>
       <c r="E467" t="n">
-        <v>44.41801827444932</v>
+        <v>26.61730537182997</v>
       </c>
       <c r="F467" t="n">
-        <v>82.11899811829028</v>
+        <v>71.00894403469276</v>
       </c>
     </row>
     <row r="468">
@@ -8953,16 +8953,16 @@
         <v>11</v>
       </c>
       <c r="C468" t="n">
-        <v>71.34654448927215</v>
+        <v>63.50111514688752</v>
       </c>
       <c r="D468" t="n">
-        <v>122.4503102757901</v>
+        <v>110.3608376654547</v>
       </c>
       <c r="E468" t="n">
-        <v>39.46039699117833</v>
+        <v>35.6538562856535</v>
       </c>
       <c r="F468" t="n">
-        <v>64.48871422677784</v>
+        <v>65.27631616568267</v>
       </c>
     </row>
     <row r="469">
@@ -8971,16 +8971,16 @@
         <v>12</v>
       </c>
       <c r="C469" t="n">
-        <v>38.46191153783609</v>
+        <v>34.23255170684227</v>
       </c>
       <c r="D469" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E469" t="n">
-        <v>52.75472579338076</v>
+        <v>52.97967592909679</v>
       </c>
       <c r="F469" t="n">
-        <v>51.41677247229107</v>
+        <v>53.19198397758976</v>
       </c>
     </row>
     <row r="470">
@@ -8991,16 +8991,16 @@
         <v>1</v>
       </c>
       <c r="C470" t="n">
-        <v>68.63146691778682</v>
+        <v>61.08459371990313</v>
       </c>
       <c r="D470" t="n">
-        <v>77.92292472095734</v>
+        <v>70.22962396892568</v>
       </c>
       <c r="E470" t="n">
-        <v>53.41778844056546</v>
+        <v>42.97702438118014</v>
       </c>
       <c r="F470" t="n">
-        <v>44.42486035562371</v>
+        <v>43.02598433998768</v>
       </c>
     </row>
     <row r="471">
@@ -9009,16 +9009,16 @@
         <v>2</v>
       </c>
       <c r="C471" t="n">
-        <v>35.86838228258782</v>
+        <v>31.92421286502064</v>
       </c>
       <c r="D471" t="n">
-        <v>111.3184638870819</v>
+        <v>100.3280342413224</v>
       </c>
       <c r="E471" t="n">
-        <v>15.29917387581439</v>
+        <v>15.55453955788668</v>
       </c>
       <c r="F471" t="n">
-        <v>48.99574674314176</v>
+        <v>51.4696487731146</v>
       </c>
     </row>
     <row r="472">
@@ -9027,16 +9027,16 @@
         <v>3</v>
       </c>
       <c r="C472" t="n">
-        <v>22.03227787819984</v>
+        <v>19.60955817141444</v>
       </c>
       <c r="D472" t="n">
-        <v>122.4503102757901</v>
+        <v>110.3608376654547</v>
       </c>
       <c r="E472" t="n">
-        <v>14.00528432381445</v>
+        <v>14.4209787562007</v>
       </c>
       <c r="F472" t="n">
-        <v>64.96385742897598</v>
+        <v>68.13301538504427</v>
       </c>
     </row>
     <row r="473">
@@ -9045,16 +9045,16 @@
         <v>4</v>
       </c>
       <c r="C473" t="n">
-        <v>28.48525982834174</v>
+        <v>25.35295545561454</v>
       </c>
       <c r="D473" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E473" t="n">
-        <v>12.6373970948275</v>
+        <v>12.66106185941307</v>
       </c>
       <c r="F473" t="n">
-        <v>34.37070104260776</v>
+        <v>35.60431223519978</v>
       </c>
     </row>
     <row r="474">
@@ -9063,16 +9063,16 @@
         <v>5</v>
       </c>
       <c r="C474" t="n">
-        <v>17.10259388720414</v>
+        <v>15.22195351598428</v>
       </c>
       <c r="D474" t="n">
-        <v>100.1866174983737</v>
+        <v>90.29523081719017</v>
       </c>
       <c r="E474" t="n">
-        <v>12.49336526980025</v>
+        <v>12.84938912367982</v>
       </c>
       <c r="F474" t="n">
-        <v>62.35458314652274</v>
+        <v>65.28834255795257</v>
       </c>
     </row>
     <row r="475">
@@ -9081,16 +9081,16 @@
         <v>6</v>
       </c>
       <c r="C475" t="n">
-        <v>32.61578388714934</v>
+        <v>29.02927763425587</v>
       </c>
       <c r="D475" t="n">
-        <v>122.4503102757901</v>
+        <v>110.3608376654547</v>
       </c>
       <c r="E475" t="n">
-        <v>20.16686126658293</v>
+        <v>20.88286900664021</v>
       </c>
       <c r="F475" t="n">
-        <v>70.00007638409838</v>
+        <v>73.25910219196203</v>
       </c>
     </row>
     <row r="476">
@@ -9099,16 +9099,16 @@
         <v>7</v>
       </c>
       <c r="C476" t="n">
-        <v>124.86145737405</v>
+        <v>111.1314057166418</v>
       </c>
       <c r="D476" t="n">
-        <v>133.5821566644983</v>
+        <v>120.3936410895869</v>
       </c>
       <c r="E476" t="n">
-        <v>60.17172549826146</v>
+        <v>54.42342011706833</v>
       </c>
       <c r="F476" t="n">
-        <v>63.95801339133353</v>
+        <v>64.81855600196857</v>
       </c>
     </row>
     <row r="477">
@@ -9117,16 +9117,16 @@
         <v>8</v>
       </c>
       <c r="C477" t="n">
-        <v>65.79665561622186</v>
+        <v>58.56150475786598</v>
       </c>
       <c r="D477" t="n">
-        <v>113.50117886526</v>
+        <v>102.2952505989954</v>
       </c>
       <c r="E477" t="n">
-        <v>33.49804285614884</v>
+        <v>30.68860308372451</v>
       </c>
       <c r="F477" t="n">
-        <v>62.54150687607364</v>
+        <v>63.80491417430214</v>
       </c>
     </row>
     <row r="478">
@@ -9135,16 +9135,16 @@
         <v>9</v>
       </c>
       <c r="C478" t="n">
-        <v>11.40983965180143</v>
+        <v>10.15518756686961</v>
       </c>
       <c r="D478" t="n">
-        <v>56.75058943263</v>
+        <v>51.14762529949769</v>
       </c>
       <c r="E478" t="n">
-        <v>7.695801744764029</v>
+        <v>7.884222833052295</v>
       </c>
       <c r="F478" t="n">
-        <v>31.54991500448874</v>
+        <v>32.95789160865947</v>
       </c>
     </row>
     <row r="479">
@@ -9153,16 +9153,16 @@
         <v>10</v>
       </c>
       <c r="C479" t="n">
-        <v>48.93990647529007</v>
+        <v>43.55836233712185</v>
       </c>
       <c r="D479" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914611</v>
       </c>
       <c r="E479" t="n">
-        <v>34.51672313687006</v>
+        <v>35.51398012548365</v>
       </c>
       <c r="F479" t="n">
-        <v>53.68526282492691</v>
+        <v>56.40435631266211</v>
       </c>
     </row>
     <row r="480">
@@ -9171,16 +9171,16 @@
         <v>11</v>
       </c>
       <c r="C480" t="n">
-        <v>41.23222144753076</v>
+        <v>36.69823199770116</v>
       </c>
       <c r="D480" t="n">
-        <v>158.901650411364</v>
+        <v>143.2133508385936</v>
       </c>
       <c r="E480" t="n">
-        <v>57.92333287132708</v>
+        <v>44.79455461376094</v>
       </c>
       <c r="F480" t="n">
-        <v>125.2150696312357</v>
+        <v>113.552565537841</v>
       </c>
     </row>
     <row r="481">
@@ -9189,16 +9189,16 @@
         <v>12</v>
       </c>
       <c r="C481" t="n">
-        <v>39.32572608078563</v>
+        <v>35.00137922540055</v>
       </c>
       <c r="D481" t="n">
-        <v>113.50117886526</v>
+        <v>102.2952505989954</v>
       </c>
       <c r="E481" t="n">
-        <v>23.22000499750157</v>
+        <v>23.64524865859934</v>
       </c>
       <c r="F481" t="n">
-        <v>66.08183964455404</v>
+        <v>68.94268746712875</v>
       </c>
     </row>
     <row r="482">
@@ -9209,16 +9209,16 @@
         <v>1</v>
       </c>
       <c r="C482" t="n">
-        <v>90.08525742482982</v>
+        <v>80.17927631563535</v>
       </c>
       <c r="D482" t="n">
-        <v>158.901650411364</v>
+        <v>143.2133508385936</v>
       </c>
       <c r="E482" t="n">
-        <v>39.97438553395173</v>
+        <v>40.72768566875269</v>
       </c>
       <c r="F482" t="n">
-        <v>82.98960555071108</v>
+        <v>86.7342373993349</v>
       </c>
     </row>
     <row r="483">
@@ -9227,16 +9227,16 @@
         <v>2</v>
       </c>
       <c r="C483" t="n">
-        <v>18.7693394789069</v>
+        <v>16.70541994728704</v>
       </c>
       <c r="D483" t="n">
-        <v>56.75058943263</v>
+        <v>51.1476252994977</v>
       </c>
       <c r="E483" t="n">
-        <v>13.99612999898499</v>
+        <v>14.32284469986799</v>
       </c>
       <c r="F483" t="n">
-        <v>37.52563269159464</v>
+        <v>39.12751515934048</v>
       </c>
     </row>
     <row r="484">
@@ -9245,16 +9245,16 @@
         <v>3</v>
       </c>
       <c r="C484" t="n">
-        <v>14.97924683622556</v>
+        <v>13.33209456701627</v>
       </c>
       <c r="D484" t="n">
-        <v>26.483608401894</v>
+        <v>23.86889180643226</v>
       </c>
       <c r="E484" t="n">
-        <v>17.45674080555609</v>
+        <v>15.78696476850444</v>
       </c>
       <c r="F484" t="n">
-        <v>40.28222916624659</v>
+        <v>36.72249960504621</v>
       </c>
     </row>
     <row r="485">
@@ -9263,16 +9263,16 @@
         <v>4</v>
       </c>
       <c r="C485" t="n">
-        <v>46.10753561178613</v>
+        <v>41.03744545699044</v>
       </c>
       <c r="D485" t="n">
-        <v>56.75058943263</v>
+        <v>51.1476252994977</v>
       </c>
       <c r="E485" t="n">
-        <v>29.1818286417802</v>
+        <v>25.78814910332806</v>
       </c>
       <c r="F485" t="n">
-        <v>29.46344502797239</v>
+        <v>29.25193853813267</v>
       </c>
     </row>
     <row r="486">
@@ -9281,16 +9281,16 @@
         <v>5</v>
       </c>
       <c r="C486" t="n">
-        <v>152.7953440083853</v>
+        <v>135.9936182367414</v>
       </c>
       <c r="D486" t="n">
-        <v>68.100707319156</v>
+        <v>61.37715035939724</v>
       </c>
       <c r="E486" t="n">
-        <v>94.86056597763026</v>
+        <v>78.12059329462474</v>
       </c>
       <c r="F486" t="n">
-        <v>66.44250875039431</v>
+        <v>50.03285773396098</v>
       </c>
     </row>
     <row r="487">
@@ -9299,16 +9299,16 @@
         <v>6</v>
       </c>
       <c r="C487" t="n">
-        <v>72.27563689405898</v>
+        <v>64.32804242417616</v>
       </c>
       <c r="D487" t="n">
-        <v>79.45082520568201</v>
+        <v>71.60667541929679</v>
       </c>
       <c r="E487" t="n">
-        <v>40.43608263523781</v>
+        <v>28.0667468593289</v>
       </c>
       <c r="F487" t="n">
-        <v>46.07624674341451</v>
+        <v>35.38762666193404</v>
       </c>
     </row>
     <row r="488">
@@ -9317,16 +9317,16 @@
         <v>7</v>
       </c>
       <c r="C488" t="n">
-        <v>67.24847856507807</v>
+        <v>59.85368193208181</v>
       </c>
       <c r="D488" t="n">
-        <v>45.400471546104</v>
+        <v>40.91810023959815</v>
       </c>
       <c r="E488" t="n">
-        <v>24.8280746862383</v>
+        <v>22.99592830789107</v>
       </c>
       <c r="F488" t="n">
-        <v>15.29822436859453</v>
+        <v>15.22274674215801</v>
       </c>
     </row>
     <row r="489">
@@ -9335,16 +9335,16 @@
         <v>8</v>
       </c>
       <c r="C489" t="n">
-        <v>62.69094956284944</v>
+        <v>55.79730925100102</v>
       </c>
       <c r="D489" t="n">
-        <v>68.100707319156</v>
+        <v>61.37715035939724</v>
       </c>
       <c r="E489" t="n">
-        <v>44.18978541304094</v>
+        <v>47.38021169821609</v>
       </c>
       <c r="F489" t="n">
-        <v>38.10166009900302</v>
+        <v>40.58927513448437</v>
       </c>
     </row>
     <row r="490">
@@ -9353,16 +9353,16 @@
         <v>9</v>
       </c>
       <c r="C490" t="n">
-        <v>35.41825763676366</v>
+        <v>31.52358495557466</v>
       </c>
       <c r="D490" t="n">
-        <v>41.61709891726201</v>
+        <v>37.50825855296498</v>
       </c>
       <c r="E490" t="n">
-        <v>49.05706942777823</v>
+        <v>51.2488544341709</v>
       </c>
       <c r="F490" t="n">
-        <v>37.19073081563833</v>
+        <v>39.4215085217615</v>
       </c>
     </row>
     <row r="491">
@@ -9371,16 +9371,16 @@
         <v>10</v>
       </c>
       <c r="C491" t="n">
-        <v>101.5334240247898</v>
+        <v>90.36857631171459</v>
       </c>
       <c r="D491" t="n">
-        <v>90.80094309220802</v>
+        <v>81.83620047919632</v>
       </c>
       <c r="E491" t="n">
-        <v>70.75887713768279</v>
+        <v>51.1043575684003</v>
       </c>
       <c r="F491" t="n">
-        <v>68.33861156536901</v>
+        <v>48.80941526499907</v>
       </c>
     </row>
     <row r="492">
@@ -9389,16 +9389,16 @@
         <v>11</v>
       </c>
       <c r="C492" t="n">
-        <v>6.996217787013015</v>
+        <v>6.226897664996478</v>
       </c>
       <c r="D492" t="n">
-        <v>22.700235773052</v>
+        <v>20.45905011979908</v>
       </c>
       <c r="E492" t="n">
-        <v>4.718866057293203</v>
+        <v>4.834400982371891</v>
       </c>
       <c r="F492" t="n">
-        <v>12.61996600179549</v>
+        <v>13.18315664346378</v>
       </c>
     </row>
     <row r="493">
@@ -9427,16 +9427,16 @@
         <v>1</v>
       </c>
       <c r="C494" t="n">
-        <v>68.84240420701279</v>
+        <v>61.27233586197597</v>
       </c>
       <c r="D494" t="n">
-        <v>102.151060978734</v>
+        <v>92.06572553909585</v>
       </c>
       <c r="E494" t="n">
-        <v>41.4229803105232</v>
+        <v>43.10762276359068</v>
       </c>
       <c r="F494" t="n">
-        <v>49.69618674318723</v>
+        <v>52.41830724909321</v>
       </c>
     </row>
     <row r="495">
@@ -9445,16 +9445,16 @@
         <v>2</v>
       </c>
       <c r="C495" t="n">
-        <v>66.7785699556449</v>
+        <v>59.43544554895023</v>
       </c>
       <c r="D495" t="n">
-        <v>124.851296751786</v>
+        <v>112.5247756588949</v>
       </c>
       <c r="E495" t="n">
-        <v>26.6560570459472</v>
+        <v>27.46598833071594</v>
       </c>
       <c r="F495" t="n">
-        <v>62.66156426190396</v>
+        <v>65.75831491167253</v>
       </c>
     </row>
     <row r="496">
@@ -9463,16 +9463,16 @@
         <v>3</v>
       </c>
       <c r="C496" t="n">
-        <v>36.45964175921033</v>
+        <v>32.45045609621651</v>
       </c>
       <c r="D496" t="n">
-        <v>22.700235773052</v>
+        <v>20.45905011979908</v>
       </c>
       <c r="E496" t="n">
-        <v>31.41876220983544</v>
+        <v>29.6856014540485</v>
       </c>
       <c r="F496" t="n">
-        <v>16.40477170637862</v>
+        <v>16.11254619617742</v>
       </c>
     </row>
     <row r="497">
@@ -9481,16 +9481,16 @@
         <v>4</v>
       </c>
       <c r="C497" t="n">
-        <v>60.29055125720639</v>
+        <v>53.6608642374944</v>
       </c>
       <c r="D497" t="n">
-        <v>68.100707319156</v>
+        <v>61.37715035939724</v>
       </c>
       <c r="E497" t="n">
-        <v>62.79880929181559</v>
+        <v>64.27237990384303</v>
       </c>
       <c r="F497" t="n">
-        <v>54.1328314910381</v>
+        <v>55.53989780226941</v>
       </c>
     </row>
     <row r="498">
@@ -9499,16 +9499,16 @@
         <v>5</v>
       </c>
       <c r="C498" t="n">
-        <v>21.12423181063861</v>
+        <v>18.80136292793556</v>
       </c>
       <c r="D498" t="n">
-        <v>30.26698103073599</v>
+        <v>27.27873349306544</v>
       </c>
       <c r="E498" t="n">
-        <v>20.91409485118585</v>
+        <v>20.79582305607279</v>
       </c>
       <c r="F498" t="n">
-        <v>20.69263056651497</v>
+        <v>21.16897814258503</v>
       </c>
     </row>
     <row r="499">
@@ -9517,16 +9517,16 @@
         <v>6</v>
       </c>
       <c r="C499" t="n">
-        <v>61.42604025120318</v>
+        <v>54.67149226260717</v>
       </c>
       <c r="D499" t="n">
-        <v>81.63354018386009</v>
+        <v>73.57389177696976</v>
       </c>
       <c r="E499" t="n">
-        <v>56.96131352531132</v>
+        <v>54.30911846513325</v>
       </c>
       <c r="F499" t="n">
-        <v>70.48884527673967</v>
+        <v>71.97281887008316</v>
       </c>
     </row>
     <row r="500">
@@ -9535,16 +9535,16 @@
         <v>7</v>
       </c>
       <c r="C500" t="n">
-        <v>38.60641272808318</v>
+        <v>34.3611632154504</v>
       </c>
       <c r="D500" t="n">
-        <v>89.05477110966554</v>
+        <v>80.26242739305793</v>
       </c>
       <c r="E500" t="n">
-        <v>61.5946982639501</v>
+        <v>47.40787821225221</v>
       </c>
       <c r="F500" t="n">
-        <v>96.62972523053713</v>
+        <v>83.39816065472868</v>
       </c>
     </row>
     <row r="501">
@@ -9553,16 +9553,16 @@
         <v>8</v>
       </c>
       <c r="C501" t="n">
-        <v>55.99455931216881</v>
+        <v>49.83726940014455</v>
       </c>
       <c r="D501" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E501" t="n">
-        <v>24.06667331408277</v>
+        <v>24.67402208574337</v>
       </c>
       <c r="F501" t="n">
-        <v>37.35880342103114</v>
+        <v>38.98529307041148</v>
       </c>
     </row>
     <row r="502">
@@ -9571,16 +9571,16 @@
         <v>9</v>
       </c>
       <c r="C502" t="n">
-        <v>18.0949852928758</v>
+        <v>16.10521929113073</v>
       </c>
       <c r="D502" t="n">
-        <v>22.26369277741638</v>
+        <v>20.06560684826448</v>
       </c>
       <c r="E502" t="n">
-        <v>25.51302752954025</v>
+        <v>24.75625413406165</v>
       </c>
       <c r="F502" t="n">
-        <v>23.39064573874641</v>
+        <v>23.26880322688601</v>
       </c>
     </row>
     <row r="503">
@@ -9589,16 +9589,16 @@
         <v>10</v>
       </c>
       <c r="C503" t="n">
-        <v>33.81657639453627</v>
+        <v>30.09802824894839</v>
       </c>
       <c r="D503" t="n">
-        <v>63.08046286934643</v>
+        <v>56.85255273674937</v>
       </c>
       <c r="E503" t="n">
-        <v>26.78351604167609</v>
+        <v>24.49202806463599</v>
       </c>
       <c r="F503" t="n">
-        <v>46.76089254921807</v>
+        <v>47.71822508745051</v>
       </c>
     </row>
     <row r="504">
@@ -9607,16 +9607,16 @@
         <v>11</v>
       </c>
       <c r="C504" t="n">
-        <v>46.44514146949781</v>
+        <v>41.33792740181731</v>
       </c>
       <c r="D504" t="n">
-        <v>18.55307731451365</v>
+        <v>16.7213390402204</v>
       </c>
       <c r="E504" t="n">
-        <v>88.82410872116975</v>
+        <v>91.28515218415525</v>
       </c>
       <c r="F504" t="n">
-        <v>16.77110375614025</v>
+        <v>17.69037105247476</v>
       </c>
     </row>
     <row r="505">
@@ -9625,16 +9625,16 @@
         <v>12</v>
       </c>
       <c r="C505" t="n">
-        <v>71.37662864889232</v>
+        <v>63.52789118345402</v>
       </c>
       <c r="D505" t="n">
-        <v>185.5307731451365</v>
+        <v>167.213390402204</v>
       </c>
       <c r="E505" t="n">
-        <v>47.995705608733</v>
+        <v>48.29379150528383</v>
       </c>
       <c r="F505" t="n">
-        <v>107.7201908939304</v>
+        <v>112.2097461853489</v>
       </c>
     </row>
     <row r="506">
@@ -9645,16 +9645,16 @@
         <v>1</v>
       </c>
       <c r="C506" t="n">
-        <v>48.95335424499449</v>
+        <v>43.57033135928799</v>
       </c>
       <c r="D506" t="n">
-        <v>63.08046286934643</v>
+        <v>56.85255273674937</v>
       </c>
       <c r="E506" t="n">
-        <v>46.67550417990829</v>
+        <v>43.04946740967064</v>
       </c>
       <c r="F506" t="n">
-        <v>47.0997102709321</v>
+        <v>47.43022795549867</v>
       </c>
     </row>
     <row r="507">
@@ -9663,16 +9663,16 @@
         <v>2</v>
       </c>
       <c r="C507" t="n">
-        <v>11.65190858164139</v>
+        <v>10.37063804309502</v>
       </c>
       <c r="D507" t="n">
-        <v>33.39553916612458</v>
+        <v>30.09841027239672</v>
       </c>
       <c r="E507" t="n">
-        <v>8.166855819142766</v>
+        <v>8.363134132974592</v>
       </c>
       <c r="F507" t="n">
-        <v>20.51951153496453</v>
+        <v>21.41144391512609</v>
       </c>
     </row>
     <row r="508">
@@ -9681,16 +9681,16 @@
         <v>3</v>
       </c>
       <c r="C508" t="n">
-        <v>43.28602821531866</v>
+        <v>38.52619747219399</v>
       </c>
       <c r="D508" t="n">
-        <v>40.81677009193005</v>
+        <v>36.78694588848489</v>
       </c>
       <c r="E508" t="n">
-        <v>60.73914947849062</v>
+        <v>58.75082706414041</v>
       </c>
       <c r="F508" t="n">
-        <v>45.30897772218606</v>
+        <v>42.76775618659318</v>
       </c>
     </row>
     <row r="509">
@@ -9699,16 +9699,16 @@
         <v>4</v>
       </c>
       <c r="C509" t="n">
-        <v>73.98783192774101</v>
+        <v>65.8519605727856</v>
       </c>
       <c r="D509" t="n">
-        <v>44.52738555483277</v>
+        <v>40.13121369652897</v>
       </c>
       <c r="E509" t="n">
-        <v>65.5132822478248</v>
+        <v>53.83832694037135</v>
       </c>
       <c r="F509" t="n">
-        <v>46.69384280300714</v>
+        <v>28.84280185149711</v>
       </c>
     </row>
     <row r="510">
@@ -9717,16 +9717,16 @@
         <v>5</v>
       </c>
       <c r="C510" t="n">
-        <v>56.10298990253574</v>
+        <v>49.93377671459999</v>
       </c>
       <c r="D510" t="n">
-        <v>77.92292472095734</v>
+        <v>70.22962396892569</v>
       </c>
       <c r="E510" t="n">
-        <v>79.09821818899596</v>
+        <v>60.54077499335895</v>
       </c>
       <c r="F510" t="n">
-        <v>91.25458673045273</v>
+        <v>74.58115872089421</v>
       </c>
     </row>
     <row r="511">
@@ -9735,16 +9735,16 @@
         <v>6</v>
       </c>
       <c r="C511" t="n">
-        <v>37.20841566008501</v>
+        <v>33.11689310502745</v>
       </c>
       <c r="D511" t="n">
-        <v>92.76538657256827</v>
+        <v>83.606695201102</v>
       </c>
       <c r="E511" t="n">
-        <v>70.64277755007916</v>
+        <v>63.21596174833359</v>
       </c>
       <c r="F511" t="n">
-        <v>101.3170674754721</v>
+        <v>95.8242769881313</v>
       </c>
     </row>
     <row r="512">
@@ -9753,16 +9753,16 @@
         <v>7</v>
       </c>
       <c r="C512" t="n">
-        <v>38.65209659894379</v>
+        <v>34.40182358330201</v>
       </c>
       <c r="D512" t="n">
-        <v>85.3441556467628</v>
+        <v>76.91815958501387</v>
       </c>
       <c r="E512" t="n">
-        <v>29.29763012126833</v>
+        <v>28.41759573558631</v>
       </c>
       <c r="F512" t="n">
-        <v>52.85708175209572</v>
+        <v>54.21790198611477</v>
       </c>
     </row>
     <row r="513">
@@ -9771,16 +9771,16 @@
         <v>8</v>
       </c>
       <c r="C513" t="n">
-        <v>29.20041825812482</v>
+        <v>25.98947342748004</v>
       </c>
       <c r="D513" t="n">
-        <v>44.52738555483277</v>
+        <v>40.13121369652897</v>
       </c>
       <c r="E513" t="n">
-        <v>18.85978419074448</v>
+        <v>16.36741454635978</v>
       </c>
       <c r="F513" t="n">
-        <v>26.21737889730866</v>
+        <v>25.73156328139735</v>
       </c>
     </row>
     <row r="514">
@@ -9789,16 +9789,16 @@
         <v>9</v>
       </c>
       <c r="C514" t="n">
-        <v>34.66543084899669</v>
+        <v>30.85354072459106</v>
       </c>
       <c r="D514" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E514" t="n">
-        <v>26.16364036003925</v>
+        <v>23.67649012185463</v>
       </c>
       <c r="F514" t="n">
-        <v>43.88241427197642</v>
+        <v>44.28747779388951</v>
       </c>
     </row>
     <row r="515">
@@ -9807,16 +9807,16 @@
         <v>10</v>
       </c>
       <c r="C515" t="n">
-        <v>30.9305724948715</v>
+        <v>27.52937594407698</v>
       </c>
       <c r="D515" t="n">
-        <v>96.47600203547098</v>
+        <v>86.95096300914611</v>
       </c>
       <c r="E515" t="n">
-        <v>30.94179466155124</v>
+        <v>31.35488887249838</v>
       </c>
       <c r="F515" t="n">
-        <v>63.61827913238609</v>
+        <v>66.41410040491603</v>
       </c>
     </row>
     <row r="516">
@@ -9825,16 +9825,16 @@
         <v>11</v>
       </c>
       <c r="C516" t="n">
-        <v>85.09646335834016</v>
+        <v>75.73906146391394</v>
       </c>
       <c r="D516" t="n">
-        <v>107.6078484241792</v>
+        <v>96.98376643327833</v>
       </c>
       <c r="E516" t="n">
-        <v>58.94031902352384</v>
+        <v>54.39756795810806</v>
       </c>
       <c r="F516" t="n">
-        <v>66.71008788106879</v>
+        <v>66.6561218062775</v>
       </c>
     </row>
     <row r="517">
@@ -9843,16 +9843,16 @@
         <v>12</v>
       </c>
       <c r="C517" t="n">
-        <v>25.98387980902638</v>
+        <v>23.12663290881549</v>
       </c>
       <c r="D517" t="n">
-        <v>96.476002035471</v>
+        <v>86.95096300914609</v>
       </c>
       <c r="E517" t="n">
-        <v>29.89130193351478</v>
+        <v>30.18270644276467</v>
       </c>
       <c r="F517" t="n">
-        <v>72.59023065621852</v>
+        <v>75.44505116557026</v>
       </c>
     </row>
     <row r="518">
@@ -9863,16 +9863,16 @@
         <v>1</v>
       </c>
       <c r="C518" t="n">
-        <v>43.58637949583288</v>
+        <v>38.79352143840676</v>
       </c>
       <c r="D518" t="n">
-        <v>33.39553916612458</v>
+        <v>30.09841027239672</v>
       </c>
       <c r="E518" t="n">
-        <v>19.52067747535678</v>
+        <v>17.33356454491265</v>
       </c>
       <c r="F518" t="n">
-        <v>15.24737711762671</v>
+        <v>15.07316241748144</v>
       </c>
     </row>
     <row r="519">
@@ -9881,16 +9881,16 @@
         <v>2</v>
       </c>
       <c r="C519" t="n">
-        <v>14.82931209195381</v>
+        <v>13.19864699042129</v>
       </c>
       <c r="D519" t="n">
-        <v>44.52738555483277</v>
+        <v>40.13121369652897</v>
       </c>
       <c r="E519" t="n">
-        <v>12.53457513001782</v>
+        <v>13.02634781704744</v>
       </c>
       <c r="F519" t="n">
-        <v>44.05885974022053</v>
+        <v>47.07500934254023</v>
       </c>
     </row>
     <row r="520">
@@ -9899,16 +9899,16 @@
         <v>3</v>
       </c>
       <c r="C520" t="n">
-        <v>88.84420131974491</v>
+        <v>79.07468958061003</v>
       </c>
       <c r="D520" t="n">
-        <v>174.3989267564284</v>
+        <v>157.1805869780717</v>
       </c>
       <c r="E520" t="n">
-        <v>75.06606173720819</v>
+        <v>41.92098401188805</v>
       </c>
       <c r="F520" t="n">
-        <v>99.04555497349226</v>
+        <v>88.98727562012975</v>
       </c>
     </row>
     <row r="521">
@@ -9917,16 +9917,16 @@
         <v>4</v>
       </c>
       <c r="C521" t="n">
-        <v>137.5964794830527</v>
+        <v>122.4660556444114</v>
       </c>
       <c r="D521" t="n">
-        <v>166.9776958306228</v>
+        <v>150.4920513619836</v>
       </c>
       <c r="E521" t="n">
-        <v>166.9902480733642</v>
+        <v>113.2896629763918</v>
       </c>
       <c r="F521" t="n">
-        <v>208.7672241252708</v>
+        <v>153.4301410857915</v>
       </c>
     </row>
     <row r="522">
@@ -9935,16 +9935,16 @@
         <v>5</v>
       </c>
       <c r="C522" t="n">
-        <v>81.02213797633979</v>
+        <v>72.11275822694085</v>
       </c>
       <c r="D522" t="n">
-        <v>256.0324669402885</v>
+        <v>230.7544787550415</v>
       </c>
       <c r="E522" t="n">
-        <v>44.90393245979558</v>
+        <v>42.77801885716038</v>
       </c>
       <c r="F522" t="n">
-        <v>126.0576447911092</v>
+        <v>130.9033268668584</v>
       </c>
     </row>
     <row r="523">
@@ -9953,16 +9953,16 @@
         <v>6</v>
       </c>
       <c r="C523" t="n">
-        <v>22.87830930423397</v>
+        <v>20.36255804529841</v>
       </c>
       <c r="D523" t="n">
-        <v>96.476002035471</v>
+        <v>86.95096300914611</v>
       </c>
       <c r="E523" t="n">
-        <v>22.2347084399265</v>
+        <v>21.58437436713322</v>
       </c>
       <c r="F523" t="n">
-        <v>67.07611756738704</v>
+        <v>67.86294564896208</v>
       </c>
     </row>
     <row r="524">
@@ -9971,16 +9971,16 @@
         <v>7</v>
       </c>
       <c r="C524" t="n">
-        <v>72.86743870818951</v>
+        <v>64.85476835620628</v>
       </c>
       <c r="D524" t="n">
-        <v>133.5821566644983</v>
+        <v>120.3936410895869</v>
       </c>
       <c r="E524" t="n">
-        <v>55.36906719032171</v>
+        <v>39.80574328476052</v>
       </c>
       <c r="F524" t="n">
-        <v>87.89265089801461</v>
+        <v>71.02609293736093</v>
       </c>
     </row>
     <row r="525">
@@ -9989,16 +9989,16 @@
         <v>8</v>
       </c>
       <c r="C525" t="n">
-        <v>92.40986213632057</v>
+        <v>82.24826217209217</v>
       </c>
       <c r="D525" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E525" t="n">
-        <v>76.91312856124871</v>
+        <v>70.88100886769442</v>
       </c>
       <c r="F525" t="n">
-        <v>120.2349301249528</v>
+        <v>120.2466703490237</v>
       </c>
     </row>
     <row r="526">
@@ -10007,16 +10007,16 @@
         <v>9</v>
       </c>
       <c r="C526" t="n">
-        <v>77.49360517073681</v>
+        <v>68.9722309653598</v>
       </c>
       <c r="D526" t="n">
-        <v>211.5050813854557</v>
+        <v>190.6232650585126</v>
       </c>
       <c r="E526" t="n">
-        <v>55.36899989276345</v>
+        <v>58.41712256743746</v>
       </c>
       <c r="F526" t="n">
-        <v>122.1435025208855</v>
+        <v>128.1696172746932</v>
       </c>
     </row>
     <row r="527">
@@ -10025,16 +10025,16 @@
         <v>10</v>
       </c>
       <c r="C527" t="n">
-        <v>17.0476340509633</v>
+        <v>15.17303718913809</v>
       </c>
       <c r="D527" t="n">
-        <v>77.92292472095734</v>
+        <v>70.22962396892568</v>
       </c>
       <c r="E527" t="n">
-        <v>11.35582627037839</v>
+        <v>11.69178710923149</v>
       </c>
       <c r="F527" t="n">
-        <v>44.11650875933099</v>
+        <v>46.30773121369519</v>
       </c>
     </row>
     <row r="528">
@@ -10043,16 +10043,16 @@
         <v>11</v>
       </c>
       <c r="C528" t="n">
-        <v>76.54577785881102</v>
+        <v>68.12862891420488</v>
       </c>
       <c r="D528" t="n">
-        <v>256.0324669402885</v>
+        <v>230.7544787550416</v>
       </c>
       <c r="E528" t="n">
-        <v>65.90171152667072</v>
+        <v>63.25831897683954</v>
       </c>
       <c r="F528" t="n">
-        <v>171.0789389722949</v>
+        <v>176.1776186325855</v>
       </c>
     </row>
     <row r="529">
@@ -10061,16 +10061,16 @@
         <v>12</v>
       </c>
       <c r="C529" t="n">
-        <v>31.23066366934345</v>
+        <v>27.79646840610328</v>
       </c>
       <c r="D529" t="n">
-        <v>89.05477110966554</v>
+        <v>80.26242739305793</v>
       </c>
       <c r="E529" t="n">
-        <v>30.6337810614091</v>
+        <v>30.1290685967279</v>
       </c>
       <c r="F529" t="n">
-        <v>67.73008350924609</v>
+        <v>68.95245811665146</v>
       </c>
     </row>
     <row r="530">
@@ -10081,16 +10081,16 @@
         <v>1</v>
       </c>
       <c r="C530" t="n">
-        <v>41.15245272174866</v>
+        <v>36.62723482359455</v>
       </c>
       <c r="D530" t="n">
-        <v>111.3184638870819</v>
+        <v>100.3280342413224</v>
       </c>
       <c r="E530" t="n">
-        <v>25.00254324150773</v>
+        <v>25.55988332050517</v>
       </c>
       <c r="F530" t="n">
-        <v>61.30185928063487</v>
+        <v>64.10988733129508</v>
       </c>
     </row>
     <row r="531">
@@ -10099,16 +10099,16 @@
         <v>2</v>
       </c>
       <c r="C531" t="n">
-        <v>26.51879427091592</v>
+        <v>23.60272695207067</v>
       </c>
       <c r="D531" t="n">
-        <v>48.2380010177355</v>
+        <v>43.47548150457305</v>
       </c>
       <c r="E531" t="n">
-        <v>24.98635430765609</v>
+        <v>24.27593091956847</v>
       </c>
       <c r="F531" t="n">
-        <v>36.59660949494116</v>
+        <v>37.82950084743015</v>
       </c>
     </row>
     <row r="532">
@@ -10117,16 +10117,16 @@
         <v>3</v>
       </c>
       <c r="C532" t="n">
-        <v>53.06322308898055</v>
+        <v>47.22826961780878</v>
       </c>
       <c r="D532" t="n">
-        <v>89.05477110966551</v>
+        <v>80.26242739305792</v>
       </c>
       <c r="E532" t="n">
-        <v>29.93797249526848</v>
+        <v>28.32518213199761</v>
       </c>
       <c r="F532" t="n">
-        <v>51.47832401416671</v>
+        <v>53.02352853045399</v>
       </c>
     </row>
     <row r="533">
@@ -10135,16 +10135,16 @@
         <v>4</v>
       </c>
       <c r="C533" t="n">
-        <v>91.5133995015271</v>
+        <v>81.45037662059974</v>
       </c>
       <c r="D533" t="n">
-        <v>200.3732349967474</v>
+        <v>180.5904616343803</v>
       </c>
       <c r="E533" t="n">
-        <v>80.06134971727309</v>
+        <v>85.08478200773308</v>
       </c>
       <c r="F533" t="n">
-        <v>121.1723788796771</v>
+        <v>128.488518458739</v>
       </c>
     </row>
     <row r="534">
@@ -10153,16 +10153,16 @@
         <v>5</v>
       </c>
       <c r="C534" t="n">
-        <v>173.4905059963739</v>
+        <v>154.413092841855</v>
       </c>
       <c r="D534" t="n">
-        <v>393.3252390676894</v>
+        <v>354.4923876526724</v>
       </c>
       <c r="E534" t="n">
-        <v>167.6460136718497</v>
+        <v>168.3776221988468</v>
       </c>
       <c r="F534" t="n">
-        <v>243.4305200412696</v>
+        <v>249.9712440348572</v>
       </c>
     </row>
     <row r="535">
@@ -10171,16 +10171,16 @@
         <v>6</v>
       </c>
       <c r="C535" t="n">
-        <v>33.09744325993491</v>
+        <v>29.45797263990443</v>
       </c>
       <c r="D535" t="n">
-        <v>166.9776958306228</v>
+        <v>150.4920513619836</v>
       </c>
       <c r="E535" t="n">
-        <v>23.28744084238226</v>
+        <v>23.94819013171003</v>
       </c>
       <c r="F535" t="n">
-        <v>100.2824547318963</v>
+        <v>105.1312565714876</v>
       </c>
     </row>
     <row r="536">
@@ -10189,16 +10189,16 @@
         <v>7</v>
       </c>
       <c r="C536" t="n">
-        <v>76.24154203747599</v>
+        <v>67.85784756017158</v>
       </c>
       <c r="D536" t="n">
-        <v>111.3184638870819</v>
+        <v>100.3280342413224</v>
       </c>
       <c r="E536" t="n">
-        <v>65.39911600057677</v>
+        <v>68.02849461232562</v>
       </c>
       <c r="F536" t="n">
-        <v>80.70607084137667</v>
+        <v>85.44049048321131</v>
       </c>
     </row>
     <row r="537">
@@ -10207,16 +10207,16 @@
         <v>8</v>
       </c>
       <c r="C537" t="n">
-        <v>307.6587611225045</v>
+        <v>273.8278995267459</v>
       </c>
       <c r="D537" t="n">
-        <v>244.9006205515802</v>
+        <v>220.7216753309093</v>
       </c>
       <c r="E537" t="n">
-        <v>297.6908526701312</v>
+        <v>224.8542801863792</v>
       </c>
       <c r="F537" t="n">
-        <v>283.1071077213973</v>
+        <v>217.9848915228116</v>
       </c>
     </row>
     <row r="538">
@@ -10225,16 +10225,16 @@
         <v>9</v>
       </c>
       <c r="C538" t="n">
-        <v>280.0005966867184</v>
+        <v>249.2110901611222</v>
       </c>
       <c r="D538" t="n">
-        <v>474.9587792515496</v>
+        <v>428.0662794296422</v>
       </c>
       <c r="E538" t="n">
-        <v>567.3406830646751</v>
+        <v>525.4782476339309</v>
       </c>
       <c r="F538" t="n">
-        <v>803.2489180159465</v>
+        <v>746.1460084178195</v>
       </c>
     </row>
     <row r="539">
@@ -10243,16 +10243,16 @@
         <v>10</v>
       </c>
       <c r="C539" t="n">
-        <v>257.3928380937098</v>
+        <v>229.0893324515594</v>
       </c>
       <c r="D539" t="n">
-        <v>653.0683214708806</v>
+        <v>588.5911342157582</v>
       </c>
       <c r="E539" t="n">
-        <v>284.3133666941187</v>
+        <v>271.7838175141242</v>
       </c>
       <c r="F539" t="n">
-        <v>487.7642755704292</v>
+        <v>490.1122852069144</v>
       </c>
     </row>
     <row r="540">
@@ -10261,16 +10261,16 @@
         <v>11</v>
       </c>
       <c r="C540" t="n">
-        <v>369.3218857407618</v>
+        <v>328.7104058167262</v>
       </c>
       <c r="D540" t="n">
-        <v>615.9621668418533</v>
+        <v>555.1484561353174</v>
       </c>
       <c r="E540" t="n">
-        <v>273.6390862470367</v>
+        <v>256.3146996300939</v>
       </c>
       <c r="F540" t="n">
-        <v>372.913871065375</v>
+        <v>375.0319560861359</v>
       </c>
     </row>
     <row r="541">
@@ -10279,16 +10279,16 @@
         <v>12</v>
       </c>
       <c r="C541" t="n">
-        <v>267.8999826453878</v>
+        <v>238.4410873377602</v>
       </c>
       <c r="D541" t="n">
-        <v>348.7978535128567</v>
+        <v>314.3611739561436</v>
       </c>
       <c r="E541" t="n">
-        <v>345.5428295112658</v>
+        <v>265.5054229976877</v>
       </c>
       <c r="F541" t="n">
-        <v>308.3028515908243</v>
+        <v>261.5947472947021</v>
       </c>
     </row>
     <row r="542">
@@ -10299,16 +10299,16 @@
         <v>1</v>
       </c>
       <c r="C542" t="n">
-        <v>408.2996532462657</v>
+        <v>363.4020887882508</v>
       </c>
       <c r="D542" t="n">
-        <v>371.0615462902731</v>
+        <v>334.426780804408</v>
       </c>
       <c r="E542" t="n">
-        <v>336.8132121465897</v>
+        <v>283.9881798799939</v>
       </c>
       <c r="F542" t="n">
-        <v>300.8552761381175</v>
+        <v>264.7004931054045</v>
       </c>
     </row>
     <row r="543">
@@ -10317,16 +10317,16 @@
         <v>2</v>
       </c>
       <c r="C543" t="n">
-        <v>260.3069292876845</v>
+        <v>231.6829835075673</v>
       </c>
       <c r="D543" t="n">
-        <v>326.5341607354403</v>
+        <v>294.295567107879</v>
       </c>
       <c r="E543" t="n">
-        <v>322.6028491030056</v>
+        <v>323.957717046861</v>
       </c>
       <c r="F543" t="n">
-        <v>292.9483987189328</v>
+        <v>301.5030660267513</v>
       </c>
     </row>
     <row r="544">
@@ -10335,16 +10335,16 @@
         <v>3</v>
       </c>
       <c r="C544" t="n">
-        <v>878.3792264158863</v>
+        <v>781.7906360924895</v>
       </c>
       <c r="D544" t="n">
-        <v>912.8114038740717</v>
+        <v>822.6898807788438</v>
       </c>
       <c r="E544" t="n">
-        <v>1018.20205463385</v>
+        <v>900.4832003771459</v>
       </c>
       <c r="F544" t="n">
-        <v>1024.207465332855</v>
+        <v>935.3763525361393</v>
       </c>
     </row>
     <row r="545">
@@ -10353,16 +10353,16 @@
         <v>4</v>
       </c>
       <c r="C545" t="n">
-        <v>878.116714927378</v>
+        <v>781.5569909681394</v>
       </c>
       <c r="D545" t="n">
-        <v>768.024643654926</v>
+        <v>692.1978623865356</v>
       </c>
       <c r="E545" t="n">
-        <v>887.1595719562582</v>
+        <v>752.316446723057</v>
       </c>
       <c r="F545" t="n">
-        <v>919.5081983925357</v>
+        <v>776.1716364261766</v>
       </c>
     </row>
     <row r="546">
@@ -10371,16 +10371,16 @@
         <v>5</v>
       </c>
       <c r="C546" t="n">
-        <v>1018.303873359015</v>
+        <v>906.328848573954</v>
       </c>
       <c r="D546" t="n">
-        <v>1123.661670766074</v>
+        <v>1012.722980930054</v>
       </c>
       <c r="E546" t="n">
-        <v>1092.4422148089</v>
+        <v>972.2555876835343</v>
       </c>
       <c r="F546" t="n">
-        <v>1198.532178897173</v>
+        <v>1110.258643451172</v>
       </c>
     </row>
     <row r="547">
@@ -10389,16 +10389,16 @@
         <v>6</v>
       </c>
       <c r="C547" t="n">
-        <v>1175.885322726375</v>
+        <v>1046.582281069129</v>
       </c>
       <c r="D547" t="n">
-        <v>896.659313035554</v>
+        <v>808.1324797320636</v>
       </c>
       <c r="E547" t="n">
-        <v>937.7212755936458</v>
+        <v>793.9834853037391</v>
       </c>
       <c r="F547" t="n">
-        <v>731.411400528023</v>
+        <v>664.7274102406049</v>
       </c>
     </row>
     <row r="548">
@@ -10407,16 +10407,16 @@
         <v>7</v>
       </c>
       <c r="C548" t="n">
-        <v>746.2722214082872</v>
+        <v>664.2104197449497</v>
       </c>
       <c r="D548" t="n">
-        <v>692.357191078086</v>
+        <v>624.001028653872</v>
       </c>
       <c r="E548" t="n">
-        <v>1041.162904188541</v>
+        <v>880.0752424288959</v>
       </c>
       <c r="F548" t="n">
-        <v>873.0703533009952</v>
+        <v>756.0085622839335</v>
       </c>
     </row>
     <row r="549">
@@ -10425,16 +10425,16 @@
         <v>8</v>
       </c>
       <c r="C549" t="n">
-        <v>529.9022264644077</v>
+        <v>471.6329647102675</v>
       </c>
       <c r="D549" t="n">
-        <v>454.00471546104</v>
+        <v>409.1810023959815</v>
       </c>
       <c r="E549" t="n">
-        <v>508.3157923803081</v>
+        <v>505.4482477862766</v>
       </c>
       <c r="F549" t="n">
-        <v>501.3358642626301</v>
+        <v>509.8939881782312</v>
       </c>
     </row>
     <row r="550">
@@ -10443,16 +10443,16 @@
         <v>9</v>
       </c>
       <c r="C550" t="n">
-        <v>542.7596490646046</v>
+        <v>483.076555691048</v>
       </c>
       <c r="D550" t="n">
-        <v>578.856012212826</v>
+        <v>521.7057780548765</v>
       </c>
       <c r="E550" t="n">
-        <v>611.8974574074496</v>
+        <v>526.2879708281985</v>
       </c>
       <c r="F550" t="n">
-        <v>516.3467106490051</v>
+        <v>451.1865925229616</v>
       </c>
     </row>
     <row r="551">
@@ -10461,16 +10461,16 @@
         <v>10</v>
       </c>
       <c r="C551" t="n">
-        <v>435.6229492554189</v>
+        <v>387.7208526259391</v>
       </c>
       <c r="D551" t="n">
-        <v>408.6042439149361</v>
+        <v>368.2629021563834</v>
       </c>
       <c r="E551" t="n">
-        <v>316.107604674387</v>
+        <v>298.4031165645544</v>
       </c>
       <c r="F551" t="n">
-        <v>333.207569216007</v>
+        <v>318.6375497369412</v>
       </c>
     </row>
     <row r="552">
@@ -10479,16 +10479,16 @@
         <v>11</v>
       </c>
       <c r="C552" t="n">
-        <v>584.4031158864468</v>
+        <v>520.1408115803716</v>
       </c>
       <c r="D552" t="n">
-        <v>480.488323862934</v>
+        <v>433.0498942024139</v>
       </c>
       <c r="E552" t="n">
-        <v>451.1754482488973</v>
+        <v>401.0157969452434</v>
       </c>
       <c r="F552" t="n">
-        <v>422.088392603584</v>
+        <v>382.1153136559954</v>
       </c>
     </row>
     <row r="553">
@@ -10497,16 +10497,16 @@
         <v>12</v>
       </c>
       <c r="C553" t="n">
-        <v>431.4713669709003</v>
+        <v>384.0257878322877</v>
       </c>
       <c r="D553" t="n">
-        <v>314.019928193886</v>
+        <v>283.0168599905539</v>
       </c>
       <c r="E553" t="n">
-        <v>312.796073758022</v>
+        <v>282.1237689124196</v>
       </c>
       <c r="F553" t="n">
-        <v>239.5800071187042</v>
+        <v>227.9891126739436</v>
       </c>
     </row>
     <row r="554">
@@ -10517,16 +10517,16 @@
         <v>1</v>
       </c>
       <c r="C554" t="n">
-        <v>193.5603067585346</v>
+        <v>172.275972372968</v>
       </c>
       <c r="D554" t="n">
-        <v>181.601886184416</v>
+        <v>163.6724009583926</v>
       </c>
       <c r="E554" t="n">
-        <v>109.3943039096884</v>
+        <v>101.9493747699391</v>
       </c>
       <c r="F554" t="n">
-        <v>104.5960653738065</v>
+        <v>105.9922568130929</v>
       </c>
     </row>
     <row r="555">
@@ -10535,16 +10535,16 @@
         <v>2</v>
       </c>
       <c r="C555" t="n">
-        <v>161.2363246517427</v>
+        <v>143.5064093273749</v>
       </c>
       <c r="D555" t="n">
-        <v>98.36768834989202</v>
+        <v>88.65588385246268</v>
       </c>
       <c r="E555" t="n">
-        <v>176.6017182223664</v>
+        <v>126.0143177732123</v>
       </c>
       <c r="F555" t="n">
-        <v>149.681717529146</v>
+        <v>89.42940784359405</v>
       </c>
     </row>
     <row r="556">
@@ -10553,16 +10553,16 @@
         <v>3</v>
       </c>
       <c r="C556" t="n">
-        <v>349.4627238586066</v>
+        <v>311.0350028322265</v>
       </c>
       <c r="D556" t="n">
-        <v>227.00235773052</v>
+        <v>204.5905011979908</v>
       </c>
       <c r="E556" t="n">
-        <v>422.1919125641214</v>
+        <v>385.1436343640781</v>
       </c>
       <c r="F556" t="n">
-        <v>182.2999284651864</v>
+        <v>168.3733000909885</v>
       </c>
     </row>
     <row r="557">
@@ -10571,16 +10571,16 @@
         <v>4</v>
       </c>
       <c r="C557" t="n">
-        <v>161.3566208845062</v>
+        <v>143.6134775110289</v>
       </c>
       <c r="D557" t="n">
-        <v>94.58431572104999</v>
+        <v>85.24604216582951</v>
       </c>
       <c r="E557" t="n">
-        <v>216.1930394357836</v>
+        <v>150.1974748816266</v>
       </c>
       <c r="F557" t="n">
-        <v>155.8754388544808</v>
+        <v>88.53548026439651</v>
       </c>
     </row>
     <row r="558">
@@ -10589,16 +10589,16 @@
         <v>5</v>
       </c>
       <c r="C558" t="n">
-        <v>176.1148696278859</v>
+        <v>156.7488754413473</v>
       </c>
       <c r="D558" t="n">
-        <v>128.634669380628</v>
+        <v>115.9346173455281</v>
       </c>
       <c r="E558" t="n">
-        <v>112.2070439691683</v>
+        <v>106.0586919925666</v>
       </c>
       <c r="F558" t="n">
-        <v>89.37379841728412</v>
+        <v>85.36896204384608</v>
       </c>
     </row>
     <row r="559">
@@ -10607,16 +10607,16 @@
         <v>6</v>
       </c>
       <c r="C559" t="n">
-        <v>364.0722118711706</v>
+        <v>324.0379981021991</v>
       </c>
       <c r="D559" t="n">
-        <v>215.652239843994</v>
+        <v>194.3609761380913</v>
       </c>
       <c r="E559" t="n">
-        <v>234.3438248524019</v>
+        <v>227.8678438337575</v>
       </c>
       <c r="F559" t="n">
-        <v>117.7277934363787</v>
+        <v>121.6954206226678</v>
       </c>
     </row>
     <row r="560">
@@ -10625,16 +10625,16 @@
         <v>7</v>
       </c>
       <c r="C560" t="n">
-        <v>216.9922093951668</v>
+        <v>193.1312493606736</v>
       </c>
       <c r="D560" t="n">
-        <v>272.402829276624</v>
+        <v>245.508601437589</v>
       </c>
       <c r="E560" t="n">
-        <v>271.3264132939798</v>
+        <v>268.1919353953348</v>
       </c>
       <c r="F560" t="n">
-        <v>257.8460623370858</v>
+        <v>255.0230372907183</v>
       </c>
     </row>
     <row r="561">
@@ -10643,16 +10643,16 @@
         <v>8</v>
       </c>
       <c r="C561" t="n">
-        <v>268.8305655278613</v>
+        <v>239.2693411963975</v>
       </c>
       <c r="D561" t="n">
-        <v>200.518749328626</v>
+        <v>180.7216093915586</v>
       </c>
       <c r="E561" t="n">
-        <v>174.556993777306</v>
+        <v>160.5468949426897</v>
       </c>
       <c r="F561" t="n">
-        <v>123.3205090156988</v>
+        <v>121.9584468265267</v>
       </c>
     </row>
     <row r="562">
@@ -10661,16 +10661,16 @@
         <v>9</v>
       </c>
       <c r="C562" t="n">
-        <v>109.4781300933046</v>
+        <v>97.43966431571445</v>
       </c>
       <c r="D562" t="n">
-        <v>98.36768834989202</v>
+        <v>88.65588385246268</v>
       </c>
       <c r="E562" t="n">
-        <v>67.36145018230857</v>
+        <v>67.06558722911056</v>
       </c>
       <c r="F562" t="n">
-        <v>74.06313137549662</v>
+        <v>71.2427813837826</v>
       </c>
     </row>
     <row r="563">
@@ -10679,16 +10679,16 @@
         <v>10</v>
       </c>
       <c r="C563" t="n">
-        <v>41.23414775611437</v>
+        <v>36.69994648498364</v>
       </c>
       <c r="D563" t="n">
-        <v>75.66745257683999</v>
+        <v>68.19683373266361</v>
       </c>
       <c r="E563" t="n">
-        <v>127.9939135273705</v>
+        <v>95.8534659820522</v>
       </c>
       <c r="F563" t="n">
-        <v>147.3496498675517</v>
+        <v>111.2825259843779</v>
       </c>
     </row>
     <row r="564">
@@ -10697,16 +10697,16 @@
         <v>11</v>
       </c>
       <c r="C564" t="n">
-        <v>99.53164643908052</v>
+        <v>88.58691877134562</v>
       </c>
       <c r="D564" t="n">
-        <v>79.45082520568201</v>
+        <v>71.60667541929679</v>
       </c>
       <c r="E564" t="n">
-        <v>63.02761783396474</v>
+        <v>63.54508689352674</v>
       </c>
       <c r="F564" t="n">
-        <v>41.39391988968791</v>
+        <v>43.63864792203684</v>
       </c>
     </row>
     <row r="565">
@@ -10715,16 +10715,16 @@
         <v>12</v>
       </c>
       <c r="C565" t="n">
-        <v>96.83391617092022</v>
+        <v>86.18583709850513</v>
       </c>
       <c r="D565" t="n">
-        <v>71.884079947998</v>
+        <v>64.78699204603043</v>
       </c>
       <c r="E565" t="n">
-        <v>55.76201087624622</v>
+        <v>59.55597211055151</v>
       </c>
       <c r="F565" t="n">
-        <v>57.94224723530867</v>
+        <v>61.54890903908666</v>
       </c>
     </row>
     <row r="566">
@@ -10735,16 +10735,16 @@
         <v>1</v>
       </c>
       <c r="C566" t="n">
-        <v>344.8405789058541</v>
+        <v>306.9211195184456</v>
       </c>
       <c r="D566" t="n">
-        <v>178.1095422193311</v>
+        <v>160.5248547861159</v>
       </c>
       <c r="E566" t="n">
-        <v>269.3033769734301</v>
+        <v>264.3994031638377</v>
       </c>
       <c r="F566" t="n">
-        <v>105.1437470711175</v>
+        <v>107.5091761700047</v>
       </c>
     </row>
     <row r="567">
@@ -10753,16 +10753,16 @@
         <v>2</v>
       </c>
       <c r="C567" t="n">
-        <v>168.2202982773957</v>
+        <v>149.7224092270211</v>
       </c>
       <c r="D567" t="n">
-        <v>122.4503102757901</v>
+        <v>110.3608376654547</v>
       </c>
       <c r="E567" t="n">
-        <v>86.12087431485369</v>
+        <v>78.33338268510747</v>
       </c>
       <c r="F567" t="n">
-        <v>51.06717907914807</v>
+        <v>50.44781952356533</v>
       </c>
     </row>
     <row r="568">
@@ -10771,16 +10771,16 @@
         <v>3</v>
       </c>
       <c r="C568" t="n">
-        <v>59.99565773475284</v>
+        <v>53.39839788177328</v>
       </c>
       <c r="D568" t="n">
-        <v>74.21230925805462</v>
+        <v>66.88535616088161</v>
       </c>
       <c r="E568" t="n">
-        <v>129.7368607866352</v>
+        <v>88.89737718049587</v>
       </c>
       <c r="F568" t="n">
-        <v>122.0861047959166</v>
+        <v>79.2841958068298</v>
       </c>
     </row>
     <row r="569">
@@ -10789,16 +10789,16 @@
         <v>4</v>
       </c>
       <c r="C569" t="n">
-        <v>53.51347576008621</v>
+        <v>47.62901147458327</v>
       </c>
       <c r="D569" t="n">
-        <v>66.79107833224916</v>
+        <v>60.19682054479345</v>
       </c>
       <c r="E569" t="n">
-        <v>39.19041481194938</v>
+        <v>36.14688275404544</v>
       </c>
       <c r="F569" t="n">
-        <v>40.37323851660637</v>
+        <v>40.78049857088524</v>
       </c>
     </row>
     <row r="570">
@@ -10807,16 +10807,16 @@
         <v>5</v>
       </c>
       <c r="C570" t="n">
-        <v>52.34207897110947</v>
+        <v>46.58642415781853</v>
       </c>
       <c r="D570" t="n">
-        <v>124.851296751786</v>
+        <v>112.524775658895</v>
       </c>
       <c r="E570" t="n">
-        <v>33.159995773879</v>
+        <v>33.88466831733458</v>
       </c>
       <c r="F570" t="n">
-        <v>70.80574541803134</v>
+        <v>74.01506345092642</v>
       </c>
     </row>
     <row r="571">
@@ -10825,16 +10825,16 @@
         <v>6</v>
       </c>
       <c r="C571" t="n">
-        <v>187.0013832423537</v>
+        <v>166.4382830998279</v>
       </c>
       <c r="D571" t="n">
-        <v>88.75792187263332</v>
+        <v>79.99488596841441</v>
       </c>
       <c r="E571" t="n">
-        <v>105.6895280149121</v>
+        <v>74.04758826781253</v>
       </c>
       <c r="F571" t="n">
-        <v>58.30319138244527</v>
+        <v>45.05317785574705</v>
       </c>
     </row>
     <row r="572">
@@ -10843,16 +10843,16 @@
         <v>7</v>
       </c>
       <c r="C572" t="n">
-        <v>125.7396522815231</v>
+        <v>111.9130323019243</v>
       </c>
       <c r="D572" t="n">
-        <v>135.0664028496594</v>
+        <v>121.7313482128045</v>
       </c>
       <c r="E572" t="n">
-        <v>57.50607033919309</v>
+        <v>57.78830891438894</v>
       </c>
       <c r="F572" t="n">
-        <v>92.95331263079265</v>
+        <v>94.59919699557334</v>
       </c>
     </row>
     <row r="573">
@@ -10861,16 +10861,16 @@
         <v>8</v>
       </c>
       <c r="C573" t="n">
-        <v>94.51532241364265</v>
+        <v>84.12220121797731</v>
       </c>
       <c r="D573" t="n">
-        <v>131.2073627682406</v>
+        <v>118.2533096924387</v>
       </c>
       <c r="E573" t="n">
-        <v>178.4769974233</v>
+        <v>184.9767521859363</v>
       </c>
       <c r="F573" t="n">
-        <v>147.1074006573396</v>
+        <v>154.1013282824057</v>
       </c>
     </row>
     <row r="574">
@@ -10879,16 +10879,16 @@
         <v>9</v>
       </c>
       <c r="C574" t="n">
-        <v>38.84760598299007</v>
+        <v>34.57583430796279</v>
       </c>
       <c r="D574" t="n">
-        <v>135.0664028496594</v>
+        <v>121.7313482128045</v>
       </c>
       <c r="E574" t="n">
-        <v>59.81875902270936</v>
+        <v>30.07276241036501</v>
       </c>
       <c r="F574" t="n">
-        <v>96.38623891228745</v>
+        <v>85.88407415312818</v>
       </c>
     </row>
     <row r="575">
@@ -10897,16 +10897,16 @@
         <v>10</v>
       </c>
       <c r="C575" t="n">
-        <v>62.27185789961234</v>
+        <v>55.42430186634314</v>
       </c>
       <c r="D575" t="n">
-        <v>254.6966453736435</v>
+        <v>229.5505423441457</v>
       </c>
       <c r="E575" t="n">
-        <v>46.19359198889919</v>
+        <v>47.42126052072132</v>
       </c>
       <c r="F575" t="n">
-        <v>135.8268139975251</v>
+        <v>143.2049376798585</v>
       </c>
     </row>
     <row r="576">
@@ -10915,16 +10915,16 @@
         <v>11</v>
       </c>
       <c r="C576" t="n">
-        <v>185.663159992293</v>
+        <v>165.2472139415014</v>
       </c>
       <c r="D576" t="n">
-        <v>848.9888179121449</v>
+        <v>765.1684744804857</v>
       </c>
       <c r="E576" t="n">
-        <v>161.4413266769102</v>
+        <v>163.7932535315789</v>
       </c>
       <c r="F576" t="n">
-        <v>492.2815671337495</v>
+        <v>517.3182788540217</v>
       </c>
     </row>
     <row r="577">
@@ -10933,16 +10933,16 @@
         <v>12</v>
       </c>
       <c r="C577" t="n">
-        <v>155.5615235842465</v>
+        <v>138.4556223747294</v>
       </c>
       <c r="D577" t="n">
-        <v>169.797763582429</v>
+        <v>153.0336948960971</v>
       </c>
       <c r="E577" t="n">
-        <v>142.8194580528993</v>
+        <v>99.68489275116785</v>
       </c>
       <c r="F577" t="n">
-        <v>101.3392288275207</v>
+        <v>87.95990358188961</v>
       </c>
     </row>
     <row r="578">
@@ -10953,16 +10953,16 @@
         <v>1</v>
       </c>
       <c r="C578" t="n">
-        <v>24.84368595629563</v>
+        <v>22.11181738200445</v>
       </c>
       <c r="D578" t="n">
-        <v>106.3204920390905</v>
+        <v>95.82351025497731</v>
       </c>
       <c r="E578" t="n">
-        <v>13.16379742203627</v>
+        <v>13.39252937724204</v>
       </c>
       <c r="F578" t="n">
-        <v>55.37160079427002</v>
+        <v>57.90336658111401</v>
       </c>
     </row>
     <row r="579">
@@ -10971,16 +10971,16 @@
         <v>2</v>
       </c>
       <c r="C579" t="n">
-        <v>19.6517272539538</v>
+        <v>17.49077834282762</v>
       </c>
       <c r="D579" t="n">
-        <v>23.15424048851304</v>
+        <v>20.86823112219506</v>
       </c>
       <c r="E579" t="n">
-        <v>38.61614305254465</v>
+        <v>36.70856976302881</v>
       </c>
       <c r="F579" t="n">
-        <v>47.90138904269249</v>
+        <v>44.4790690746479</v>
       </c>
     </row>
     <row r="580">
@@ -10989,16 +10989,16 @@
         <v>3</v>
       </c>
       <c r="C580" t="n">
-        <v>126.2506752336734</v>
+        <v>112.3678620005383</v>
       </c>
       <c r="D580" t="n">
-        <v>177.5158437452666</v>
+        <v>159.9897719368288</v>
       </c>
       <c r="E580" t="n">
-        <v>200.0204674537417</v>
+        <v>176.4450807411347</v>
       </c>
       <c r="F580" t="n">
-        <v>191.4134155492713</v>
+        <v>170.3304837728556</v>
       </c>
     </row>
     <row r="581">
@@ -11007,16 +11007,16 @@
         <v>4</v>
       </c>
       <c r="C581" t="n">
-        <v>51.8909111550419</v>
+        <v>46.18486778751689</v>
       </c>
       <c r="D581" t="n">
-        <v>65.60368138412029</v>
+        <v>59.12665484621935</v>
       </c>
       <c r="E581" t="n">
-        <v>67.28627995206752</v>
+        <v>69.01731034636207</v>
       </c>
       <c r="F581" t="n">
-        <v>41.75089510945759</v>
+        <v>43.63563814504416</v>
       </c>
     </row>
     <row r="582">
@@ -11025,16 +11025,16 @@
         <v>5</v>
       </c>
       <c r="C582" t="n">
-        <v>159.6454890195594</v>
+        <v>142.0905056226869</v>
       </c>
       <c r="D582" t="n">
-        <v>196.8110441523608</v>
+        <v>177.379964538658</v>
       </c>
       <c r="E582" t="n">
-        <v>89.60998137621903</v>
+        <v>80.03828830008061</v>
       </c>
       <c r="F582" t="n">
-        <v>117.726310859245</v>
+        <v>119.439298220418</v>
       </c>
     </row>
     <row r="583">
@@ -11043,16 +11043,16 @@
         <v>6</v>
       </c>
       <c r="C583" t="n">
-        <v>54.69653815078414</v>
+        <v>48.68198161680169</v>
       </c>
       <c r="D583" t="n">
-        <v>158.2206433381724</v>
+        <v>142.5995793349996</v>
       </c>
       <c r="E583" t="n">
-        <v>40.03395102222471</v>
+        <v>40.30457633629934</v>
       </c>
       <c r="F583" t="n">
-        <v>79.62041746952512</v>
+        <v>83.0243174701576</v>
       </c>
     </row>
     <row r="584">
@@ -11061,16 +11061,16 @@
         <v>7</v>
       </c>
       <c r="C584" t="n">
-        <v>169.4102246966949</v>
+        <v>150.7814886135442</v>
       </c>
       <c r="D584" t="n">
-        <v>594.2921725385013</v>
+        <v>535.6179321363398</v>
       </c>
       <c r="E584" t="n">
-        <v>161.3417689502247</v>
+        <v>147.0651430978514</v>
       </c>
       <c r="F584" t="n">
-        <v>364.0914145256215</v>
+        <v>370.4363281749146</v>
       </c>
     </row>
     <row r="585">
@@ -11079,16 +11079,16 @@
         <v>8</v>
       </c>
       <c r="C585" t="n">
-        <v>221.0349935263793</v>
+        <v>196.7294796949926</v>
       </c>
       <c r="D585" t="n">
-        <v>505.534250665868</v>
+        <v>455.6230461679255</v>
       </c>
       <c r="E585" t="n">
-        <v>157.7930034650301</v>
+        <v>129.4332459024463</v>
       </c>
       <c r="F585" t="n">
-        <v>354.7111298198282</v>
+        <v>331.6879015558394</v>
       </c>
     </row>
     <row r="586">
@@ -11097,16 +11097,16 @@
         <v>9</v>
       </c>
       <c r="C586" t="n">
-        <v>72.07768246516557</v>
+        <v>64.1518555173963</v>
       </c>
       <c r="D586" t="n">
-        <v>308.7232065135072</v>
+        <v>278.2430816292675</v>
       </c>
       <c r="E586" t="n">
-        <v>57.95370125452033</v>
+        <v>58.01038076353156</v>
       </c>
       <c r="F586" t="n">
-        <v>207.3517413590445</v>
+        <v>214.1134174843467</v>
       </c>
     </row>
     <row r="587">
@@ -11115,16 +11115,16 @@
         <v>10</v>
       </c>
       <c r="C587" t="n">
-        <v>112.5331842689121</v>
+        <v>100.1587777412344</v>
       </c>
       <c r="D587" t="n">
-        <v>192.952004070942</v>
+        <v>173.9019260182922</v>
       </c>
       <c r="E587" t="n">
-        <v>97.70969320410755</v>
+        <v>85.05669640450023</v>
       </c>
       <c r="F587" t="n">
-        <v>123.4495137074413</v>
+        <v>119.2273725275374</v>
       </c>
     </row>
     <row r="588">
@@ -11133,20 +11133,166 @@
         <v>11</v>
       </c>
       <c r="C588" t="n">
-        <v>87.9896332301447</v>
+        <v>78.31409175422591</v>
       </c>
       <c r="D588" t="n">
-        <v>181.3748838266854</v>
+        <v>163.4678104571946</v>
       </c>
       <c r="E588" t="n">
-        <v>71.42924356096962</v>
+        <v>68.78574519350956</v>
       </c>
       <c r="F588" t="n">
-        <v>112.7376323336296</v>
+        <v>116.0017198982655</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n"/>
+      <c r="B589" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C589" t="n">
+        <v>138.9830391334523</v>
+      </c>
+      <c r="D589" t="n">
+        <v>222.594465303414</v>
+      </c>
+      <c r="E589" t="n">
+        <v>94.44705375455821</v>
+      </c>
+      <c r="F589" t="n">
+        <v>148.5610528016237</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B590" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C590" t="n">
+        <v>29.18947250677251</v>
+      </c>
+      <c r="D590" t="n">
+        <v>135.6435022942679</v>
+      </c>
+      <c r="E590" t="n">
+        <v>19.86492288792907</v>
+      </c>
+      <c r="F590" t="n">
+        <v>84.84151096473795</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n"/>
+      <c r="B591" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C591" t="n">
+        <v>123.0911645027716</v>
+      </c>
+      <c r="D591" t="n">
+        <v>153.0336948960971</v>
+      </c>
+      <c r="E591" t="n">
+        <v>89.77405810366744</v>
+      </c>
+      <c r="F591" t="n">
+        <v>96.88161991956852</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n"/>
+      <c r="B592" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C592" t="n">
+        <v>2154.737803168337</v>
+      </c>
+      <c r="D592" t="n">
+        <v>1752.931414264385</v>
+      </c>
+      <c r="E592" t="n">
+        <v>2070.819041644427</v>
+      </c>
+      <c r="F592" t="n">
+        <v>1527.20891283512</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n"/>
+      <c r="B593" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C593" t="n">
+        <v>2490.774300412229</v>
+      </c>
+      <c r="D593" t="n">
+        <v>2055.520765536214</v>
+      </c>
+      <c r="E593" t="n">
+        <v>2422.43383041731</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1935.883821558798</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n"/>
+      <c r="B594" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C594" t="n">
+        <v>880.6846048120071</v>
+      </c>
+      <c r="D594" t="n">
+        <v>834.7292448878026</v>
+      </c>
+      <c r="E594" t="n">
+        <v>726.354649244876</v>
+      </c>
+      <c r="F594" t="n">
+        <v>679.5502718015227</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n"/>
+      <c r="B595" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C595" t="n">
+        <v>1079.05743748037</v>
+      </c>
+      <c r="D595" t="n">
+        <v>915.6468757697834</v>
+      </c>
+      <c r="E595" t="n">
+        <v>1209.356969829945</v>
+      </c>
+      <c r="F595" t="n">
+        <v>850.26431521634</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n"/>
+      <c r="B596" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C596" t="n">
+        <v>358.2685407240829</v>
+      </c>
+      <c r="D596" t="n">
+        <v>525.3287348469244</v>
+      </c>
+      <c r="E596" t="n">
+        <v>280.7735627687059</v>
+      </c>
+      <c r="F596" t="n">
+        <v>337.7153633419758</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="50">
     <mergeCell ref="A554:A565"/>
     <mergeCell ref="A26:A37"/>
     <mergeCell ref="A2:A13"/>
@@ -11155,7 +11301,6 @@
     <mergeCell ref="A62:A73"/>
     <mergeCell ref="A278:A289"/>
     <mergeCell ref="A122:A133"/>
-    <mergeCell ref="A578:A588"/>
     <mergeCell ref="A38:A49"/>
     <mergeCell ref="A14:A25"/>
     <mergeCell ref="A470:A481"/>
@@ -11179,6 +11324,7 @@
     <mergeCell ref="A110:A121"/>
     <mergeCell ref="A266:A277"/>
     <mergeCell ref="A398:A409"/>
+    <mergeCell ref="A590:A596"/>
     <mergeCell ref="A218:A229"/>
     <mergeCell ref="A74:A85"/>
     <mergeCell ref="A50:A61"/>
@@ -11189,6 +11335,7 @@
     <mergeCell ref="A422:A433"/>
     <mergeCell ref="A158:A169"/>
     <mergeCell ref="A242:A253"/>
+    <mergeCell ref="A578:A589"/>
     <mergeCell ref="A254:A265"/>
     <mergeCell ref="A374:A385"/>
     <mergeCell ref="A434:A445"/>
